--- a/data/SAC.MI.xlsx
+++ b/data/SAC.MI.xlsx
@@ -22153,6 +22153,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="948">
+      <c r="A948" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B948" t="n">
+        <v>0</v>
+      </c>
+      <c r="C948" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="D948" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="E948" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="F948" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="G948" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B949" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C949" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="D949" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="E949" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="F949" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="G949" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SAC.MI.xlsx
+++ b/data/SAC.MI.xlsx
@@ -22199,6 +22199,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="950">
+      <c r="A950" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B950" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C950" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="D950" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="E950" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="F950" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="G950" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SAC.MI.xlsx
+++ b/data/SAC.MI.xlsx
@@ -22222,6 +22222,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="951">
+      <c r="A951" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B951" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C951" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="D951" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="E951" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="F951" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="G951" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SAC.MI.xlsx
+++ b/data/SAC.MI.xlsx
@@ -22063,22 +22063,22 @@
     </row>
     <row r="944">
       <c r="A944" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B944" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="C944" t="n">
-        <v>1.22000002861023</v>
+        <v>1.23000001907349</v>
       </c>
       <c r="D944" t="n">
-        <v>1.22000002861023</v>
+        <v>1.23000001907349</v>
       </c>
       <c r="E944" t="n">
-        <v>1.22000002861023</v>
+        <v>1.23000001907349</v>
       </c>
       <c r="F944" t="n">
-        <v>1.22000002861023</v>
+        <v>1.23000001907349</v>
       </c>
       <c r="G944" t="s">
         <v>7</v>
@@ -22086,10 +22086,10 @@
     </row>
     <row r="945">
       <c r="A945" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B945" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="C945" t="n">
         <v>1.22000002861023</v>
@@ -22109,22 +22109,22 @@
     </row>
     <row r="946">
       <c r="A946" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B946" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="C946" t="n">
-        <v>1.20000004768372</v>
+        <v>1.22000002861023</v>
       </c>
       <c r="D946" t="n">
-        <v>1.20000004768372</v>
+        <v>1.22000002861023</v>
       </c>
       <c r="E946" t="n">
-        <v>1.20000004768372</v>
+        <v>1.22000002861023</v>
       </c>
       <c r="F946" t="n">
-        <v>1.20000004768372</v>
+        <v>1.22000002861023</v>
       </c>
       <c r="G946" t="s">
         <v>7</v>
@@ -22132,10 +22132,10 @@
     </row>
     <row r="947">
       <c r="A947" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B947" t="n">
-        <v>3000</v>
+        <v>15000</v>
       </c>
       <c r="C947" t="n">
         <v>1.20000004768372</v>
@@ -22155,10 +22155,10 @@
     </row>
     <row r="948">
       <c r="A948" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B948" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="C948" t="n">
         <v>1.20000004768372</v>
@@ -22178,22 +22178,22 @@
     </row>
     <row r="949">
       <c r="A949" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B949" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="C949" t="n">
-        <v>1.21000003814697</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="D949" t="n">
-        <v>1.21000003814697</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="E949" t="n">
-        <v>1.21000003814697</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="F949" t="n">
-        <v>1.21000003814697</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="G949" t="s">
         <v>7</v>
@@ -22201,22 +22201,22 @@
     </row>
     <row r="950">
       <c r="A950" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B950" t="n">
-        <v>18000</v>
+        <v>1500</v>
       </c>
       <c r="C950" t="n">
         <v>1.21000003814697</v>
       </c>
       <c r="D950" t="n">
-        <v>1.20000004768372</v>
+        <v>1.21000003814697</v>
       </c>
       <c r="E950" t="n">
         <v>1.21000003814697</v>
       </c>
       <c r="F950" t="n">
-        <v>1.20000004768372</v>
+        <v>1.21000003814697</v>
       </c>
       <c r="G950" t="s">
         <v>7</v>
@@ -22224,22 +22224,22 @@
     </row>
     <row r="951">
       <c r="A951" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B951" t="n">
-        <v>4500</v>
+        <v>18000</v>
       </c>
       <c r="C951" t="n">
-        <v>1.22000002861023</v>
+        <v>1.21000003814697</v>
       </c>
       <c r="D951" t="n">
-        <v>1.22000002861023</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="E951" t="n">
-        <v>1.22000002861023</v>
+        <v>1.21000003814697</v>
       </c>
       <c r="F951" t="n">
-        <v>1.22000002861023</v>
+        <v>1.20000004768372</v>
       </c>
       <c r="G951" t="s">
         <v>7</v>

--- a/data/SAC.MI.xlsx
+++ b/data/SAC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.02749991416931</v>
       </c>
       <c r="G2" t="n">
-        <v>1.69863843917847</v>
+        <v>1.69863855838776</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G4" t="n">
-        <v>1.52479517459869</v>
+        <v>1.52479529380798</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>1.67559897899628</v>
+        <v>1.67559909820557</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G6" t="n">
-        <v>1.75100088119507</v>
+        <v>1.75100111961365</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G7" t="n">
-        <v>1.81802499294281</v>
+        <v>1.8180251121521</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G9" t="n">
-        <v>1.75519013404846</v>
+        <v>1.75519025325775</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G14" t="n">
-        <v>1.73424518108368</v>
+        <v>1.73424506187439</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G15" t="n">
-        <v>1.69235503673553</v>
+        <v>1.69235515594482</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G16" t="n">
-        <v>1.73424518108368</v>
+        <v>1.73424506187439</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G17" t="n">
-        <v>1.69235503673553</v>
+        <v>1.69235515594482</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G20" t="n">
-        <v>1.59852147102356</v>
+        <v>1.59852159023285</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G21" t="n">
-        <v>1.57841420173645</v>
+        <v>1.57841408252716</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G23" t="n">
-        <v>1.6018728017807</v>
+        <v>1.60187268257141</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G24" t="n">
-        <v>1.6018728017807</v>
+        <v>1.60187268257141</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G25" t="n">
-        <v>1.62700664997101</v>
+        <v>1.62700688838959</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G28" t="n">
-        <v>1.59852147102356</v>
+        <v>1.59852159023285</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G29" t="n">
-        <v>1.54992914199829</v>
+        <v>1.54992926120758</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G30" t="n">
-        <v>1.57841420173645</v>
+        <v>1.57841408252716</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1.75800001621246</v>
       </c>
       <c r="G33" t="n">
-        <v>1.47285151481628</v>
+        <v>1.47285163402557</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>1.75800001621246</v>
       </c>
       <c r="G34" t="n">
-        <v>1.47285151481628</v>
+        <v>1.47285163402557</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G35" t="n">
-        <v>1.41169214248657</v>
+        <v>1.41169226169586</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G36" t="n">
-        <v>1.38655817508698</v>
+        <v>1.38655829429626</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G37" t="n">
-        <v>1.34885728359222</v>
+        <v>1.34885740280151</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G38" t="n">
-        <v>1.31534540653229</v>
+        <v>1.315345287323</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G43" t="n">
-        <v>1.19805335998535</v>
+        <v>1.19805324077606</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G44" t="n">
-        <v>1.20643126964569</v>
+        <v>1.20643150806427</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G45" t="n">
-        <v>1.21062028408051</v>
+        <v>1.21062052249908</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G46" t="n">
-        <v>1.22737646102905</v>
+        <v>1.22737634181976</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G49" t="n">
-        <v>1.30277824401855</v>
+        <v>1.30277812480927</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G50" t="n">
-        <v>1.30277824401855</v>
+        <v>1.30277812480927</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>1.23994326591492</v>
+        <v>1.23994338512421</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G61" t="n">
-        <v>1.24413216114044</v>
+        <v>1.24413228034973</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G62" t="n">
-        <v>1.23994326591492</v>
+        <v>1.23994338512421</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G63" t="n">
-        <v>1.26507723331451</v>
+        <v>1.2650773525238</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G64" t="n">
-        <v>1.27764439582825</v>
+        <v>1.27764427661896</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G67" t="n">
-        <v>1.23994326591492</v>
+        <v>1.23994338512421</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G73" t="n">
-        <v>1.30277824401855</v>
+        <v>1.30277812480927</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G79" t="n">
-        <v>1.27764439582825</v>
+        <v>1.27764427661896</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G80" t="n">
-        <v>1.27764439582825</v>
+        <v>1.27764427661896</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G81" t="n">
-        <v>1.29858922958374</v>
+        <v>1.29858934879303</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G82" t="n">
-        <v>1.34885728359222</v>
+        <v>1.34885740280151</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G83" t="n">
-        <v>1.34047937393188</v>
+        <v>1.3404792547226</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G84" t="n">
-        <v>1.35723507404327</v>
+        <v>1.35723531246185</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G85" t="n">
-        <v>1.32791221141815</v>
+        <v>1.32791244983673</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G86" t="n">
-        <v>1.31953430175781</v>
+        <v>1.3195344209671</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G87" t="n">
-        <v>1.30696725845337</v>
+        <v>1.30696713924408</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.5</v>
       </c>
       <c r="G99" t="n">
-        <v>1.29225814342499</v>
+        <v>1.2922580242157</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G101" t="n">
-        <v>1.21903002262115</v>
+        <v>1.21903014183044</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>1.375</v>
       </c>
       <c r="G104" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G106" t="n">
-        <v>1.14149475097656</v>
+        <v>1.14149463176727</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G107" t="n">
-        <v>1.14149475097656</v>
+        <v>1.14149463176727</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G108" t="n">
-        <v>1.1285719871521</v>
+        <v>1.12857210636139</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G109" t="n">
-        <v>1.1285719871521</v>
+        <v>1.12857210636139</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G110" t="n">
-        <v>1.1285719871521</v>
+        <v>1.12857210636139</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G111" t="n">
-        <v>1.1285719871521</v>
+        <v>1.12857210636139</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G112" t="n">
-        <v>1.1285719871521</v>
+        <v>1.12857210636139</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G113" t="n">
-        <v>1.2104150056839</v>
+        <v>1.21041512489319</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G114" t="n">
-        <v>1.21903002262115</v>
+        <v>1.21903014183044</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G115" t="n">
-        <v>1.1931848526001</v>
+        <v>1.19318497180939</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G116" t="n">
-        <v>1.1931848526001</v>
+        <v>1.19318497180939</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G117" t="n">
-        <v>1.1931848526001</v>
+        <v>1.19318497180939</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G119" t="n">
-        <v>1.18887746334076</v>
+        <v>1.18887734413147</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G120" t="n">
-        <v>1.18887746334076</v>
+        <v>1.18887734413147</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G121" t="n">
-        <v>1.18887746334076</v>
+        <v>1.18887734413147</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G122" t="n">
-        <v>1.2104150056839</v>
+        <v>1.21041512489319</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>1.375</v>
       </c>
       <c r="G123" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>1.375</v>
       </c>
       <c r="G124" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G125" t="n">
-        <v>1.18026232719421</v>
+        <v>1.18026256561279</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G126" t="n">
-        <v>1.18887746334076</v>
+        <v>1.18887734413147</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>1.375</v>
       </c>
       <c r="G127" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>1.375</v>
       </c>
       <c r="G128" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>1.375</v>
       </c>
       <c r="G129" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>1.375</v>
       </c>
       <c r="G130" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.375</v>
       </c>
       <c r="G131" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>1.375</v>
       </c>
       <c r="G132" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.375</v>
       </c>
       <c r="G133" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>1.375</v>
       </c>
       <c r="G134" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.375</v>
       </c>
       <c r="G135" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>1.375</v>
       </c>
       <c r="G136" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>1.375</v>
       </c>
       <c r="G137" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>1.375</v>
       </c>
       <c r="G138" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G139" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G140" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G141" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G142" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G143" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G144" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G145" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G147" t="n">
-        <v>1.24056780338287</v>
+        <v>1.24056792259216</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G148" t="n">
-        <v>1.23195254802704</v>
+        <v>1.23195266723633</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G149" t="n">
-        <v>1.23195254802704</v>
+        <v>1.23195266723633</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G150" t="n">
-        <v>1.23195254802704</v>
+        <v>1.23195266723633</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G152" t="n">
-        <v>1.17595481872559</v>
+        <v>1.17595493793488</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G161" t="n">
-        <v>1.18026232719421</v>
+        <v>1.18026256561279</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G163" t="n">
-        <v>1.12426459789276</v>
+        <v>1.12426447868347</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G164" t="n">
-        <v>1.1458021402359</v>
+        <v>1.14580225944519</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G165" t="n">
-        <v>1.1458021402359</v>
+        <v>1.14580225944519</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G166" t="n">
-        <v>1.1458021402359</v>
+        <v>1.14580225944519</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G167" t="n">
-        <v>1.1458021402359</v>
+        <v>1.14580225944519</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G168" t="n">
-        <v>1.12426459789276</v>
+        <v>1.12426447868347</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G169" t="n">
-        <v>1.12426459789276</v>
+        <v>1.12426447868347</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G178" t="n">
-        <v>1.0984194278717</v>
+        <v>1.09841930866241</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G179" t="n">
-        <v>1.08549690246582</v>
+        <v>1.08549678325653</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G188" t="n">
-        <v>0.999346196651459</v>
+        <v>0.999346256256104</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G189" t="n">
-        <v>0.930425882339478</v>
+        <v>0.930425941944122</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G194" t="n">
-        <v>0.900273084640503</v>
+        <v>0.900273203849792</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G195" t="n">
-        <v>0.900273084640503</v>
+        <v>0.900273203849792</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G196" t="n">
-        <v>0.900273084640503</v>
+        <v>0.900273203849792</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G206" t="n">
-        <v>0.865812957286835</v>
+        <v>0.86581289768219</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G210" t="n">
-        <v>0.908888161182404</v>
+        <v>0.908888101577759</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G211" t="n">
-        <v>0.908888161182404</v>
+        <v>0.908888101577759</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G212" t="n">
-        <v>0.908888161182404</v>
+        <v>0.908888101577759</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G213" t="n">
-        <v>0.908888161182404</v>
+        <v>0.908888101577759</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G214" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G215" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G216" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G217" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G218" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G219" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G220" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G221" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G222" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G223" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G224" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G225" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G226" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G229" t="n">
-        <v>0.865812957286835</v>
+        <v>0.86581289768219</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G230" t="n">
-        <v>0.865812957286835</v>
+        <v>0.86581289768219</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G233" t="n">
-        <v>0.747786641120911</v>
+        <v>0.747786581516266</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G234" t="n">
-        <v>0.680589258670807</v>
+        <v>0.680589318275452</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G237" t="n">
-        <v>0.671974182128906</v>
+        <v>0.671974122524261</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G238" t="n">
-        <v>0.706434369087219</v>
+        <v>0.706434428691864</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G242" t="n">
-        <v>0.792585015296936</v>
+        <v>0.792584955692291</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G243" t="n">
-        <v>0.847721338272095</v>
+        <v>0.84772139787674</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G244" t="n">
-        <v>0.797753989696503</v>
+        <v>0.797754049301147</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G245" t="n">
-        <v>0.835660219192505</v>
+        <v>0.83566027879715</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G247" t="n">
-        <v>0.851167321205139</v>
+        <v>0.851167261600494</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G251" t="n">
-        <v>1.14149475097656</v>
+        <v>1.14149463176727</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G252" t="n">
-        <v>1.07257437705994</v>
+        <v>1.07257413864136</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G253" t="n">
-        <v>1.0122686624527</v>
+        <v>1.01226890087128</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G254" t="n">
-        <v>1.03380656242371</v>
+        <v>1.03380644321442</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G257" t="n">
-        <v>1.07257437705994</v>
+        <v>1.07257413864136</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>1.05965185165405</v>
+        <v>1.05965173244476</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G260" t="n">
-        <v>1.0984194278717</v>
+        <v>1.09841930866241</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G262" t="n">
-        <v>1.0984194278717</v>
+        <v>1.09841930866241</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G263" t="n">
-        <v>1.11134195327759</v>
+        <v>1.1113418340683</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G267" t="n">
-        <v>1.11134195327759</v>
+        <v>1.1113418340683</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G268" t="n">
-        <v>1.11134195327759</v>
+        <v>1.1113418340683</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G269" t="n">
-        <v>1.11134195327759</v>
+        <v>1.1113418340683</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G270" t="n">
-        <v>1.11995697021484</v>
+        <v>1.11995708942413</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G271" t="n">
-        <v>1.11134195327759</v>
+        <v>1.1113418340683</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G273" t="n">
-        <v>1.13718724250793</v>
+        <v>1.13718712329865</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G277" t="n">
-        <v>1.12983453273773</v>
+        <v>1.12983465194702</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>1.12983453273773</v>
+        <v>1.12983465194702</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>1.25</v>
       </c>
       <c r="G279" t="n">
-        <v>1.11204195022583</v>
+        <v>1.11204183101654</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G281" t="n">
-        <v>1.12983453273773</v>
+        <v>1.12983465194702</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G287" t="n">
-        <v>1.01863038539886</v>
+        <v>1.01863026618958</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G288" t="n">
-        <v>1.01863038539886</v>
+        <v>1.01863026618958</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G289" t="n">
-        <v>0.996389508247375</v>
+        <v>0.99638956785202</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G290" t="n">
-        <v>1.02307856082916</v>
+        <v>1.02307868003845</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G291" t="n">
-        <v>1.02307856082916</v>
+        <v>1.02307868003845</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G292" t="n">
-        <v>1.00528585910797</v>
+        <v>1.00528597831726</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G295" t="n">
-        <v>1.00528585910797</v>
+        <v>1.00528597831726</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G300" t="n">
-        <v>1.02307856082916</v>
+        <v>1.02307868003845</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G305" t="n">
-        <v>1.00528585910797</v>
+        <v>1.00528597831726</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G306" t="n">
-        <v>1.00528585910797</v>
+        <v>1.00528597831726</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G307" t="n">
-        <v>1.00528585910797</v>
+        <v>1.00528597831726</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G309" t="n">
-        <v>0.991941332817078</v>
+        <v>0.991941392421722</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G312" t="n">
-        <v>0.996389508247375</v>
+        <v>0.99638956785202</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G313" t="n">
-        <v>0.991941332817078</v>
+        <v>0.991941392421722</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G314" t="n">
-        <v>0.991941332817078</v>
+        <v>0.991941392421722</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G318" t="n">
-        <v>0.920770585536957</v>
+        <v>0.920770645141602</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G321" t="n">
-        <v>1.12983453273773</v>
+        <v>1.12983465194702</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G327" t="n">
-        <v>1.05866396427155</v>
+        <v>1.05866384506226</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>1.05866396427155</v>
+        <v>1.05866384506226</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G334" t="n">
-        <v>1.12093830108643</v>
+        <v>1.12093818187714</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G335" t="n">
-        <v>1.12983453273773</v>
+        <v>1.12983465194702</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>1.09424936771393</v>
+        <v>1.09424912929535</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>1.25</v>
       </c>
       <c r="G337" t="n">
-        <v>1.11204195022583</v>
+        <v>1.11204183101654</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>1.25</v>
       </c>
       <c r="G338" t="n">
-        <v>1.11204195022583</v>
+        <v>1.11204183101654</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G340" t="n">
-        <v>1.09424936771393</v>
+        <v>1.09424912929535</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G341" t="n">
-        <v>1.09424936771393</v>
+        <v>1.09424912929535</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G347" t="n">
-        <v>1.02307856082916</v>
+        <v>1.02307868003845</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G349" t="n">
-        <v>0.996389508247375</v>
+        <v>0.99638956785202</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G350" t="n">
-        <v>0.996389508247375</v>
+        <v>0.99638956785202</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G351" t="n">
-        <v>0.996389508247375</v>
+        <v>0.99638956785202</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G352" t="n">
-        <v>0.996389508247375</v>
+        <v>0.99638956785202</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G353" t="n">
-        <v>1.02307856082916</v>
+        <v>1.02307868003845</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G354" t="n">
-        <v>1.02307856082916</v>
+        <v>1.02307868003845</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>1.05866396427155</v>
+        <v>1.05866384506226</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G356" t="n">
-        <v>1.05866396427155</v>
+        <v>1.05866384506226</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G363" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G412" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G418" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G419" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G420" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G421" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G422" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G423" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G424" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G425" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G442" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G443" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G448" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G449" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G463" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G464" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G465" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G466" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G467" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G468" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G496" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G497" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G498" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G499" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G500" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G518" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G519" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G526" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G527" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G563" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G564" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G565" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G566" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G567" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G568" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G569" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G570" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G571" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G572" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G573" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G574" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G587" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G588" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G589" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G590" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G591" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G592" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G593" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G594" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G599" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G600" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -25176,6 +25176,32 @@
         <v>1.24000000953674</v>
       </c>
       <c r="H954" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B955" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C955" t="n">
+        <v>1.25999999046326</v>
+      </c>
+      <c r="D955" t="n">
+        <v>1.25999999046326</v>
+      </c>
+      <c r="E955" t="n">
+        <v>1.25999999046326</v>
+      </c>
+      <c r="F955" t="n">
+        <v>1.25999999046326</v>
+      </c>
+      <c r="G955" t="n">
+        <v>1.25999999046326</v>
+      </c>
+      <c r="H955" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SAC.MI.xlsx
+++ b/data/SAC.MI.xlsx
@@ -22383,6 +22383,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="958">
+      <c r="A958" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B958" t="n">
+        <v>0</v>
+      </c>
+      <c r="C958" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="D958" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="E958" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="F958" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="G958" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SAC.MI.xlsx
+++ b/data/SAC.MI.xlsx
@@ -22452,6 +22452,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="961">
+      <c r="A961" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B961" t="n">
+        <v>0</v>
+      </c>
+      <c r="C961" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="D961" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="E961" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="F961" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="G961" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B962" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C962" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="D962" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="E962" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="F962"/>
+      <c r="G962" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SAC.MI.xlsx
+++ b/data/SAC.MI.xlsx
@@ -22491,7 +22491,9 @@
       <c r="E962" t="n">
         <v>1.17999994754791</v>
       </c>
-      <c r="F962"/>
+      <c r="F962" t="n">
+        <v>1.1599999666214</v>
+      </c>
       <c r="G962" t="s">
         <v>7</v>
       </c>

--- a/data/SAC.MI.xlsx
+++ b/data/SAC.MI.xlsx
@@ -22498,6 +22498,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="963">
+      <c r="A963" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B963" t="n">
+        <v>0</v>
+      </c>
+      <c r="C963" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="D963" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="E963" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="F963" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="G963" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SAC.MI.xlsx
+++ b/data/SAC.MI.xlsx
@@ -22521,6 +22521,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="964">
+      <c r="A964" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B964" t="n">
+        <v>0</v>
+      </c>
+      <c r="C964" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="D964" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="E964" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="F964" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="G964" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SAC.MI.xlsx
+++ b/data/SAC.MI.xlsx
@@ -22544,6 +22544,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="965">
+      <c r="A965" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B965" t="n">
+        <v>0</v>
+      </c>
+      <c r="C965" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="D965" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="E965" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="F965" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="G965" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B966" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C966" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="D966" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="E966" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="F966"/>
+      <c r="G966" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SAC.MI.xlsx
+++ b/data/SAC.MI.xlsx
@@ -22583,7 +22583,9 @@
       <c r="E966" t="n">
         <v>1.11000001430511</v>
       </c>
-      <c r="F966"/>
+      <c r="F966" t="n">
+        <v>1.12999999523163</v>
+      </c>
       <c r="G966" t="s">
         <v>7</v>
       </c>

--- a/data/SAC.MI.xlsx
+++ b/data/SAC.MI.xlsx
@@ -22590,6 +22590,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="967">
+      <c r="A967" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B967" t="n">
+        <v>0</v>
+      </c>
+      <c r="C967" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="D967" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="E967" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="F967" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="G967" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B968" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C968" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="D968" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="E968" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="F968"/>
+      <c r="G968" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SAC.MI.xlsx
+++ b/data/SAC.MI.xlsx
@@ -22636,6 +22636,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="969">
+      <c r="A969" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B969" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C969" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="D969" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="E969" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="F969" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="G969" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SAC.MI.xlsx
+++ b/data/SAC.MI.xlsx
@@ -22659,6 +22659,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="970">
+      <c r="A970" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B970" t="n">
+        <v>0</v>
+      </c>
+      <c r="C970" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="D970" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="E970" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="F970" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="G970" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SAC.MI.xlsx
+++ b/data/SAC.MI.xlsx
@@ -543,7 +543,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G6" t="n">
-        <v>1.75100088119507</v>
+        <v>1.75100076198578</v>
       </c>
       <c r="H6" t="n">
         <v>144000</v>
@@ -630,7 +630,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G9" t="n">
-        <v>1.75519013404846</v>
+        <v>1.75519001483917</v>
       </c>
       <c r="H9" t="n">
         <v>57000</v>
@@ -659,7 +659,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G10" t="n">
-        <v>1.70492208003998</v>
+        <v>1.70492219924927</v>
       </c>
       <c r="H10" t="n">
         <v>13500</v>
@@ -688,7 +688,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7091109752655</v>
+        <v>1.70911109447479</v>
       </c>
       <c r="H11" t="n">
         <v>18000</v>
@@ -717,7 +717,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7091109752655</v>
+        <v>1.70911109447479</v>
       </c>
       <c r="H12" t="n">
         <v>3000</v>
@@ -746,7 +746,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G13" t="n">
-        <v>1.70492208003998</v>
+        <v>1.70492219924927</v>
       </c>
       <c r="H13" t="n">
         <v>18000</v>
@@ -775,7 +775,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7342449426651</v>
+        <v>1.73424506187439</v>
       </c>
       <c r="H14" t="n">
         <v>1500</v>
@@ -833,7 +833,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7342449426651</v>
+        <v>1.73424506187439</v>
       </c>
       <c r="H16" t="n">
         <v>7500</v>
@@ -949,7 +949,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G20" t="n">
-        <v>1.59852147102356</v>
+        <v>1.59852159023285</v>
       </c>
       <c r="H20" t="n">
         <v>16500</v>
@@ -1007,7 +1007,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G22" t="n">
-        <v>1.60522401332855</v>
+        <v>1.60522389411926</v>
       </c>
       <c r="H22" t="n">
         <v>6000</v>
@@ -1094,7 +1094,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G25" t="n">
-        <v>1.6270067691803</v>
+        <v>1.62700688838959</v>
       </c>
       <c r="H25" t="n">
         <v>12000</v>
@@ -1181,7 +1181,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G28" t="n">
-        <v>1.59852147102356</v>
+        <v>1.59852159023285</v>
       </c>
       <c r="H28" t="n">
         <v>7500</v>
@@ -1587,7 +1587,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G42" t="n">
-        <v>1.21480941772461</v>
+        <v>1.2148095369339</v>
       </c>
       <c r="H42" t="n">
         <v>13500</v>
@@ -1616,7 +1616,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G43" t="n">
-        <v>1.19805324077606</v>
+        <v>1.19805335998535</v>
       </c>
       <c r="H43" t="n">
         <v>10500</v>
@@ -1674,7 +1674,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G45" t="n">
-        <v>1.21062028408051</v>
+        <v>1.21062040328979</v>
       </c>
       <c r="H45" t="n">
         <v>100500</v>
@@ -1703,7 +1703,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G46" t="n">
-        <v>1.22737646102905</v>
+        <v>1.22737634181976</v>
       </c>
       <c r="H46" t="n">
         <v>30000</v>
@@ -1790,7 +1790,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G49" t="n">
-        <v>1.30277824401855</v>
+        <v>1.30277812480927</v>
       </c>
       <c r="H49" t="n">
         <v>48000</v>
@@ -1819,7 +1819,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G50" t="n">
-        <v>1.30277824401855</v>
+        <v>1.30277812480927</v>
       </c>
       <c r="H50" t="n">
         <v>54000</v>
@@ -2109,7 +2109,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G60" t="n">
-        <v>1.24832141399384</v>
+        <v>1.24832129478455</v>
       </c>
       <c r="H60" t="n">
         <v>58500</v>
@@ -2283,7 +2283,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G66" t="n">
-        <v>1.26088833808899</v>
+        <v>1.2608882188797</v>
       </c>
       <c r="H66" t="n">
         <v>21000</v>
@@ -2341,7 +2341,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G68" t="n">
-        <v>1.24832141399384</v>
+        <v>1.24832129478455</v>
       </c>
       <c r="H68" t="n">
         <v>1500</v>
@@ -2486,7 +2486,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G73" t="n">
-        <v>1.30277824401855</v>
+        <v>1.30277812480927</v>
       </c>
       <c r="H73" t="n">
         <v>1500</v>
@@ -2718,7 +2718,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G81" t="n">
-        <v>1.29858934879303</v>
+        <v>1.29858922958374</v>
       </c>
       <c r="H81" t="n">
         <v>33000</v>
@@ -2776,7 +2776,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G83" t="n">
-        <v>1.34047937393188</v>
+        <v>1.3404792547226</v>
       </c>
       <c r="H83" t="n">
         <v>19500</v>
@@ -2805,7 +2805,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G84" t="n">
-        <v>1.35723519325256</v>
+        <v>1.35723531246185</v>
       </c>
       <c r="H84" t="n">
         <v>39000</v>
@@ -2834,7 +2834,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G85" t="n">
-        <v>1.32791221141815</v>
+        <v>1.32791233062744</v>
       </c>
       <c r="H85" t="n">
         <v>19500</v>
@@ -2950,7 +2950,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G89" t="n">
-        <v>1.26088833808899</v>
+        <v>1.2608882188797</v>
       </c>
       <c r="H89" t="n">
         <v>6000</v>
@@ -2979,7 +2979,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G90" t="n">
-        <v>1.26088833808899</v>
+        <v>1.2608882188797</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G91" t="n">
-        <v>1.26088833808899</v>
+        <v>1.2608882188797</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G92" t="n">
-        <v>1.26088833808899</v>
+        <v>1.2608882188797</v>
       </c>
       <c r="H92" t="n">
         <v>1500</v>
@@ -3066,7 +3066,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G93" t="n">
-        <v>1.26088833808899</v>
+        <v>1.2608882188797</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G94" t="n">
-        <v>1.24832141399384</v>
+        <v>1.24832129478455</v>
       </c>
       <c r="H94" t="n">
         <v>10500</v>
@@ -3211,7 +3211,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G98" t="n">
-        <v>1.24832141399384</v>
+        <v>1.24832129478455</v>
       </c>
       <c r="H98" t="n">
         <v>4500</v>
@@ -3269,7 +3269,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G100" t="n">
-        <v>1.2276451587677</v>
+        <v>1.22764503955841</v>
       </c>
       <c r="H100" t="n">
         <v>30000</v>
@@ -3443,7 +3443,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G106" t="n">
-        <v>1.14149463176727</v>
+        <v>1.14149475097656</v>
       </c>
       <c r="H106" t="n">
         <v>4500</v>
@@ -3472,7 +3472,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G107" t="n">
-        <v>1.14149463176727</v>
+        <v>1.14149475097656</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G113" t="n">
-        <v>1.21041512489319</v>
+        <v>1.2104150056839</v>
       </c>
       <c r="H113" t="n">
         <v>9000</v>
@@ -3791,7 +3791,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G118" t="n">
-        <v>1.17164731025696</v>
+        <v>1.17164742946625</v>
       </c>
       <c r="H118" t="n">
         <v>10500</v>
@@ -3820,7 +3820,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G119" t="n">
-        <v>1.18887746334076</v>
+        <v>1.18887734413147</v>
       </c>
       <c r="H119" t="n">
         <v>1500</v>
@@ -3849,7 +3849,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G120" t="n">
-        <v>1.18887746334076</v>
+        <v>1.18887734413147</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G121" t="n">
-        <v>1.18887746334076</v>
+        <v>1.18887734413147</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G122" t="n">
-        <v>1.21041512489319</v>
+        <v>1.2104150056839</v>
       </c>
       <c r="H122" t="n">
         <v>1500</v>
@@ -3994,7 +3994,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G125" t="n">
-        <v>1.18026232719421</v>
+        <v>1.1802624464035</v>
       </c>
       <c r="H125" t="n">
         <v>3000</v>
@@ -4023,7 +4023,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G126" t="n">
-        <v>1.18887746334076</v>
+        <v>1.18887734413147</v>
       </c>
       <c r="H126" t="n">
         <v>3000</v>
@@ -4400,7 +4400,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G139" t="n">
-        <v>1.20610761642456</v>
+        <v>1.20610749721527</v>
       </c>
       <c r="H139" t="n">
         <v>9000</v>
@@ -4429,7 +4429,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G140" t="n">
-        <v>1.20610761642456</v>
+        <v>1.20610749721527</v>
       </c>
       <c r="H140" t="n">
         <v>1500</v>
@@ -4458,7 +4458,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G141" t="n">
-        <v>1.20610761642456</v>
+        <v>1.20610749721527</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G142" t="n">
-        <v>1.20610761642456</v>
+        <v>1.20610749721527</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G143" t="n">
-        <v>1.20610761642456</v>
+        <v>1.20610749721527</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G144" t="n">
-        <v>1.20610761642456</v>
+        <v>1.20610749721527</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G145" t="n">
-        <v>1.20610761642456</v>
+        <v>1.20610749721527</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G147" t="n">
-        <v>1.24056780338287</v>
+        <v>1.24056792259216</v>
       </c>
       <c r="H147" t="n">
         <v>18000</v>
@@ -4748,7 +4748,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G151" t="n">
-        <v>1.16733980178833</v>
+        <v>1.16733992099762</v>
       </c>
       <c r="H151" t="n">
         <v>28500</v>
@@ -4806,7 +4806,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G153" t="n">
-        <v>1.17164731025696</v>
+        <v>1.17164742946625</v>
       </c>
       <c r="H153" t="n">
         <v>7500</v>
@@ -4835,7 +4835,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G154" t="n">
-        <v>1.16733980178833</v>
+        <v>1.16733992099762</v>
       </c>
       <c r="H154" t="n">
         <v>1500</v>
@@ -4864,7 +4864,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G155" t="n">
-        <v>1.16733980178833</v>
+        <v>1.16733992099762</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G156" t="n">
-        <v>1.16733980178833</v>
+        <v>1.16733992099762</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G157" t="n">
-        <v>1.16733980178833</v>
+        <v>1.16733992099762</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G158" t="n">
-        <v>1.16733980178833</v>
+        <v>1.16733992099762</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>1.16733980178833</v>
+        <v>1.16733992099762</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G160" t="n">
-        <v>1.16733980178833</v>
+        <v>1.16733992099762</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G161" t="n">
-        <v>1.18026232719421</v>
+        <v>1.1802624464035</v>
       </c>
       <c r="H161" t="n">
         <v>4500</v>
@@ -5299,7 +5299,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G170" t="n">
-        <v>1.11564934253693</v>
+        <v>1.11564946174622</v>
       </c>
       <c r="H170" t="n">
         <v>24000</v>
@@ -5531,7 +5531,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G178" t="n">
-        <v>1.0984194278717</v>
+        <v>1.09841930866241</v>
       </c>
       <c r="H178" t="n">
         <v>16500</v>
@@ -5560,7 +5560,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G179" t="n">
-        <v>1.08549690246582</v>
+        <v>1.08549678325653</v>
       </c>
       <c r="H179" t="n">
         <v>7500</v>
@@ -5821,7 +5821,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G188" t="n">
-        <v>0.999346256256104</v>
+        <v>0.999346315860748</v>
       </c>
       <c r="H188" t="n">
         <v>4500</v>
@@ -5850,7 +5850,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G189" t="n">
-        <v>0.930425941944122</v>
+        <v>0.930425882339478</v>
       </c>
       <c r="H189" t="n">
         <v>45000</v>
@@ -6140,7 +6140,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>0.878735482692719</v>
+        <v>0.878735423088074</v>
       </c>
       <c r="H199" t="n">
         <v>3000</v>
@@ -6198,7 +6198,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G201" t="n">
-        <v>0.878735482692719</v>
+        <v>0.878735423088074</v>
       </c>
       <c r="H201" t="n">
         <v>3000</v>
@@ -6372,7 +6372,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G207" t="n">
-        <v>0.870120525360107</v>
+        <v>0.870120406150818</v>
       </c>
       <c r="H207" t="n">
         <v>6000</v>
@@ -6401,7 +6401,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G208" t="n">
-        <v>0.870120525360107</v>
+        <v>0.870120406150818</v>
       </c>
       <c r="H208" t="n">
         <v>4500</v>
@@ -6459,7 +6459,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G210" t="n">
-        <v>0.908888220787048</v>
+        <v>0.908888161182404</v>
       </c>
       <c r="H210" t="n">
         <v>1500</v>
@@ -6488,7 +6488,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G211" t="n">
-        <v>0.908888220787048</v>
+        <v>0.908888161182404</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G212" t="n">
-        <v>0.908888220787048</v>
+        <v>0.908888161182404</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G213" t="n">
-        <v>0.908888220787048</v>
+        <v>0.908888161182404</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>0.878735482692719</v>
+        <v>0.878735423088074</v>
       </c>
       <c r="H227" t="n">
         <v>9000</v>
@@ -6981,7 +6981,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G228" t="n">
-        <v>0.878735482692719</v>
+        <v>0.878735423088074</v>
       </c>
       <c r="H228" t="n">
         <v>15000</v>
@@ -7097,7 +7097,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G232" t="n">
-        <v>0.770185887813568</v>
+        <v>0.770185828208923</v>
       </c>
       <c r="H232" t="n">
         <v>42000</v>
@@ -7126,7 +7126,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G233" t="n">
-        <v>0.747786641120911</v>
+        <v>0.747786700725555</v>
       </c>
       <c r="H233" t="n">
         <v>31500</v>
@@ -7242,7 +7242,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G237" t="n">
-        <v>0.671974122524261</v>
+        <v>0.671974182128906</v>
       </c>
       <c r="H237" t="n">
         <v>51000</v>
@@ -7329,7 +7329,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G240" t="n">
-        <v>0.732279658317566</v>
+        <v>0.732279598712921</v>
       </c>
       <c r="H240" t="n">
         <v>25500</v>
@@ -7387,7 +7387,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G242" t="n">
-        <v>0.792585015296936</v>
+        <v>0.792584955692291</v>
       </c>
       <c r="H242" t="n">
         <v>75000</v>
@@ -7416,7 +7416,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G243" t="n">
-        <v>0.84772139787674</v>
+        <v>0.847721338272095</v>
       </c>
       <c r="H243" t="n">
         <v>48000</v>
@@ -7474,7 +7474,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G245" t="n">
-        <v>0.835660219192505</v>
+        <v>0.83566027879715</v>
       </c>
       <c r="H245" t="n">
         <v>43500</v>
@@ -7532,7 +7532,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G247" t="n">
-        <v>0.851167380809784</v>
+        <v>0.851167321205139</v>
       </c>
       <c r="H247" t="n">
         <v>4500</v>
@@ -7590,7 +7590,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G249" t="n">
-        <v>0.990731179714203</v>
+        <v>0.990731239318848</v>
       </c>
       <c r="H249" t="n">
         <v>90000</v>
@@ -7648,7 +7648,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G251" t="n">
-        <v>1.14149463176727</v>
+        <v>1.14149475097656</v>
       </c>
       <c r="H251" t="n">
         <v>184500</v>
@@ -7706,7 +7706,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G253" t="n">
-        <v>1.01226890087128</v>
+        <v>1.01226878166199</v>
       </c>
       <c r="H253" t="n">
         <v>136500</v>
@@ -7764,7 +7764,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G255" t="n">
-        <v>1.04242157936096</v>
+        <v>1.04242169857025</v>
       </c>
       <c r="H255" t="n">
         <v>22500</v>
@@ -7851,7 +7851,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>1.05965173244476</v>
+        <v>1.05965161323547</v>
       </c>
       <c r="H258" t="n">
         <v>18000</v>
@@ -7909,7 +7909,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G260" t="n">
-        <v>1.0984194278717</v>
+        <v>1.09841930866241</v>
       </c>
       <c r="H260" t="n">
         <v>52500</v>
@@ -7967,7 +7967,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G262" t="n">
-        <v>1.0984194278717</v>
+        <v>1.09841930866241</v>
       </c>
       <c r="H262" t="n">
         <v>36000</v>
@@ -8025,7 +8025,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G264" t="n">
-        <v>1.10272681713104</v>
+        <v>1.10272693634033</v>
       </c>
       <c r="H264" t="n">
         <v>18000</v>
@@ -8054,7 +8054,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G265" t="n">
-        <v>1.10272681713104</v>
+        <v>1.10272693634033</v>
       </c>
       <c r="H265" t="n">
         <v>13500</v>
@@ -8083,7 +8083,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G266" t="n">
-        <v>1.10272681713104</v>
+        <v>1.10272693634033</v>
       </c>
       <c r="H266" t="n">
         <v>4500</v>
@@ -8199,7 +8199,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G270" t="n">
-        <v>1.11995697021484</v>
+        <v>1.11995708942413</v>
       </c>
       <c r="H270" t="n">
         <v>7500</v>
@@ -8257,7 +8257,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G272" t="n">
-        <v>1.10272681713104</v>
+        <v>1.10272693634033</v>
       </c>
       <c r="H272" t="n">
         <v>39000</v>
@@ -8286,7 +8286,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G273" t="n">
-        <v>1.13718724250793</v>
+        <v>1.13718712329865</v>
       </c>
       <c r="H273" t="n">
         <v>69000</v>
@@ -8315,7 +8315,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G274" t="n">
-        <v>1.17164731025696</v>
+        <v>1.17164742946625</v>
       </c>
       <c r="H274" t="n">
         <v>54000</v>
@@ -28592,6 +28592,35 @@
         <v>0</v>
       </c>
       <c r="I973" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="s">
+        <v>9</v>
+      </c>
+      <c r="B974" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C974" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="D974" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="E974" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="F974" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="G974" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="H974" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I974" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SAC.MI.xlsx
+++ b/data/SAC.MI.xlsx
@@ -456,7 +456,7 @@
         <v>1.96200001239777</v>
       </c>
       <c r="G3" t="n">
-        <v>1.64376282691956</v>
+        <v>1.64376270771027</v>
       </c>
       <c r="H3" t="n">
         <v>132000</v>
@@ -514,7 +514,7 @@
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>1.67559909820557</v>
+        <v>1.67559897899628</v>
       </c>
       <c r="H5" t="n">
         <v>51000</v>
@@ -543,7 +543,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G6" t="n">
-        <v>1.75100076198578</v>
+        <v>1.75100100040436</v>
       </c>
       <c r="H6" t="n">
         <v>144000</v>
@@ -572,7 +572,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8180251121521</v>
+        <v>1.81802499294281</v>
       </c>
       <c r="H7" t="n">
         <v>87000</v>
@@ -630,7 +630,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G9" t="n">
-        <v>1.75519001483917</v>
+        <v>1.75519013404846</v>
       </c>
       <c r="H9" t="n">
         <v>57000</v>
@@ -659,7 +659,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G10" t="n">
-        <v>1.70492219924927</v>
+        <v>1.70492208003998</v>
       </c>
       <c r="H10" t="n">
         <v>13500</v>
@@ -688,7 +688,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>1.70911109447479</v>
+        <v>1.7091109752655</v>
       </c>
       <c r="H11" t="n">
         <v>18000</v>
@@ -717,7 +717,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>1.70911109447479</v>
+        <v>1.7091109752655</v>
       </c>
       <c r="H12" t="n">
         <v>3000</v>
@@ -746,7 +746,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G13" t="n">
-        <v>1.70492219924927</v>
+        <v>1.70492208003998</v>
       </c>
       <c r="H13" t="n">
         <v>18000</v>
@@ -775,7 +775,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G14" t="n">
-        <v>1.73424506187439</v>
+        <v>1.7342449426651</v>
       </c>
       <c r="H14" t="n">
         <v>1500</v>
@@ -804,7 +804,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G15" t="n">
-        <v>1.69235515594482</v>
+        <v>1.69235503673553</v>
       </c>
       <c r="H15" t="n">
         <v>15000</v>
@@ -833,7 +833,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G16" t="n">
-        <v>1.73424506187439</v>
+        <v>1.7342449426651</v>
       </c>
       <c r="H16" t="n">
         <v>7500</v>
@@ -862,7 +862,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G17" t="n">
-        <v>1.69235515594482</v>
+        <v>1.69235503673553</v>
       </c>
       <c r="H17" t="n">
         <v>12000</v>
@@ -978,7 +978,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G21" t="n">
-        <v>1.57841432094574</v>
+        <v>1.57841444015503</v>
       </c>
       <c r="H21" t="n">
         <v>6000</v>
@@ -1036,7 +1036,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G23" t="n">
-        <v>1.60187268257141</v>
+        <v>1.6018728017807</v>
       </c>
       <c r="H23" t="n">
         <v>13500</v>
@@ -1065,7 +1065,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G24" t="n">
-        <v>1.60187268257141</v>
+        <v>1.6018728017807</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G25" t="n">
-        <v>1.62700688838959</v>
+        <v>1.6270067691803</v>
       </c>
       <c r="H25" t="n">
         <v>12000</v>
@@ -1239,7 +1239,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G30" t="n">
-        <v>1.57841432094574</v>
+        <v>1.57841444015503</v>
       </c>
       <c r="H30" t="n">
         <v>24000</v>
@@ -1297,7 +1297,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G32" t="n">
-        <v>1.44604206085205</v>
+        <v>1.44604194164276</v>
       </c>
       <c r="H32" t="n">
         <v>18000</v>
@@ -1384,7 +1384,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G35" t="n">
-        <v>1.41169226169586</v>
+        <v>1.41169214248657</v>
       </c>
       <c r="H35" t="n">
         <v>12000</v>
@@ -1413,7 +1413,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G36" t="n">
-        <v>1.38655829429626</v>
+        <v>1.38655817508698</v>
       </c>
       <c r="H36" t="n">
         <v>3000</v>
@@ -1442,7 +1442,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G37" t="n">
-        <v>1.34885740280151</v>
+        <v>1.34885728359222</v>
       </c>
       <c r="H37" t="n">
         <v>7500</v>
@@ -1529,7 +1529,7 @@
         <v>1.5</v>
       </c>
       <c r="G40" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H40" t="n">
         <v>15000</v>
@@ -1558,7 +1558,7 @@
         <v>1.5</v>
       </c>
       <c r="G41" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G42" t="n">
-        <v>1.2148095369339</v>
+        <v>1.21480941772461</v>
       </c>
       <c r="H42" t="n">
         <v>13500</v>
@@ -1616,7 +1616,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G43" t="n">
-        <v>1.19805335998535</v>
+        <v>1.19805312156677</v>
       </c>
       <c r="H43" t="n">
         <v>10500</v>
@@ -1674,7 +1674,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G45" t="n">
-        <v>1.21062040328979</v>
+        <v>1.21062016487122</v>
       </c>
       <c r="H45" t="n">
         <v>100500</v>
@@ -1703,7 +1703,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G46" t="n">
-        <v>1.22737634181976</v>
+        <v>1.22737646102905</v>
       </c>
       <c r="H46" t="n">
         <v>30000</v>
@@ -1732,7 +1732,7 @@
         <v>1.5</v>
       </c>
       <c r="G47" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H47" t="n">
         <v>28500</v>
@@ -1790,7 +1790,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G49" t="n">
-        <v>1.30277812480927</v>
+        <v>1.30277824401855</v>
       </c>
       <c r="H49" t="n">
         <v>48000</v>
@@ -1819,7 +1819,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G50" t="n">
-        <v>1.30277812480927</v>
+        <v>1.30277824401855</v>
       </c>
       <c r="H50" t="n">
         <v>54000</v>
@@ -1848,7 +1848,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>1.27345526218414</v>
+        <v>1.27345538139343</v>
       </c>
       <c r="H51" t="n">
         <v>7500</v>
@@ -1906,7 +1906,7 @@
         <v>1.5</v>
       </c>
       <c r="G53" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H53" t="n">
         <v>13500</v>
@@ -1935,7 +1935,7 @@
         <v>1.5</v>
       </c>
       <c r="G54" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>1.5</v>
       </c>
       <c r="G55" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>1.5</v>
       </c>
       <c r="G57" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H57" t="n">
         <v>9000</v>
@@ -2109,7 +2109,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G60" t="n">
-        <v>1.24832129478455</v>
+        <v>1.24832141399384</v>
       </c>
       <c r="H60" t="n">
         <v>58500</v>
@@ -2138,7 +2138,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G61" t="n">
-        <v>1.24413228034973</v>
+        <v>1.24413239955902</v>
       </c>
       <c r="H61" t="n">
         <v>21000</v>
@@ -2196,7 +2196,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G63" t="n">
-        <v>1.2650773525238</v>
+        <v>1.26507723331451</v>
       </c>
       <c r="H63" t="n">
         <v>15000</v>
@@ -2283,7 +2283,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G66" t="n">
-        <v>1.2608882188797</v>
+        <v>1.26088845729828</v>
       </c>
       <c r="H66" t="n">
         <v>21000</v>
@@ -2341,7 +2341,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G68" t="n">
-        <v>1.24832129478455</v>
+        <v>1.24832141399384</v>
       </c>
       <c r="H68" t="n">
         <v>1500</v>
@@ -2370,7 +2370,7 @@
         <v>1.5</v>
       </c>
       <c r="G69" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H69" t="n">
         <v>1500</v>
@@ -2399,7 +2399,7 @@
         <v>1.5</v>
       </c>
       <c r="G70" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G73" t="n">
-        <v>1.30277812480927</v>
+        <v>1.30277824401855</v>
       </c>
       <c r="H73" t="n">
         <v>1500</v>
@@ -2515,7 +2515,7 @@
         <v>1.5</v>
       </c>
       <c r="G74" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H74" t="n">
         <v>31500</v>
@@ -2544,7 +2544,7 @@
         <v>1.5</v>
       </c>
       <c r="G75" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>1.5</v>
       </c>
       <c r="G76" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>1.5</v>
       </c>
       <c r="G77" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H77" t="n">
         <v>3000</v>
@@ -2631,7 +2631,7 @@
         <v>1.5</v>
       </c>
       <c r="G78" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H78" t="n">
         <v>1500</v>
@@ -2718,7 +2718,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G81" t="n">
-        <v>1.29858922958374</v>
+        <v>1.29858934879303</v>
       </c>
       <c r="H81" t="n">
         <v>33000</v>
@@ -2747,7 +2747,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G82" t="n">
-        <v>1.34885740280151</v>
+        <v>1.34885728359222</v>
       </c>
       <c r="H82" t="n">
         <v>78000</v>
@@ -2805,7 +2805,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G84" t="n">
-        <v>1.35723531246185</v>
+        <v>1.35723519325256</v>
       </c>
       <c r="H84" t="n">
         <v>39000</v>
@@ -2834,7 +2834,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G85" t="n">
-        <v>1.32791233062744</v>
+        <v>1.32791221141815</v>
       </c>
       <c r="H85" t="n">
         <v>19500</v>
@@ -2863,7 +2863,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G86" t="n">
-        <v>1.31953430175781</v>
+        <v>1.3195344209671</v>
       </c>
       <c r="H86" t="n">
         <v>9000</v>
@@ -2950,7 +2950,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G89" t="n">
-        <v>1.2608882188797</v>
+        <v>1.26088845729828</v>
       </c>
       <c r="H89" t="n">
         <v>6000</v>
@@ -2979,7 +2979,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G90" t="n">
-        <v>1.2608882188797</v>
+        <v>1.26088845729828</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G91" t="n">
-        <v>1.2608882188797</v>
+        <v>1.26088845729828</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G92" t="n">
-        <v>1.2608882188797</v>
+        <v>1.26088845729828</v>
       </c>
       <c r="H92" t="n">
         <v>1500</v>
@@ -3066,7 +3066,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G93" t="n">
-        <v>1.2608882188797</v>
+        <v>1.26088845729828</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G94" t="n">
-        <v>1.24832129478455</v>
+        <v>1.24832141399384</v>
       </c>
       <c r="H94" t="n">
         <v>10500</v>
@@ -3124,7 +3124,7 @@
         <v>1.5</v>
       </c>
       <c r="G95" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H95" t="n">
         <v>1500</v>
@@ -3211,7 +3211,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G98" t="n">
-        <v>1.24832129478455</v>
+        <v>1.24832141399384</v>
       </c>
       <c r="H98" t="n">
         <v>4500</v>
@@ -3240,7 +3240,7 @@
         <v>1.5</v>
       </c>
       <c r="G99" t="n">
-        <v>1.2922580242157</v>
+        <v>1.29225826263428</v>
       </c>
       <c r="H99" t="n">
         <v>4500</v>
@@ -3298,7 +3298,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G101" t="n">
-        <v>1.21903014183044</v>
+        <v>1.21903002262115</v>
       </c>
       <c r="H101" t="n">
         <v>22500</v>
@@ -3385,7 +3385,7 @@
         <v>1.375</v>
       </c>
       <c r="G104" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H104" t="n">
         <v>9000</v>
@@ -3414,7 +3414,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G105" t="n">
-        <v>1.15441715717316</v>
+        <v>1.15441727638245</v>
       </c>
       <c r="H105" t="n">
         <v>3000</v>
@@ -3675,7 +3675,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G114" t="n">
-        <v>1.21903014183044</v>
+        <v>1.21903002262115</v>
       </c>
       <c r="H114" t="n">
         <v>13500</v>
@@ -3704,7 +3704,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G115" t="n">
-        <v>1.19318497180939</v>
+        <v>1.1931848526001</v>
       </c>
       <c r="H115" t="n">
         <v>4500</v>
@@ -3733,7 +3733,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G116" t="n">
-        <v>1.19318497180939</v>
+        <v>1.1931848526001</v>
       </c>
       <c r="H116" t="n">
         <v>1500</v>
@@ -3762,7 +3762,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G117" t="n">
-        <v>1.19318497180939</v>
+        <v>1.1931848526001</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G118" t="n">
-        <v>1.17164742946625</v>
+        <v>1.17164731025696</v>
       </c>
       <c r="H118" t="n">
         <v>10500</v>
@@ -3936,7 +3936,7 @@
         <v>1.375</v>
       </c>
       <c r="G123" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H123" t="n">
         <v>3000</v>
@@ -3965,7 +3965,7 @@
         <v>1.375</v>
       </c>
       <c r="G124" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G125" t="n">
-        <v>1.1802624464035</v>
+        <v>1.18026232719421</v>
       </c>
       <c r="H125" t="n">
         <v>3000</v>
@@ -4052,7 +4052,7 @@
         <v>1.375</v>
       </c>
       <c r="G127" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H127" t="n">
         <v>1500</v>
@@ -4081,7 +4081,7 @@
         <v>1.375</v>
       </c>
       <c r="G128" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>1.375</v>
       </c>
       <c r="G129" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H129" t="n">
         <v>3000</v>
@@ -4139,7 +4139,7 @@
         <v>1.375</v>
       </c>
       <c r="G130" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>1.375</v>
       </c>
       <c r="G131" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -4197,7 +4197,7 @@
         <v>1.375</v>
       </c>
       <c r="G132" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H132" t="n">
         <v>1500</v>
@@ -4226,7 +4226,7 @@
         <v>1.375</v>
       </c>
       <c r="G133" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>1.375</v>
       </c>
       <c r="G134" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>1.375</v>
       </c>
       <c r="G135" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>1.375</v>
       </c>
       <c r="G136" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>1.375</v>
       </c>
       <c r="G137" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H137" t="n">
         <v>1500</v>
@@ -4371,7 +4371,7 @@
         <v>1.375</v>
       </c>
       <c r="G138" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G139" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610737800598</v>
       </c>
       <c r="H139" t="n">
         <v>9000</v>
@@ -4429,7 +4429,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G140" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610737800598</v>
       </c>
       <c r="H140" t="n">
         <v>1500</v>
@@ -4458,7 +4458,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G141" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610737800598</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G142" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610737800598</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G143" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610737800598</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G144" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610737800598</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G145" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610737800598</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G147" t="n">
-        <v>1.24056792259216</v>
+        <v>1.24056768417358</v>
       </c>
       <c r="H147" t="n">
         <v>18000</v>
@@ -4661,7 +4661,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G148" t="n">
-        <v>1.23195266723633</v>
+        <v>1.23195254802704</v>
       </c>
       <c r="H148" t="n">
         <v>3000</v>
@@ -4690,7 +4690,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G149" t="n">
-        <v>1.23195266723633</v>
+        <v>1.23195254802704</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G150" t="n">
-        <v>1.23195266723633</v>
+        <v>1.23195254802704</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G151" t="n">
-        <v>1.16733992099762</v>
+        <v>1.16733980178833</v>
       </c>
       <c r="H151" t="n">
         <v>28500</v>
@@ -4806,7 +4806,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G153" t="n">
-        <v>1.17164742946625</v>
+        <v>1.17164731025696</v>
       </c>
       <c r="H153" t="n">
         <v>7500</v>
@@ -4835,7 +4835,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G154" t="n">
-        <v>1.16733992099762</v>
+        <v>1.16733980178833</v>
       </c>
       <c r="H154" t="n">
         <v>1500</v>
@@ -4864,7 +4864,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G155" t="n">
-        <v>1.16733992099762</v>
+        <v>1.16733980178833</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G156" t="n">
-        <v>1.16733992099762</v>
+        <v>1.16733980178833</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G157" t="n">
-        <v>1.16733992099762</v>
+        <v>1.16733980178833</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G158" t="n">
-        <v>1.16733992099762</v>
+        <v>1.16733980178833</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>1.16733992099762</v>
+        <v>1.16733980178833</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G160" t="n">
-        <v>1.16733992099762</v>
+        <v>1.16733980178833</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G161" t="n">
-        <v>1.1802624464035</v>
+        <v>1.18026232719421</v>
       </c>
       <c r="H161" t="n">
         <v>4500</v>
@@ -5067,7 +5067,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G162" t="n">
-        <v>1.15441715717316</v>
+        <v>1.15441727638245</v>
       </c>
       <c r="H162" t="n">
         <v>3000</v>
@@ -5096,7 +5096,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G163" t="n">
-        <v>1.12426459789276</v>
+        <v>1.12426447868347</v>
       </c>
       <c r="H163" t="n">
         <v>4500</v>
@@ -5241,7 +5241,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G168" t="n">
-        <v>1.12426459789276</v>
+        <v>1.12426447868347</v>
       </c>
       <c r="H168" t="n">
         <v>1500</v>
@@ -5270,7 +5270,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G169" t="n">
-        <v>1.12426459789276</v>
+        <v>1.12426447868347</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G171" t="n">
-        <v>1.09411180019379</v>
+        <v>1.09411191940308</v>
       </c>
       <c r="H171" t="n">
         <v>19500</v>
@@ -5357,7 +5357,7 @@
         <v>1.25</v>
       </c>
       <c r="G172" t="n">
-        <v>1.07688164710999</v>
+        <v>1.07688188552856</v>
       </c>
       <c r="H172" t="n">
         <v>4500</v>
@@ -5386,7 +5386,7 @@
         <v>1.25</v>
       </c>
       <c r="G173" t="n">
-        <v>1.07688164710999</v>
+        <v>1.07688188552856</v>
       </c>
       <c r="H173" t="n">
         <v>33000</v>
@@ -5415,7 +5415,7 @@
         <v>1.25</v>
       </c>
       <c r="G174" t="n">
-        <v>1.07688164710999</v>
+        <v>1.07688188552856</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>1.25</v>
       </c>
       <c r="G175" t="n">
-        <v>1.07688164710999</v>
+        <v>1.07688188552856</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>1.25</v>
       </c>
       <c r="G176" t="n">
-        <v>1.07688164710999</v>
+        <v>1.07688188552856</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>1.25</v>
       </c>
       <c r="G177" t="n">
-        <v>1.07688164710999</v>
+        <v>1.07688188552856</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G178" t="n">
-        <v>1.09841930866241</v>
+        <v>1.0984194278717</v>
       </c>
       <c r="H178" t="n">
         <v>16500</v>
@@ -5560,7 +5560,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G179" t="n">
-        <v>1.08549678325653</v>
+        <v>1.08549690246582</v>
       </c>
       <c r="H179" t="n">
         <v>7500</v>
@@ -5589,7 +5589,7 @@
         <v>1.25</v>
       </c>
       <c r="G180" t="n">
-        <v>1.07688164710999</v>
+        <v>1.07688188552856</v>
       </c>
       <c r="H180" t="n">
         <v>10500</v>
@@ -5618,7 +5618,7 @@
         <v>1.25</v>
       </c>
       <c r="G181" t="n">
-        <v>1.07688164710999</v>
+        <v>1.07688188552856</v>
       </c>
       <c r="H181" t="n">
         <v>1500</v>
@@ -5879,7 +5879,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G190" t="n">
-        <v>0.926118314266205</v>
+        <v>0.92611837387085</v>
       </c>
       <c r="H190" t="n">
         <v>63000</v>
@@ -5908,7 +5908,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G191" t="n">
-        <v>0.926118314266205</v>
+        <v>0.92611837387085</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G192" t="n">
-        <v>0.926118314266205</v>
+        <v>0.92611837387085</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G193" t="n">
-        <v>0.926118314266205</v>
+        <v>0.92611837387085</v>
       </c>
       <c r="H193" t="n">
         <v>1500</v>
@@ -5995,7 +5995,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G194" t="n">
-        <v>0.900273084640503</v>
+        <v>0.900273144245148</v>
       </c>
       <c r="H194" t="n">
         <v>9000</v>
@@ -6024,7 +6024,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G195" t="n">
-        <v>0.900273084640503</v>
+        <v>0.900273144245148</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G196" t="n">
-        <v>0.900273084640503</v>
+        <v>0.900273144245148</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G197" t="n">
-        <v>0.887350559234619</v>
+        <v>0.887350499629974</v>
       </c>
       <c r="H197" t="n">
         <v>3000</v>
@@ -6111,7 +6111,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G198" t="n">
-        <v>0.887350559234619</v>
+        <v>0.887350499629974</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>0.878735423088074</v>
+        <v>0.878735482692719</v>
       </c>
       <c r="H199" t="n">
         <v>3000</v>
@@ -6169,7 +6169,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>0.89596563577652</v>
+        <v>0.89596551656723</v>
       </c>
       <c r="H200" t="n">
         <v>6000</v>
@@ -6198,7 +6198,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G201" t="n">
-        <v>0.878735423088074</v>
+        <v>0.878735482692719</v>
       </c>
       <c r="H201" t="n">
         <v>3000</v>
@@ -6227,7 +6227,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G202" t="n">
-        <v>0.887350559234619</v>
+        <v>0.887350499629974</v>
       </c>
       <c r="H202" t="n">
         <v>7500</v>
@@ -6314,7 +6314,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G205" t="n">
-        <v>0.849444329738617</v>
+        <v>0.849444389343262</v>
       </c>
       <c r="H205" t="n">
         <v>9000</v>
@@ -6343,7 +6343,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G206" t="n">
-        <v>0.86581289768219</v>
+        <v>0.865812957286835</v>
       </c>
       <c r="H206" t="n">
         <v>3000</v>
@@ -6372,7 +6372,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G207" t="n">
-        <v>0.870120406150818</v>
+        <v>0.870120465755463</v>
       </c>
       <c r="H207" t="n">
         <v>6000</v>
@@ -6401,7 +6401,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G208" t="n">
-        <v>0.870120406150818</v>
+        <v>0.870120465755463</v>
       </c>
       <c r="H208" t="n">
         <v>4500</v>
@@ -6430,7 +6430,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G209" t="n">
-        <v>0.891658067703247</v>
+        <v>0.891658008098602</v>
       </c>
       <c r="H209" t="n">
         <v>3000</v>
@@ -6459,7 +6459,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G210" t="n">
-        <v>0.908888161182404</v>
+        <v>0.908888220787048</v>
       </c>
       <c r="H210" t="n">
         <v>1500</v>
@@ -6488,7 +6488,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G211" t="n">
-        <v>0.908888161182404</v>
+        <v>0.908888220787048</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G212" t="n">
-        <v>0.908888161182404</v>
+        <v>0.908888220787048</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G213" t="n">
-        <v>0.908888161182404</v>
+        <v>0.908888220787048</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>0.878735423088074</v>
+        <v>0.878735482692719</v>
       </c>
       <c r="H227" t="n">
         <v>9000</v>
@@ -6981,7 +6981,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G228" t="n">
-        <v>0.878735423088074</v>
+        <v>0.878735482692719</v>
       </c>
       <c r="H228" t="n">
         <v>15000</v>
@@ -7010,7 +7010,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G229" t="n">
-        <v>0.86581289768219</v>
+        <v>0.865812957286835</v>
       </c>
       <c r="H229" t="n">
         <v>19500</v>
@@ -7039,7 +7039,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G230" t="n">
-        <v>0.86581289768219</v>
+        <v>0.865812957286835</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G234" t="n">
-        <v>0.680589258670807</v>
+        <v>0.680589318275452</v>
       </c>
       <c r="H234" t="n">
         <v>120000</v>
@@ -7271,7 +7271,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G238" t="n">
-        <v>0.706434428691864</v>
+        <v>0.706434369087219</v>
       </c>
       <c r="H238" t="n">
         <v>63000</v>
@@ -7358,7 +7358,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G241" t="n">
-        <v>0.73917156457901</v>
+        <v>0.7391716837883</v>
       </c>
       <c r="H241" t="n">
         <v>12000</v>
@@ -7387,7 +7387,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G242" t="n">
-        <v>0.792584955692291</v>
+        <v>0.792585015296936</v>
       </c>
       <c r="H242" t="n">
         <v>75000</v>
@@ -7561,7 +7561,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G248" t="n">
-        <v>0.89596563577652</v>
+        <v>0.89596551656723</v>
       </c>
       <c r="H248" t="n">
         <v>25500</v>
@@ -7590,7 +7590,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G249" t="n">
-        <v>0.990731239318848</v>
+        <v>0.990731298923492</v>
       </c>
       <c r="H249" t="n">
         <v>90000</v>
@@ -7677,7 +7677,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G252" t="n">
-        <v>1.07257425785065</v>
+        <v>1.07257437705994</v>
       </c>
       <c r="H252" t="n">
         <v>73500</v>
@@ -7764,7 +7764,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G255" t="n">
-        <v>1.04242169857025</v>
+        <v>1.04242157936096</v>
       </c>
       <c r="H255" t="n">
         <v>22500</v>
@@ -7822,7 +7822,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G257" t="n">
-        <v>1.07257425785065</v>
+        <v>1.07257437705994</v>
       </c>
       <c r="H257" t="n">
         <v>45000</v>
@@ -7851,7 +7851,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>1.05965161323547</v>
+        <v>1.05965173244476</v>
       </c>
       <c r="H258" t="n">
         <v>18000</v>
@@ -7880,7 +7880,7 @@
         <v>1.25</v>
       </c>
       <c r="G259" t="n">
-        <v>1.07688164710999</v>
+        <v>1.07688188552856</v>
       </c>
       <c r="H259" t="n">
         <v>4500</v>
@@ -7909,7 +7909,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G260" t="n">
-        <v>1.09841930866241</v>
+        <v>1.0984194278717</v>
       </c>
       <c r="H260" t="n">
         <v>52500</v>
@@ -7967,7 +7967,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G262" t="n">
-        <v>1.09841930866241</v>
+        <v>1.0984194278717</v>
       </c>
       <c r="H262" t="n">
         <v>36000</v>
@@ -8199,7 +8199,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G270" t="n">
-        <v>1.11995708942413</v>
+        <v>1.11995697021484</v>
       </c>
       <c r="H270" t="n">
         <v>7500</v>
@@ -8286,7 +8286,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G273" t="n">
-        <v>1.13718712329865</v>
+        <v>1.13718724250793</v>
       </c>
       <c r="H273" t="n">
         <v>69000</v>
@@ -8315,7 +8315,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G274" t="n">
-        <v>1.17164742946625</v>
+        <v>1.17164731025696</v>
       </c>
       <c r="H274" t="n">
         <v>54000</v>
@@ -8460,7 +8460,7 @@
         <v>1.25</v>
       </c>
       <c r="G279" t="n">
-        <v>1.11204183101654</v>
+        <v>1.11204195022583</v>
       </c>
       <c r="H279" t="n">
         <v>12000</v>
@@ -8576,7 +8576,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G283" t="n">
-        <v>1.07645666599274</v>
+        <v>1.07645654678345</v>
       </c>
       <c r="H283" t="n">
         <v>16500</v>
@@ -8750,7 +8750,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G289" t="n">
-        <v>0.996389448642731</v>
+        <v>0.996389508247375</v>
       </c>
       <c r="H289" t="n">
         <v>12000</v>
@@ -8837,7 +8837,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G292" t="n">
-        <v>1.00528597831726</v>
+        <v>1.00528585910797</v>
       </c>
       <c r="H292" t="n">
         <v>10500</v>
@@ -8866,7 +8866,7 @@
         <v>1.125</v>
       </c>
       <c r="G293" t="n">
-        <v>1.00083780288696</v>
+        <v>1.00083768367767</v>
       </c>
       <c r="H293" t="n">
         <v>6000</v>
@@ -8924,7 +8924,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G295" t="n">
-        <v>1.00528597831726</v>
+        <v>1.00528585910797</v>
       </c>
       <c r="H295" t="n">
         <v>27000</v>
@@ -9214,7 +9214,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G305" t="n">
-        <v>1.00528597831726</v>
+        <v>1.00528585910797</v>
       </c>
       <c r="H305" t="n">
         <v>15000</v>
@@ -9243,7 +9243,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G306" t="n">
-        <v>1.00528597831726</v>
+        <v>1.00528585910797</v>
       </c>
       <c r="H306" t="n">
         <v>3000</v>
@@ -9272,7 +9272,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G307" t="n">
-        <v>1.00528597831726</v>
+        <v>1.00528585910797</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G309" t="n">
-        <v>0.991941392421722</v>
+        <v>0.991941332817078</v>
       </c>
       <c r="H309" t="n">
         <v>1500</v>
@@ -9359,7 +9359,7 @@
         <v>1.125</v>
       </c>
       <c r="G310" t="n">
-        <v>1.00083780288696</v>
+        <v>1.00083768367767</v>
       </c>
       <c r="H310" t="n">
         <v>3000</v>
@@ -9388,7 +9388,7 @@
         <v>1.125</v>
       </c>
       <c r="G311" t="n">
-        <v>1.00083780288696</v>
+        <v>1.00083768367767</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G312" t="n">
-        <v>0.996389448642731</v>
+        <v>0.996389508247375</v>
       </c>
       <c r="H312" t="n">
         <v>1500</v>
@@ -9446,7 +9446,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G313" t="n">
-        <v>0.991941392421722</v>
+        <v>0.991941332817078</v>
       </c>
       <c r="H313" t="n">
         <v>3000</v>
@@ -9475,7 +9475,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G314" t="n">
-        <v>0.991941392421722</v>
+        <v>0.991941332817078</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G318" t="n">
-        <v>0.920770645141602</v>
+        <v>0.920770585536957</v>
       </c>
       <c r="H318" t="n">
         <v>12000</v>
@@ -9620,7 +9620,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G319" t="n">
-        <v>1.06756031513214</v>
+        <v>1.06756019592285</v>
       </c>
       <c r="H319" t="n">
         <v>37500</v>
@@ -9707,7 +9707,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G322" t="n">
-        <v>1.07645666599274</v>
+        <v>1.07645654678345</v>
       </c>
       <c r="H322" t="n">
         <v>27000</v>
@@ -9736,7 +9736,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G323" t="n">
-        <v>1.07645666599274</v>
+        <v>1.07645654678345</v>
       </c>
       <c r="H323" t="n">
         <v>7500</v>
@@ -9765,7 +9765,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G324" t="n">
-        <v>1.07645666599274</v>
+        <v>1.07645654678345</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G325" t="n">
-        <v>1.06756031513214</v>
+        <v>1.06756019592285</v>
       </c>
       <c r="H325" t="n">
         <v>1500</v>
@@ -9823,7 +9823,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G326" t="n">
-        <v>1.06311202049255</v>
+        <v>1.06311213970184</v>
       </c>
       <c r="H326" t="n">
         <v>1500</v>
@@ -9852,7 +9852,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G327" t="n">
-        <v>1.05866384506226</v>
+        <v>1.05866396427155</v>
       </c>
       <c r="H327" t="n">
         <v>4500</v>
@@ -9881,7 +9881,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>1.05866384506226</v>
+        <v>1.05866396427155</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G334" t="n">
-        <v>1.12093818187714</v>
+        <v>1.12093830108643</v>
       </c>
       <c r="H334" t="n">
         <v>63000</v>
@@ -10113,7 +10113,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>1.09424924850464</v>
+        <v>1.09424936771393</v>
       </c>
       <c r="H336" t="n">
         <v>36000</v>
@@ -10142,7 +10142,7 @@
         <v>1.25</v>
       </c>
       <c r="G337" t="n">
-        <v>1.11204183101654</v>
+        <v>1.11204195022583</v>
       </c>
       <c r="H337" t="n">
         <v>22500</v>
@@ -10171,7 +10171,7 @@
         <v>1.25</v>
       </c>
       <c r="G338" t="n">
-        <v>1.11204183101654</v>
+        <v>1.11204195022583</v>
       </c>
       <c r="H338" t="n">
         <v>4500</v>
@@ -10229,7 +10229,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G340" t="n">
-        <v>1.09424924850464</v>
+        <v>1.09424936771393</v>
       </c>
       <c r="H340" t="n">
         <v>13500</v>
@@ -10258,7 +10258,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G341" t="n">
-        <v>1.09424924850464</v>
+        <v>1.09424936771393</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -10287,7 +10287,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G342" t="n">
-        <v>1.06756031513214</v>
+        <v>1.06756019592285</v>
       </c>
       <c r="H342" t="n">
         <v>6000</v>
@@ -10374,7 +10374,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G345" t="n">
-        <v>1.07645666599274</v>
+        <v>1.07645654678345</v>
       </c>
       <c r="H345" t="n">
         <v>4500</v>
@@ -10490,7 +10490,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G349" t="n">
-        <v>0.996389448642731</v>
+        <v>0.996389508247375</v>
       </c>
       <c r="H349" t="n">
         <v>24000</v>
@@ -10519,7 +10519,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G350" t="n">
-        <v>0.996389448642731</v>
+        <v>0.996389508247375</v>
       </c>
       <c r="H350" t="n">
         <v>3000</v>
@@ -10548,7 +10548,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G351" t="n">
-        <v>0.996389448642731</v>
+        <v>0.996389508247375</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -10577,7 +10577,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G352" t="n">
-        <v>0.996389448642731</v>
+        <v>0.996389508247375</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>1.05866384506226</v>
+        <v>1.05866396427155</v>
       </c>
       <c r="H355" t="n">
         <v>7500</v>
@@ -10693,7 +10693,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G356" t="n">
-        <v>1.05866384506226</v>
+        <v>1.05866396427155</v>
       </c>
       <c r="H356" t="n">
         <v>9000</v>
@@ -10896,7 +10896,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G363" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H363" t="n">
         <v>22500</v>
@@ -12317,7 +12317,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G412" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H412" t="n">
         <v>1500</v>
@@ -12491,7 +12491,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G418" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H418" t="n">
         <v>3000</v>
@@ -12520,7 +12520,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G419" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G420" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G421" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H421" t="n">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G422" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H422" t="n">
         <v>3000</v>
@@ -12636,7 +12636,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G423" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H423" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G424" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H424" t="n">
         <v>0</v>
@@ -12694,7 +12694,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G425" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G442" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H442" t="n">
         <v>3000</v>
@@ -13216,7 +13216,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G443" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G448" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H448" t="n">
         <v>1500</v>
@@ -13390,7 +13390,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G449" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H449" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G463" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H463" t="n">
         <v>6000</v>
@@ -13825,7 +13825,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G464" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H464" t="n">
         <v>1500</v>
@@ -13854,7 +13854,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G465" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H465" t="n">
         <v>6000</v>
@@ -13883,7 +13883,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G466" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H466" t="n">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G467" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H467" t="n">
         <v>1500</v>
@@ -13941,7 +13941,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G468" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H468" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G496" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H496" t="n">
         <v>6000</v>
@@ -14782,7 +14782,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G497" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H497" t="n">
         <v>0</v>
@@ -14811,7 +14811,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G498" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H498" t="n">
         <v>6000</v>
@@ -14840,7 +14840,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G499" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H499" t="n">
         <v>1500</v>
@@ -14869,7 +14869,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G500" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G518" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H518" t="n">
         <v>3000</v>
@@ -15420,7 +15420,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G519" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H519" t="n">
         <v>0</v>
@@ -15623,7 +15623,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G526" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H526" t="n">
         <v>24000</v>
@@ -15652,7 +15652,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G527" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H527" t="n">
         <v>18000</v>
@@ -16696,7 +16696,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G563" t="n">
-        <v>0.977511882781982</v>
+        <v>0.977511942386627</v>
       </c>
       <c r="H563" t="n">
         <v>10500</v>
@@ -16725,7 +16725,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G564" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H564" t="n">
         <v>9000</v>
@@ -16754,7 +16754,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G565" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H565" t="n">
         <v>0</v>
@@ -16783,7 +16783,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G566" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -16812,7 +16812,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G567" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G568" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H568" t="n">
         <v>4500</v>
@@ -16870,7 +16870,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G569" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H569" t="n">
         <v>0</v>
@@ -16899,7 +16899,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G570" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H570" t="n">
         <v>1500</v>
@@ -16928,7 +16928,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G571" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G572" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H572" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G573" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H573" t="n">
         <v>0</v>
@@ -17015,7 +17015,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G574" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H574" t="n">
         <v>0</v>
@@ -17392,7 +17392,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G587" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H587" t="n">
         <v>1500</v>
@@ -17421,7 +17421,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G588" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H588" t="n">
         <v>0</v>
@@ -17450,7 +17450,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G589" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -17479,7 +17479,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G590" t="n">
-        <v>0.977511882781982</v>
+        <v>0.977511942386627</v>
       </c>
       <c r="H590" t="n">
         <v>12000</v>
@@ -17508,7 +17508,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G591" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H591" t="n">
         <v>1500</v>
@@ -17537,7 +17537,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G592" t="n">
-        <v>0.977511882781982</v>
+        <v>0.977511942386627</v>
       </c>
       <c r="H592" t="n">
         <v>1500</v>
@@ -17566,7 +17566,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G593" t="n">
-        <v>0.977511882781982</v>
+        <v>0.977511942386627</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G594" t="n">
-        <v>0.977511882781982</v>
+        <v>0.977511942386627</v>
       </c>
       <c r="H594" t="n">
         <v>3000</v>
@@ -17624,7 +17624,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>0.977511882781982</v>
+        <v>0.977511942386627</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -17740,7 +17740,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G599" t="n">
-        <v>0.977511882781982</v>
+        <v>0.977511942386627</v>
       </c>
       <c r="H599" t="n">
         <v>9000</v>
@@ -17769,7 +17769,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G600" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H600" t="n">
         <v>1500</v>
@@ -28621,6 +28621,64 @@
         <v>12000</v>
       </c>
       <c r="I974" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="s">
+        <v>9</v>
+      </c>
+      <c r="B975" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C975" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="D975" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="E975" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="F975" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="G975" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="H975" t="n">
+        <v>0</v>
+      </c>
+      <c r="I975" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="s">
+        <v>9</v>
+      </c>
+      <c r="B976" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C976" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="D976" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="E976" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="F976" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="G976" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="H976" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I976" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SAC.MI.xlsx
+++ b/data/SAC.MI.xlsx
@@ -543,7 +543,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G6" t="n">
-        <v>1.75100100040436</v>
+        <v>1.75100088119507</v>
       </c>
       <c r="H6" t="n">
         <v>144000</v>
@@ -659,7 +659,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G10" t="n">
-        <v>1.70492208003998</v>
+        <v>1.70492219924927</v>
       </c>
       <c r="H10" t="n">
         <v>13500</v>
@@ -688,7 +688,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7091109752655</v>
+        <v>1.70911109447479</v>
       </c>
       <c r="H11" t="n">
         <v>18000</v>
@@ -717,7 +717,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7091109752655</v>
+        <v>1.70911109447479</v>
       </c>
       <c r="H12" t="n">
         <v>3000</v>
@@ -746,7 +746,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G13" t="n">
-        <v>1.70492208003998</v>
+        <v>1.70492219924927</v>
       </c>
       <c r="H13" t="n">
         <v>18000</v>
@@ -775,7 +775,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7342449426651</v>
+        <v>1.73424506187439</v>
       </c>
       <c r="H14" t="n">
         <v>1500</v>
@@ -833,7 +833,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7342449426651</v>
+        <v>1.73424506187439</v>
       </c>
       <c r="H16" t="n">
         <v>7500</v>
@@ -891,7 +891,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G18" t="n">
-        <v>1.61192631721497</v>
+        <v>1.61192619800568</v>
       </c>
       <c r="H18" t="n">
         <v>28500</v>
@@ -920,7 +920,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G19" t="n">
-        <v>1.59181916713715</v>
+        <v>1.59181904792786</v>
       </c>
       <c r="H19" t="n">
         <v>16500</v>
@@ -949,7 +949,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G20" t="n">
-        <v>1.59852159023285</v>
+        <v>1.59852147102356</v>
       </c>
       <c r="H20" t="n">
         <v>16500</v>
@@ -978,7 +978,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G21" t="n">
-        <v>1.57841444015503</v>
+        <v>1.57841432094574</v>
       </c>
       <c r="H21" t="n">
         <v>6000</v>
@@ -1181,7 +1181,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G28" t="n">
-        <v>1.59852159023285</v>
+        <v>1.59852147102356</v>
       </c>
       <c r="H28" t="n">
         <v>7500</v>
@@ -1239,7 +1239,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G30" t="n">
-        <v>1.57841444015503</v>
+        <v>1.57841432094574</v>
       </c>
       <c r="H30" t="n">
         <v>24000</v>
@@ -1297,7 +1297,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G32" t="n">
-        <v>1.44604194164276</v>
+        <v>1.44604182243347</v>
       </c>
       <c r="H32" t="n">
         <v>18000</v>
@@ -1413,7 +1413,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G36" t="n">
-        <v>1.38655817508698</v>
+        <v>1.38655829429626</v>
       </c>
       <c r="H36" t="n">
         <v>3000</v>
@@ -1471,7 +1471,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G38" t="n">
-        <v>1.315345287323</v>
+        <v>1.31534516811371</v>
       </c>
       <c r="H38" t="n">
         <v>12000</v>
@@ -1529,7 +1529,7 @@
         <v>1.5</v>
       </c>
       <c r="G40" t="n">
-        <v>1.25669944286346</v>
+        <v>1.25669932365417</v>
       </c>
       <c r="H40" t="n">
         <v>15000</v>
@@ -1558,7 +1558,7 @@
         <v>1.5</v>
       </c>
       <c r="G41" t="n">
-        <v>1.25669944286346</v>
+        <v>1.25669932365417</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G43" t="n">
-        <v>1.19805312156677</v>
+        <v>1.19805324077606</v>
       </c>
       <c r="H43" t="n">
         <v>10500</v>
@@ -1645,7 +1645,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G44" t="n">
-        <v>1.20643138885498</v>
+        <v>1.20643150806427</v>
       </c>
       <c r="H44" t="n">
         <v>7500</v>
@@ -1674,7 +1674,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G45" t="n">
-        <v>1.21062016487122</v>
+        <v>1.21062028408051</v>
       </c>
       <c r="H45" t="n">
         <v>100500</v>
@@ -1703,7 +1703,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G46" t="n">
-        <v>1.22737646102905</v>
+        <v>1.22737634181976</v>
       </c>
       <c r="H46" t="n">
         <v>30000</v>
@@ -1732,7 +1732,7 @@
         <v>1.5</v>
       </c>
       <c r="G47" t="n">
-        <v>1.25669944286346</v>
+        <v>1.25669932365417</v>
       </c>
       <c r="H47" t="n">
         <v>28500</v>
@@ -1906,7 +1906,7 @@
         <v>1.5</v>
       </c>
       <c r="G53" t="n">
-        <v>1.25669944286346</v>
+        <v>1.25669932365417</v>
       </c>
       <c r="H53" t="n">
         <v>13500</v>
@@ -1935,7 +1935,7 @@
         <v>1.5</v>
       </c>
       <c r="G54" t="n">
-        <v>1.25669944286346</v>
+        <v>1.25669932365417</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>1.5</v>
       </c>
       <c r="G55" t="n">
-        <v>1.25669944286346</v>
+        <v>1.25669932365417</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>1.5</v>
       </c>
       <c r="G57" t="n">
-        <v>1.25669944286346</v>
+        <v>1.25669932365417</v>
       </c>
       <c r="H57" t="n">
         <v>9000</v>
@@ -2051,7 +2051,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>1.23994338512421</v>
+        <v>1.23994326591492</v>
       </c>
       <c r="H58" t="n">
         <v>7500</v>
@@ -2138,7 +2138,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G61" t="n">
-        <v>1.24413239955902</v>
+        <v>1.24413228034973</v>
       </c>
       <c r="H61" t="n">
         <v>21000</v>
@@ -2167,7 +2167,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G62" t="n">
-        <v>1.23994338512421</v>
+        <v>1.23994326591492</v>
       </c>
       <c r="H62" t="n">
         <v>10500</v>
@@ -2225,7 +2225,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G64" t="n">
-        <v>1.27764439582825</v>
+        <v>1.27764427661896</v>
       </c>
       <c r="H64" t="n">
         <v>4500</v>
@@ -2283,7 +2283,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G66" t="n">
-        <v>1.26088845729828</v>
+        <v>1.26088833808899</v>
       </c>
       <c r="H66" t="n">
         <v>21000</v>
@@ -2312,7 +2312,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G67" t="n">
-        <v>1.23994338512421</v>
+        <v>1.23994326591492</v>
       </c>
       <c r="H67" t="n">
         <v>16500</v>
@@ -2370,7 +2370,7 @@
         <v>1.5</v>
       </c>
       <c r="G69" t="n">
-        <v>1.25669944286346</v>
+        <v>1.25669932365417</v>
       </c>
       <c r="H69" t="n">
         <v>1500</v>
@@ -2399,7 +2399,7 @@
         <v>1.5</v>
       </c>
       <c r="G70" t="n">
-        <v>1.25669944286346</v>
+        <v>1.25669932365417</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>1.5</v>
       </c>
       <c r="G74" t="n">
-        <v>1.25669944286346</v>
+        <v>1.25669932365417</v>
       </c>
       <c r="H74" t="n">
         <v>31500</v>
@@ -2544,7 +2544,7 @@
         <v>1.5</v>
       </c>
       <c r="G75" t="n">
-        <v>1.25669944286346</v>
+        <v>1.25669932365417</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>1.5</v>
       </c>
       <c r="G76" t="n">
-        <v>1.25669944286346</v>
+        <v>1.25669932365417</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>1.5</v>
       </c>
       <c r="G77" t="n">
-        <v>1.25669944286346</v>
+        <v>1.25669932365417</v>
       </c>
       <c r="H77" t="n">
         <v>3000</v>
@@ -2631,7 +2631,7 @@
         <v>1.5</v>
       </c>
       <c r="G78" t="n">
-        <v>1.25669944286346</v>
+        <v>1.25669932365417</v>
       </c>
       <c r="H78" t="n">
         <v>1500</v>
@@ -2660,7 +2660,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G79" t="n">
-        <v>1.27764439582825</v>
+        <v>1.27764427661896</v>
       </c>
       <c r="H79" t="n">
         <v>12000</v>
@@ -2689,7 +2689,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G80" t="n">
-        <v>1.27764439582825</v>
+        <v>1.27764427661896</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G89" t="n">
-        <v>1.26088845729828</v>
+        <v>1.26088833808899</v>
       </c>
       <c r="H89" t="n">
         <v>6000</v>
@@ -2979,7 +2979,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G90" t="n">
-        <v>1.26088845729828</v>
+        <v>1.26088833808899</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G91" t="n">
-        <v>1.26088845729828</v>
+        <v>1.26088833808899</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G92" t="n">
-        <v>1.26088845729828</v>
+        <v>1.26088833808899</v>
       </c>
       <c r="H92" t="n">
         <v>1500</v>
@@ -3066,7 +3066,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G93" t="n">
-        <v>1.26088845729828</v>
+        <v>1.26088833808899</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>1.5</v>
       </c>
       <c r="G95" t="n">
-        <v>1.25669944286346</v>
+        <v>1.25669932365417</v>
       </c>
       <c r="H95" t="n">
         <v>1500</v>
@@ -3240,7 +3240,7 @@
         <v>1.5</v>
       </c>
       <c r="G99" t="n">
-        <v>1.29225826263428</v>
+        <v>1.29225814342499</v>
       </c>
       <c r="H99" t="n">
         <v>4500</v>
@@ -3269,7 +3269,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G100" t="n">
-        <v>1.22764503955841</v>
+        <v>1.2276451587677</v>
       </c>
       <c r="H100" t="n">
         <v>30000</v>
@@ -3298,7 +3298,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G101" t="n">
-        <v>1.21903002262115</v>
+        <v>1.21903014183044</v>
       </c>
       <c r="H101" t="n">
         <v>22500</v>
@@ -3327,7 +3327,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>1.27502810955048</v>
+        <v>1.27502799034119</v>
       </c>
       <c r="H102" t="n">
         <v>9000</v>
@@ -3356,7 +3356,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G103" t="n">
-        <v>1.27502810955048</v>
+        <v>1.27502799034119</v>
       </c>
       <c r="H103" t="n">
         <v>9000</v>
@@ -3385,7 +3385,7 @@
         <v>1.375</v>
       </c>
       <c r="G104" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H104" t="n">
         <v>9000</v>
@@ -3675,7 +3675,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G114" t="n">
-        <v>1.21903002262115</v>
+        <v>1.21903014183044</v>
       </c>
       <c r="H114" t="n">
         <v>13500</v>
@@ -3936,7 +3936,7 @@
         <v>1.375</v>
       </c>
       <c r="G123" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H123" t="n">
         <v>3000</v>
@@ -3965,7 +3965,7 @@
         <v>1.375</v>
       </c>
       <c r="G124" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -4052,7 +4052,7 @@
         <v>1.375</v>
       </c>
       <c r="G127" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H127" t="n">
         <v>1500</v>
@@ -4081,7 +4081,7 @@
         <v>1.375</v>
       </c>
       <c r="G128" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>1.375</v>
       </c>
       <c r="G129" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H129" t="n">
         <v>3000</v>
@@ -4139,7 +4139,7 @@
         <v>1.375</v>
       </c>
       <c r="G130" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>1.375</v>
       </c>
       <c r="G131" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -4197,7 +4197,7 @@
         <v>1.375</v>
       </c>
       <c r="G132" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H132" t="n">
         <v>1500</v>
@@ -4226,7 +4226,7 @@
         <v>1.375</v>
       </c>
       <c r="G133" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>1.375</v>
       </c>
       <c r="G134" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>1.375</v>
       </c>
       <c r="G135" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>1.375</v>
       </c>
       <c r="G136" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>1.375</v>
       </c>
       <c r="G137" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H137" t="n">
         <v>1500</v>
@@ -4371,7 +4371,7 @@
         <v>1.375</v>
       </c>
       <c r="G138" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G139" t="n">
-        <v>1.20610737800598</v>
+        <v>1.20610749721527</v>
       </c>
       <c r="H139" t="n">
         <v>9000</v>
@@ -4429,7 +4429,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G140" t="n">
-        <v>1.20610737800598</v>
+        <v>1.20610749721527</v>
       </c>
       <c r="H140" t="n">
         <v>1500</v>
@@ -4458,7 +4458,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G141" t="n">
-        <v>1.20610737800598</v>
+        <v>1.20610749721527</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G142" t="n">
-        <v>1.20610737800598</v>
+        <v>1.20610749721527</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G143" t="n">
-        <v>1.20610737800598</v>
+        <v>1.20610749721527</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G144" t="n">
-        <v>1.20610737800598</v>
+        <v>1.20610749721527</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G145" t="n">
-        <v>1.20610737800598</v>
+        <v>1.20610749721527</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G147" t="n">
-        <v>1.24056768417358</v>
+        <v>1.24056780338287</v>
       </c>
       <c r="H147" t="n">
         <v>18000</v>
@@ -4661,7 +4661,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G148" t="n">
-        <v>1.23195254802704</v>
+        <v>1.23195266723633</v>
       </c>
       <c r="H148" t="n">
         <v>3000</v>
@@ -4690,7 +4690,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G149" t="n">
-        <v>1.23195254802704</v>
+        <v>1.23195266723633</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G150" t="n">
-        <v>1.23195254802704</v>
+        <v>1.23195266723633</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G151" t="n">
-        <v>1.16733980178833</v>
+        <v>1.16733992099762</v>
       </c>
       <c r="H151" t="n">
         <v>28500</v>
@@ -4835,7 +4835,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G154" t="n">
-        <v>1.16733980178833</v>
+        <v>1.16733992099762</v>
       </c>
       <c r="H154" t="n">
         <v>1500</v>
@@ -4864,7 +4864,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G155" t="n">
-        <v>1.16733980178833</v>
+        <v>1.16733992099762</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G156" t="n">
-        <v>1.16733980178833</v>
+        <v>1.16733992099762</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G157" t="n">
-        <v>1.16733980178833</v>
+        <v>1.16733992099762</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G158" t="n">
-        <v>1.16733980178833</v>
+        <v>1.16733992099762</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>1.16733980178833</v>
+        <v>1.16733992099762</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G160" t="n">
-        <v>1.16733980178833</v>
+        <v>1.16733992099762</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>1.25</v>
       </c>
       <c r="G172" t="n">
-        <v>1.07688188552856</v>
+        <v>1.07688176631927</v>
       </c>
       <c r="H172" t="n">
         <v>4500</v>
@@ -5386,7 +5386,7 @@
         <v>1.25</v>
       </c>
       <c r="G173" t="n">
-        <v>1.07688188552856</v>
+        <v>1.07688176631927</v>
       </c>
       <c r="H173" t="n">
         <v>33000</v>
@@ -5415,7 +5415,7 @@
         <v>1.25</v>
       </c>
       <c r="G174" t="n">
-        <v>1.07688188552856</v>
+        <v>1.07688176631927</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>1.25</v>
       </c>
       <c r="G175" t="n">
-        <v>1.07688188552856</v>
+        <v>1.07688176631927</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>1.25</v>
       </c>
       <c r="G176" t="n">
-        <v>1.07688188552856</v>
+        <v>1.07688176631927</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>1.25</v>
       </c>
       <c r="G177" t="n">
-        <v>1.07688188552856</v>
+        <v>1.07688176631927</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
         <v>1.25</v>
       </c>
       <c r="G180" t="n">
-        <v>1.07688188552856</v>
+        <v>1.07688176631927</v>
       </c>
       <c r="H180" t="n">
         <v>10500</v>
@@ -5618,7 +5618,7 @@
         <v>1.25</v>
       </c>
       <c r="G181" t="n">
-        <v>1.07688188552856</v>
+        <v>1.07688176631927</v>
       </c>
       <c r="H181" t="n">
         <v>1500</v>
@@ -5850,7 +5850,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G189" t="n">
-        <v>0.930425882339478</v>
+        <v>0.930425822734833</v>
       </c>
       <c r="H189" t="n">
         <v>45000</v>
@@ -5995,7 +5995,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G194" t="n">
-        <v>0.900273144245148</v>
+        <v>0.900273084640503</v>
       </c>
       <c r="H194" t="n">
         <v>9000</v>
@@ -6024,7 +6024,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G195" t="n">
-        <v>0.900273144245148</v>
+        <v>0.900273084640503</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G196" t="n">
-        <v>0.900273144245148</v>
+        <v>0.900273084640503</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G197" t="n">
-        <v>0.887350499629974</v>
+        <v>0.887350618839264</v>
       </c>
       <c r="H197" t="n">
         <v>3000</v>
@@ -6111,7 +6111,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G198" t="n">
-        <v>0.887350499629974</v>
+        <v>0.887350618839264</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>0.878735482692719</v>
+        <v>0.878735542297363</v>
       </c>
       <c r="H199" t="n">
         <v>3000</v>
@@ -6169,7 +6169,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>0.89596551656723</v>
+        <v>0.895965576171875</v>
       </c>
       <c r="H200" t="n">
         <v>6000</v>
@@ -6198,7 +6198,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G201" t="n">
-        <v>0.878735482692719</v>
+        <v>0.878735542297363</v>
       </c>
       <c r="H201" t="n">
         <v>3000</v>
@@ -6227,7 +6227,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G202" t="n">
-        <v>0.887350499629974</v>
+        <v>0.887350618839264</v>
       </c>
       <c r="H202" t="n">
         <v>7500</v>
@@ -6343,7 +6343,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G206" t="n">
-        <v>0.865812957286835</v>
+        <v>0.865813016891479</v>
       </c>
       <c r="H206" t="n">
         <v>3000</v>
@@ -6430,7 +6430,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G209" t="n">
-        <v>0.891658008098602</v>
+        <v>0.891658067703247</v>
       </c>
       <c r="H209" t="n">
         <v>3000</v>
@@ -6575,7 +6575,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G214" t="n">
-        <v>0.874427974224091</v>
+        <v>0.874428033828735</v>
       </c>
       <c r="H214" t="n">
         <v>3000</v>
@@ -6604,7 +6604,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G215" t="n">
-        <v>0.874427974224091</v>
+        <v>0.874428033828735</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G216" t="n">
-        <v>0.874427974224091</v>
+        <v>0.874428033828735</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6662,7 +6662,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G217" t="n">
-        <v>0.874427974224091</v>
+        <v>0.874428033828735</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G218" t="n">
-        <v>0.874427974224091</v>
+        <v>0.874428033828735</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G219" t="n">
-        <v>0.874427974224091</v>
+        <v>0.874428033828735</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G220" t="n">
-        <v>0.874427974224091</v>
+        <v>0.874428033828735</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G221" t="n">
-        <v>0.874427974224091</v>
+        <v>0.874428033828735</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G222" t="n">
-        <v>0.874427974224091</v>
+        <v>0.874428033828735</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G223" t="n">
-        <v>0.874427974224091</v>
+        <v>0.874428033828735</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G224" t="n">
-        <v>0.874427974224091</v>
+        <v>0.874428033828735</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G225" t="n">
-        <v>0.874427974224091</v>
+        <v>0.874428033828735</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G226" t="n">
-        <v>0.874427974224091</v>
+        <v>0.874428033828735</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>0.878735482692719</v>
+        <v>0.878735542297363</v>
       </c>
       <c r="H227" t="n">
         <v>9000</v>
@@ -6981,7 +6981,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G228" t="n">
-        <v>0.878735482692719</v>
+        <v>0.878735542297363</v>
       </c>
       <c r="H228" t="n">
         <v>15000</v>
@@ -7010,7 +7010,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G229" t="n">
-        <v>0.865812957286835</v>
+        <v>0.865813016891479</v>
       </c>
       <c r="H229" t="n">
         <v>19500</v>
@@ -7039,7 +7039,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G230" t="n">
-        <v>0.865812957286835</v>
+        <v>0.865813016891479</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G241" t="n">
-        <v>0.7391716837883</v>
+        <v>0.739171624183655</v>
       </c>
       <c r="H241" t="n">
         <v>12000</v>
@@ -7416,7 +7416,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G243" t="n">
-        <v>0.847721338272095</v>
+        <v>0.84772127866745</v>
       </c>
       <c r="H243" t="n">
         <v>48000</v>
@@ -7445,7 +7445,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G244" t="n">
-        <v>0.797753989696503</v>
+        <v>0.797754049301147</v>
       </c>
       <c r="H244" t="n">
         <v>63000</v>
@@ -7561,7 +7561,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G248" t="n">
-        <v>0.89596551656723</v>
+        <v>0.895965576171875</v>
       </c>
       <c r="H248" t="n">
         <v>25500</v>
@@ -7677,7 +7677,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G252" t="n">
-        <v>1.07257437705994</v>
+        <v>1.07257425785065</v>
       </c>
       <c r="H252" t="n">
         <v>73500</v>
@@ -7822,7 +7822,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G257" t="n">
-        <v>1.07257437705994</v>
+        <v>1.07257425785065</v>
       </c>
       <c r="H257" t="n">
         <v>45000</v>
@@ -7851,7 +7851,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>1.05965173244476</v>
+        <v>1.05965161323547</v>
       </c>
       <c r="H258" t="n">
         <v>18000</v>
@@ -7880,7 +7880,7 @@
         <v>1.25</v>
       </c>
       <c r="G259" t="n">
-        <v>1.07688188552856</v>
+        <v>1.07688176631927</v>
       </c>
       <c r="H259" t="n">
         <v>4500</v>
@@ -8460,7 +8460,7 @@
         <v>1.25</v>
       </c>
       <c r="G279" t="n">
-        <v>1.11204195022583</v>
+        <v>1.11204183101654</v>
       </c>
       <c r="H279" t="n">
         <v>12000</v>
@@ -8692,7 +8692,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G287" t="n">
-        <v>1.01863038539886</v>
+        <v>1.01863026618958</v>
       </c>
       <c r="H287" t="n">
         <v>19500</v>
@@ -8721,7 +8721,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G288" t="n">
-        <v>1.01863038539886</v>
+        <v>1.01863026618958</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G289" t="n">
-        <v>0.996389508247375</v>
+        <v>0.996389627456665</v>
       </c>
       <c r="H289" t="n">
         <v>12000</v>
@@ -9330,7 +9330,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G309" t="n">
-        <v>0.991941332817078</v>
+        <v>0.991941452026367</v>
       </c>
       <c r="H309" t="n">
         <v>1500</v>
@@ -9417,7 +9417,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G312" t="n">
-        <v>0.996389508247375</v>
+        <v>0.996389627456665</v>
       </c>
       <c r="H312" t="n">
         <v>1500</v>
@@ -9446,7 +9446,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G313" t="n">
-        <v>0.991941332817078</v>
+        <v>0.991941452026367</v>
       </c>
       <c r="H313" t="n">
         <v>3000</v>
@@ -9475,7 +9475,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G314" t="n">
-        <v>0.991941332817078</v>
+        <v>0.991941452026367</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G318" t="n">
-        <v>0.920770585536957</v>
+        <v>0.920770645141602</v>
       </c>
       <c r="H318" t="n">
         <v>12000</v>
@@ -10113,7 +10113,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>1.09424936771393</v>
+        <v>1.09424924850464</v>
       </c>
       <c r="H336" t="n">
         <v>36000</v>
@@ -10142,7 +10142,7 @@
         <v>1.25</v>
       </c>
       <c r="G337" t="n">
-        <v>1.11204195022583</v>
+        <v>1.11204183101654</v>
       </c>
       <c r="H337" t="n">
         <v>22500</v>
@@ -10171,7 +10171,7 @@
         <v>1.25</v>
       </c>
       <c r="G338" t="n">
-        <v>1.11204195022583</v>
+        <v>1.11204183101654</v>
       </c>
       <c r="H338" t="n">
         <v>4500</v>
@@ -10229,7 +10229,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G340" t="n">
-        <v>1.09424936771393</v>
+        <v>1.09424924850464</v>
       </c>
       <c r="H340" t="n">
         <v>13500</v>
@@ -10258,7 +10258,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G341" t="n">
-        <v>1.09424936771393</v>
+        <v>1.09424924850464</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -10490,7 +10490,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G349" t="n">
-        <v>0.996389508247375</v>
+        <v>0.996389627456665</v>
       </c>
       <c r="H349" t="n">
         <v>24000</v>
@@ -10519,7 +10519,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G350" t="n">
-        <v>0.996389508247375</v>
+        <v>0.996389627456665</v>
       </c>
       <c r="H350" t="n">
         <v>3000</v>
@@ -10548,7 +10548,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G351" t="n">
-        <v>0.996389508247375</v>
+        <v>0.996389627456665</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -10577,7 +10577,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G352" t="n">
-        <v>0.996389508247375</v>
+        <v>0.996389627456665</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G363" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H363" t="n">
         <v>22500</v>
@@ -12317,7 +12317,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G412" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H412" t="n">
         <v>1500</v>
@@ -12491,7 +12491,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G418" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H418" t="n">
         <v>3000</v>
@@ -12520,7 +12520,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G419" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G420" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G421" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H421" t="n">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G422" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H422" t="n">
         <v>3000</v>
@@ -12636,7 +12636,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G423" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H423" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G424" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H424" t="n">
         <v>0</v>
@@ -12694,7 +12694,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G425" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G442" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H442" t="n">
         <v>3000</v>
@@ -13216,7 +13216,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G443" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G448" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H448" t="n">
         <v>1500</v>
@@ -13390,7 +13390,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G449" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H449" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G463" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H463" t="n">
         <v>6000</v>
@@ -13825,7 +13825,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G464" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H464" t="n">
         <v>1500</v>
@@ -13854,7 +13854,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G465" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H465" t="n">
         <v>6000</v>
@@ -13883,7 +13883,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G466" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H466" t="n">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G467" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H467" t="n">
         <v>1500</v>
@@ -13941,7 +13941,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G468" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H468" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G496" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H496" t="n">
         <v>6000</v>
@@ -14782,7 +14782,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G497" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H497" t="n">
         <v>0</v>
@@ -14811,7 +14811,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G498" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H498" t="n">
         <v>6000</v>
@@ -14840,7 +14840,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G499" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H499" t="n">
         <v>1500</v>
@@ -14869,7 +14869,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G500" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G518" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H518" t="n">
         <v>3000</v>
@@ -15420,7 +15420,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G519" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H519" t="n">
         <v>0</v>
@@ -15623,7 +15623,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G526" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H526" t="n">
         <v>24000</v>
@@ -15652,7 +15652,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G527" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H527" t="n">
         <v>18000</v>
@@ -16696,7 +16696,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G563" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H563" t="n">
         <v>10500</v>
@@ -16725,7 +16725,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G564" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H564" t="n">
         <v>9000</v>
@@ -16754,7 +16754,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G565" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H565" t="n">
         <v>0</v>
@@ -16783,7 +16783,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G566" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -16812,7 +16812,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G567" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G568" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H568" t="n">
         <v>4500</v>
@@ -16870,7 +16870,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G569" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H569" t="n">
         <v>0</v>
@@ -16899,7 +16899,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G570" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H570" t="n">
         <v>1500</v>
@@ -16928,7 +16928,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G571" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G572" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H572" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G573" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H573" t="n">
         <v>0</v>
@@ -17015,7 +17015,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G574" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H574" t="n">
         <v>0</v>
@@ -17392,7 +17392,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G587" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H587" t="n">
         <v>1500</v>
@@ -17421,7 +17421,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G588" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H588" t="n">
         <v>0</v>
@@ -17450,7 +17450,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G589" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -17479,7 +17479,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G590" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H590" t="n">
         <v>12000</v>
@@ -17508,7 +17508,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G591" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H591" t="n">
         <v>1500</v>
@@ -17537,7 +17537,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G592" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H592" t="n">
         <v>1500</v>
@@ -17566,7 +17566,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G593" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G594" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H594" t="n">
         <v>3000</v>
@@ -17624,7 +17624,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -17740,7 +17740,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G599" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H599" t="n">
         <v>9000</v>
@@ -17769,7 +17769,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G600" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H600" t="n">
         <v>1500</v>

--- a/data/SAC.MI.xlsx
+++ b/data/SAC.MI.xlsx
@@ -514,7 +514,7 @@
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>1.67559897899628</v>
+        <v>1.67559909820557</v>
       </c>
       <c r="H5" t="n">
         <v>51000</v>
@@ -543,7 +543,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G6" t="n">
-        <v>1.75100088119507</v>
+        <v>1.75100100040436</v>
       </c>
       <c r="H6" t="n">
         <v>144000</v>
@@ -572,7 +572,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G7" t="n">
-        <v>1.81802499294281</v>
+        <v>1.81802523136139</v>
       </c>
       <c r="H7" t="n">
         <v>87000</v>
@@ -659,7 +659,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G10" t="n">
-        <v>1.70492219924927</v>
+        <v>1.70492208003998</v>
       </c>
       <c r="H10" t="n">
         <v>13500</v>
@@ -688,7 +688,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>1.70911109447479</v>
+        <v>1.7091109752655</v>
       </c>
       <c r="H11" t="n">
         <v>18000</v>
@@ -717,7 +717,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>1.70911109447479</v>
+        <v>1.7091109752655</v>
       </c>
       <c r="H12" t="n">
         <v>3000</v>
@@ -746,7 +746,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G13" t="n">
-        <v>1.70492219924927</v>
+        <v>1.70492208003998</v>
       </c>
       <c r="H13" t="n">
         <v>18000</v>
@@ -891,7 +891,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G18" t="n">
-        <v>1.61192619800568</v>
+        <v>1.61192631721497</v>
       </c>
       <c r="H18" t="n">
         <v>28500</v>
@@ -920,7 +920,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G19" t="n">
-        <v>1.59181904792786</v>
+        <v>1.59181916713715</v>
       </c>
       <c r="H19" t="n">
         <v>16500</v>
@@ -949,7 +949,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G20" t="n">
-        <v>1.59852147102356</v>
+        <v>1.59852170944214</v>
       </c>
       <c r="H20" t="n">
         <v>16500</v>
@@ -1036,7 +1036,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G23" t="n">
-        <v>1.6018728017807</v>
+        <v>1.60187268257141</v>
       </c>
       <c r="H23" t="n">
         <v>13500</v>
@@ -1065,7 +1065,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G24" t="n">
-        <v>1.6018728017807</v>
+        <v>1.60187268257141</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G26" t="n">
-        <v>1.62030446529388</v>
+        <v>1.62030434608459</v>
       </c>
       <c r="H26" t="n">
         <v>9000</v>
@@ -1152,7 +1152,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G27" t="n">
-        <v>1.62030446529388</v>
+        <v>1.62030434608459</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1181,7 +1181,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G28" t="n">
-        <v>1.59852147102356</v>
+        <v>1.59852170944214</v>
       </c>
       <c r="H28" t="n">
         <v>7500</v>
@@ -1268,7 +1268,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G31" t="n">
-        <v>1.51474153995514</v>
+        <v>1.51474165916443</v>
       </c>
       <c r="H31" t="n">
         <v>10500</v>
@@ -1297,7 +1297,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G32" t="n">
-        <v>1.44604182243347</v>
+        <v>1.44604194164276</v>
       </c>
       <c r="H32" t="n">
         <v>18000</v>
@@ -1384,7 +1384,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G35" t="n">
-        <v>1.41169214248657</v>
+        <v>1.41169226169586</v>
       </c>
       <c r="H35" t="n">
         <v>12000</v>
@@ -1413,7 +1413,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G36" t="n">
-        <v>1.38655829429626</v>
+        <v>1.38655817508698</v>
       </c>
       <c r="H36" t="n">
         <v>3000</v>
@@ -1471,7 +1471,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G38" t="n">
-        <v>1.31534516811371</v>
+        <v>1.315345287323</v>
       </c>
       <c r="H38" t="n">
         <v>12000</v>
@@ -1587,7 +1587,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G42" t="n">
-        <v>1.21480941772461</v>
+        <v>1.21480929851532</v>
       </c>
       <c r="H42" t="n">
         <v>13500</v>
@@ -1616,7 +1616,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G43" t="n">
-        <v>1.19805324077606</v>
+        <v>1.19805335998535</v>
       </c>
       <c r="H43" t="n">
         <v>10500</v>
@@ -1645,7 +1645,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G44" t="n">
-        <v>1.20643150806427</v>
+        <v>1.20643138885498</v>
       </c>
       <c r="H44" t="n">
         <v>7500</v>
@@ -1674,7 +1674,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G45" t="n">
-        <v>1.21062028408051</v>
+        <v>1.21062040328979</v>
       </c>
       <c r="H45" t="n">
         <v>100500</v>
@@ -1790,7 +1790,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G49" t="n">
-        <v>1.30277824401855</v>
+        <v>1.30277812480927</v>
       </c>
       <c r="H49" t="n">
         <v>48000</v>
@@ -1819,7 +1819,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G50" t="n">
-        <v>1.30277824401855</v>
+        <v>1.30277812480927</v>
       </c>
       <c r="H50" t="n">
         <v>54000</v>
@@ -1848,7 +1848,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>1.27345538139343</v>
+        <v>1.27345526218414</v>
       </c>
       <c r="H51" t="n">
         <v>7500</v>
@@ -2051,7 +2051,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>1.23994326591492</v>
+        <v>1.23994338512421</v>
       </c>
       <c r="H58" t="n">
         <v>7500</v>
@@ -2080,7 +2080,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G59" t="n">
-        <v>1.28602230548859</v>
+        <v>1.2860221862793</v>
       </c>
       <c r="H59" t="n">
         <v>4500</v>
@@ -2109,7 +2109,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G60" t="n">
-        <v>1.24832141399384</v>
+        <v>1.24832129478455</v>
       </c>
       <c r="H60" t="n">
         <v>58500</v>
@@ -2167,7 +2167,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G62" t="n">
-        <v>1.23994326591492</v>
+        <v>1.23994338512421</v>
       </c>
       <c r="H62" t="n">
         <v>10500</v>
@@ -2196,7 +2196,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G63" t="n">
-        <v>1.26507723331451</v>
+        <v>1.2650773525238</v>
       </c>
       <c r="H63" t="n">
         <v>15000</v>
@@ -2312,7 +2312,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G67" t="n">
-        <v>1.23994326591492</v>
+        <v>1.23994338512421</v>
       </c>
       <c r="H67" t="n">
         <v>16500</v>
@@ -2341,7 +2341,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G68" t="n">
-        <v>1.24832141399384</v>
+        <v>1.24832129478455</v>
       </c>
       <c r="H68" t="n">
         <v>1500</v>
@@ -2486,7 +2486,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G73" t="n">
-        <v>1.30277824401855</v>
+        <v>1.30277812480927</v>
       </c>
       <c r="H73" t="n">
         <v>1500</v>
@@ -2718,7 +2718,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G81" t="n">
-        <v>1.29858934879303</v>
+        <v>1.29858922958374</v>
       </c>
       <c r="H81" t="n">
         <v>33000</v>
@@ -2776,7 +2776,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G83" t="n">
-        <v>1.3404792547226</v>
+        <v>1.34047937393188</v>
       </c>
       <c r="H83" t="n">
         <v>19500</v>
@@ -2805,7 +2805,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G84" t="n">
-        <v>1.35723519325256</v>
+        <v>1.35723543167114</v>
       </c>
       <c r="H84" t="n">
         <v>39000</v>
@@ -2834,7 +2834,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G85" t="n">
-        <v>1.32791221141815</v>
+        <v>1.32791233062744</v>
       </c>
       <c r="H85" t="n">
         <v>19500</v>
@@ -2863,7 +2863,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G86" t="n">
-        <v>1.3195344209671</v>
+        <v>1.31953430175781</v>
       </c>
       <c r="H86" t="n">
         <v>9000</v>
@@ -2921,7 +2921,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G88" t="n">
-        <v>1.28602230548859</v>
+        <v>1.2860221862793</v>
       </c>
       <c r="H88" t="n">
         <v>3000</v>
@@ -3095,7 +3095,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G94" t="n">
-        <v>1.24832141399384</v>
+        <v>1.24832129478455</v>
       </c>
       <c r="H94" t="n">
         <v>10500</v>
@@ -3211,7 +3211,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G98" t="n">
-        <v>1.24832141399384</v>
+        <v>1.24832129478455</v>
       </c>
       <c r="H98" t="n">
         <v>4500</v>
@@ -3327,7 +3327,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>1.27502799034119</v>
+        <v>1.27502810955048</v>
       </c>
       <c r="H102" t="n">
         <v>9000</v>
@@ -3356,7 +3356,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G103" t="n">
-        <v>1.27502799034119</v>
+        <v>1.27502810955048</v>
       </c>
       <c r="H103" t="n">
         <v>9000</v>
@@ -3385,7 +3385,7 @@
         <v>1.375</v>
       </c>
       <c r="G104" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H104" t="n">
         <v>9000</v>
@@ -3414,7 +3414,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G105" t="n">
-        <v>1.15441727638245</v>
+        <v>1.15441715717316</v>
       </c>
       <c r="H105" t="n">
         <v>3000</v>
@@ -3501,7 +3501,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G108" t="n">
-        <v>1.1285719871521</v>
+        <v>1.12857210636139</v>
       </c>
       <c r="H108" t="n">
         <v>1500</v>
@@ -3530,7 +3530,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G109" t="n">
-        <v>1.1285719871521</v>
+        <v>1.12857210636139</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G110" t="n">
-        <v>1.1285719871521</v>
+        <v>1.12857210636139</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G111" t="n">
-        <v>1.1285719871521</v>
+        <v>1.12857210636139</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G112" t="n">
-        <v>1.1285719871521</v>
+        <v>1.12857210636139</v>
       </c>
       <c r="H112" t="n">
         <v>3000</v>
@@ -3646,7 +3646,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G113" t="n">
-        <v>1.2104150056839</v>
+        <v>1.21041512489319</v>
       </c>
       <c r="H113" t="n">
         <v>9000</v>
@@ -3791,7 +3791,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G118" t="n">
-        <v>1.17164731025696</v>
+        <v>1.17164742946625</v>
       </c>
       <c r="H118" t="n">
         <v>10500</v>
@@ -3820,7 +3820,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G119" t="n">
-        <v>1.18887734413147</v>
+        <v>1.18887746334076</v>
       </c>
       <c r="H119" t="n">
         <v>1500</v>
@@ -3849,7 +3849,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G120" t="n">
-        <v>1.18887734413147</v>
+        <v>1.18887746334076</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G121" t="n">
-        <v>1.18887734413147</v>
+        <v>1.18887746334076</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G122" t="n">
-        <v>1.2104150056839</v>
+        <v>1.21041512489319</v>
       </c>
       <c r="H122" t="n">
         <v>1500</v>
@@ -3936,7 +3936,7 @@
         <v>1.375</v>
       </c>
       <c r="G123" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H123" t="n">
         <v>3000</v>
@@ -3965,7 +3965,7 @@
         <v>1.375</v>
       </c>
       <c r="G124" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G125" t="n">
-        <v>1.18026232719421</v>
+        <v>1.1802624464035</v>
       </c>
       <c r="H125" t="n">
         <v>3000</v>
@@ -4023,7 +4023,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G126" t="n">
-        <v>1.18887734413147</v>
+        <v>1.18887746334076</v>
       </c>
       <c r="H126" t="n">
         <v>3000</v>
@@ -4052,7 +4052,7 @@
         <v>1.375</v>
       </c>
       <c r="G127" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H127" t="n">
         <v>1500</v>
@@ -4081,7 +4081,7 @@
         <v>1.375</v>
       </c>
       <c r="G128" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>1.375</v>
       </c>
       <c r="G129" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H129" t="n">
         <v>3000</v>
@@ -4139,7 +4139,7 @@
         <v>1.375</v>
       </c>
       <c r="G130" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>1.375</v>
       </c>
       <c r="G131" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -4197,7 +4197,7 @@
         <v>1.375</v>
       </c>
       <c r="G132" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H132" t="n">
         <v>1500</v>
@@ -4226,7 +4226,7 @@
         <v>1.375</v>
       </c>
       <c r="G133" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>1.375</v>
       </c>
       <c r="G134" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>1.375</v>
       </c>
       <c r="G135" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>1.375</v>
       </c>
       <c r="G136" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>1.375</v>
       </c>
       <c r="G137" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H137" t="n">
         <v>1500</v>
@@ -4371,7 +4371,7 @@
         <v>1.375</v>
       </c>
       <c r="G138" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G139" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H139" t="n">
         <v>9000</v>
@@ -4429,7 +4429,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G140" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H140" t="n">
         <v>1500</v>
@@ -4458,7 +4458,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G141" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G142" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G143" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G144" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G145" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G146" t="n">
-        <v>1.13287961483002</v>
+        <v>1.13287973403931</v>
       </c>
       <c r="H146" t="n">
         <v>6000</v>
@@ -4777,7 +4777,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G152" t="n">
-        <v>1.17595481872559</v>
+        <v>1.17595493793488</v>
       </c>
       <c r="H152" t="n">
         <v>18000</v>
@@ -4806,7 +4806,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G153" t="n">
-        <v>1.17164731025696</v>
+        <v>1.17164742946625</v>
       </c>
       <c r="H153" t="n">
         <v>7500</v>
@@ -5038,7 +5038,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G161" t="n">
-        <v>1.18026232719421</v>
+        <v>1.1802624464035</v>
       </c>
       <c r="H161" t="n">
         <v>4500</v>
@@ -5067,7 +5067,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G162" t="n">
-        <v>1.15441727638245</v>
+        <v>1.15441715717316</v>
       </c>
       <c r="H162" t="n">
         <v>3000</v>
@@ -5096,7 +5096,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G163" t="n">
-        <v>1.12426447868347</v>
+        <v>1.12426435947418</v>
       </c>
       <c r="H163" t="n">
         <v>4500</v>
@@ -5125,7 +5125,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G164" t="n">
-        <v>1.14580225944519</v>
+        <v>1.1458021402359</v>
       </c>
       <c r="H164" t="n">
         <v>3000</v>
@@ -5154,7 +5154,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G165" t="n">
-        <v>1.14580225944519</v>
+        <v>1.1458021402359</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G166" t="n">
-        <v>1.14580225944519</v>
+        <v>1.1458021402359</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G167" t="n">
-        <v>1.14580225944519</v>
+        <v>1.1458021402359</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -5241,7 +5241,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G168" t="n">
-        <v>1.12426447868347</v>
+        <v>1.12426435947418</v>
       </c>
       <c r="H168" t="n">
         <v>1500</v>
@@ -5270,7 +5270,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G169" t="n">
-        <v>1.12426447868347</v>
+        <v>1.12426435947418</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G179" t="n">
-        <v>1.08549690246582</v>
+        <v>1.08549678325653</v>
       </c>
       <c r="H179" t="n">
         <v>7500</v>
@@ -5792,7 +5792,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G187" t="n">
-        <v>1.02519142627716</v>
+        <v>1.02519154548645</v>
       </c>
       <c r="H187" t="n">
         <v>3000</v>
@@ -5821,7 +5821,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G188" t="n">
-        <v>0.999346315860748</v>
+        <v>0.999346256256104</v>
       </c>
       <c r="H188" t="n">
         <v>4500</v>
@@ -5850,7 +5850,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G189" t="n">
-        <v>0.930425822734833</v>
+        <v>0.930425941944122</v>
       </c>
       <c r="H189" t="n">
         <v>45000</v>
@@ -5879,7 +5879,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G190" t="n">
-        <v>0.92611837387085</v>
+        <v>0.926118314266205</v>
       </c>
       <c r="H190" t="n">
         <v>63000</v>
@@ -5908,7 +5908,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G191" t="n">
-        <v>0.92611837387085</v>
+        <v>0.926118314266205</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G192" t="n">
-        <v>0.92611837387085</v>
+        <v>0.926118314266205</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G193" t="n">
-        <v>0.92611837387085</v>
+        <v>0.926118314266205</v>
       </c>
       <c r="H193" t="n">
         <v>1500</v>
@@ -6082,7 +6082,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G197" t="n">
-        <v>0.887350618839264</v>
+        <v>0.887350499629974</v>
       </c>
       <c r="H197" t="n">
         <v>3000</v>
@@ -6111,7 +6111,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G198" t="n">
-        <v>0.887350618839264</v>
+        <v>0.887350499629974</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>0.878735542297363</v>
+        <v>0.878735482692719</v>
       </c>
       <c r="H199" t="n">
         <v>3000</v>
@@ -6169,7 +6169,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>0.895965576171875</v>
+        <v>0.89596563577652</v>
       </c>
       <c r="H200" t="n">
         <v>6000</v>
@@ -6198,7 +6198,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G201" t="n">
-        <v>0.878735542297363</v>
+        <v>0.878735482692719</v>
       </c>
       <c r="H201" t="n">
         <v>3000</v>
@@ -6227,7 +6227,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G202" t="n">
-        <v>0.887350618839264</v>
+        <v>0.887350499629974</v>
       </c>
       <c r="H202" t="n">
         <v>7500</v>
@@ -6256,7 +6256,7 @@
         <v>1</v>
       </c>
       <c r="G203" t="n">
-        <v>0.861505448818207</v>
+        <v>0.861505389213562</v>
       </c>
       <c r="H203" t="n">
         <v>1500</v>
@@ -6285,7 +6285,7 @@
         <v>1</v>
       </c>
       <c r="G204" t="n">
-        <v>0.861505448818207</v>
+        <v>0.861505389213562</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G205" t="n">
-        <v>0.849444389343262</v>
+        <v>0.849444329738617</v>
       </c>
       <c r="H205" t="n">
         <v>9000</v>
@@ -6343,7 +6343,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G206" t="n">
-        <v>0.865813016891479</v>
+        <v>0.86581289768219</v>
       </c>
       <c r="H206" t="n">
         <v>3000</v>
@@ -6459,7 +6459,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G210" t="n">
-        <v>0.908888220787048</v>
+        <v>0.908888101577759</v>
       </c>
       <c r="H210" t="n">
         <v>1500</v>
@@ -6488,7 +6488,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G211" t="n">
-        <v>0.908888220787048</v>
+        <v>0.908888101577759</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G212" t="n">
-        <v>0.908888220787048</v>
+        <v>0.908888101577759</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G213" t="n">
-        <v>0.908888220787048</v>
+        <v>0.908888101577759</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G214" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H214" t="n">
         <v>3000</v>
@@ -6604,7 +6604,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G215" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G216" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6662,7 +6662,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G217" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G218" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G219" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G220" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G221" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G222" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G223" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G224" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G225" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G226" t="n">
-        <v>0.874428033828735</v>
+        <v>0.874427974224091</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>0.878735542297363</v>
+        <v>0.878735482692719</v>
       </c>
       <c r="H227" t="n">
         <v>9000</v>
@@ -6981,7 +6981,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G228" t="n">
-        <v>0.878735542297363</v>
+        <v>0.878735482692719</v>
       </c>
       <c r="H228" t="n">
         <v>15000</v>
@@ -7010,7 +7010,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G229" t="n">
-        <v>0.865813016891479</v>
+        <v>0.86581289768219</v>
       </c>
       <c r="H229" t="n">
         <v>19500</v>
@@ -7039,7 +7039,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G230" t="n">
-        <v>0.865813016891479</v>
+        <v>0.86581289768219</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>1</v>
       </c>
       <c r="G231" t="n">
-        <v>0.861505448818207</v>
+        <v>0.861505389213562</v>
       </c>
       <c r="H231" t="n">
         <v>6000</v>
@@ -7126,7 +7126,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G233" t="n">
-        <v>0.747786700725555</v>
+        <v>0.747786641120911</v>
       </c>
       <c r="H233" t="n">
         <v>31500</v>
@@ -7155,7 +7155,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G234" t="n">
-        <v>0.680589318275452</v>
+        <v>0.680589377880096</v>
       </c>
       <c r="H234" t="n">
         <v>120000</v>
@@ -7271,7 +7271,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G238" t="n">
-        <v>0.706434369087219</v>
+        <v>0.706434428691864</v>
       </c>
       <c r="H238" t="n">
         <v>63000</v>
@@ -7329,7 +7329,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G240" t="n">
-        <v>0.732279598712921</v>
+        <v>0.732279539108276</v>
       </c>
       <c r="H240" t="n">
         <v>25500</v>
@@ -7387,7 +7387,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G242" t="n">
-        <v>0.792585015296936</v>
+        <v>0.792584896087646</v>
       </c>
       <c r="H242" t="n">
         <v>75000</v>
@@ -7416,7 +7416,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G243" t="n">
-        <v>0.84772127866745</v>
+        <v>0.847721338272095</v>
       </c>
       <c r="H243" t="n">
         <v>48000</v>
@@ -7445,7 +7445,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G244" t="n">
-        <v>0.797754049301147</v>
+        <v>0.797753989696503</v>
       </c>
       <c r="H244" t="n">
         <v>63000</v>
@@ -7532,7 +7532,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G247" t="n">
-        <v>0.851167321205139</v>
+        <v>0.851167261600494</v>
       </c>
       <c r="H247" t="n">
         <v>4500</v>
@@ -7561,7 +7561,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G248" t="n">
-        <v>0.895965576171875</v>
+        <v>0.89596563577652</v>
       </c>
       <c r="H248" t="n">
         <v>25500</v>
@@ -7590,7 +7590,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G249" t="n">
-        <v>0.990731298923492</v>
+        <v>0.990731239318848</v>
       </c>
       <c r="H249" t="n">
         <v>90000</v>
@@ -7619,7 +7619,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G250" t="n">
-        <v>1.10703444480896</v>
+        <v>1.10703432559967</v>
       </c>
       <c r="H250" t="n">
         <v>192000</v>
@@ -7677,7 +7677,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G252" t="n">
-        <v>1.07257425785065</v>
+        <v>1.07257413864136</v>
       </c>
       <c r="H252" t="n">
         <v>73500</v>
@@ -7735,7 +7735,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G254" t="n">
-        <v>1.03380656242371</v>
+        <v>1.03380644321442</v>
       </c>
       <c r="H254" t="n">
         <v>37500</v>
@@ -7822,7 +7822,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G257" t="n">
-        <v>1.07257425785065</v>
+        <v>1.07257413864136</v>
       </c>
       <c r="H257" t="n">
         <v>45000</v>
@@ -7851,7 +7851,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>1.05965161323547</v>
+        <v>1.05965173244476</v>
       </c>
       <c r="H258" t="n">
         <v>18000</v>
@@ -7938,7 +7938,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G261" t="n">
-        <v>1.10703444480896</v>
+        <v>1.10703432559967</v>
       </c>
       <c r="H261" t="n">
         <v>48000</v>
@@ -8315,7 +8315,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G274" t="n">
-        <v>1.17164731025696</v>
+        <v>1.17164742946625</v>
       </c>
       <c r="H274" t="n">
         <v>54000</v>
@@ -8344,7 +8344,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>1.14762723445892</v>
+        <v>1.14762711524963</v>
       </c>
       <c r="H275" t="n">
         <v>22500</v>
@@ -8460,7 +8460,7 @@
         <v>1.25</v>
       </c>
       <c r="G279" t="n">
-        <v>1.11204183101654</v>
+        <v>1.11204195022583</v>
       </c>
       <c r="H279" t="n">
         <v>12000</v>
@@ -8605,7 +8605,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G284" t="n">
-        <v>1.08535289764404</v>
+        <v>1.08535277843475</v>
       </c>
       <c r="H284" t="n">
         <v>18000</v>
@@ -8634,7 +8634,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G285" t="n">
-        <v>1.05421566963196</v>
+        <v>1.05421555042267</v>
       </c>
       <c r="H285" t="n">
         <v>16500</v>
@@ -8750,7 +8750,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G289" t="n">
-        <v>0.996389627456665</v>
+        <v>0.996389508247375</v>
       </c>
       <c r="H289" t="n">
         <v>12000</v>
@@ -8779,7 +8779,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G290" t="n">
-        <v>1.02307856082916</v>
+        <v>1.02307844161987</v>
       </c>
       <c r="H290" t="n">
         <v>3000</v>
@@ -8808,7 +8808,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G291" t="n">
-        <v>1.02307856082916</v>
+        <v>1.02307844161987</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G294" t="n">
-        <v>0.98749315738678</v>
+        <v>0.987493216991425</v>
       </c>
       <c r="H294" t="n">
         <v>4500</v>
@@ -9069,7 +9069,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G300" t="n">
-        <v>1.02307856082916</v>
+        <v>1.02307844161987</v>
       </c>
       <c r="H300" t="n">
         <v>10500</v>
@@ -9185,7 +9185,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G304" t="n">
-        <v>1.02752673625946</v>
+        <v>1.02752661705017</v>
       </c>
       <c r="H304" t="n">
         <v>25500</v>
@@ -9301,7 +9301,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G308" t="n">
-        <v>0.983044981956482</v>
+        <v>0.983045041561127</v>
       </c>
       <c r="H308" t="n">
         <v>12000</v>
@@ -9330,7 +9330,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G309" t="n">
-        <v>0.991941452026367</v>
+        <v>0.991941332817078</v>
       </c>
       <c r="H309" t="n">
         <v>1500</v>
@@ -9417,7 +9417,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G312" t="n">
-        <v>0.996389627456665</v>
+        <v>0.996389508247375</v>
       </c>
       <c r="H312" t="n">
         <v>1500</v>
@@ -9446,7 +9446,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G313" t="n">
-        <v>0.991941452026367</v>
+        <v>0.991941332817078</v>
       </c>
       <c r="H313" t="n">
         <v>3000</v>
@@ -9475,7 +9475,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G314" t="n">
-        <v>0.991941452026367</v>
+        <v>0.991941332817078</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G316" t="n">
-        <v>0.98749315738678</v>
+        <v>0.987493216991425</v>
       </c>
       <c r="H316" t="n">
         <v>1500</v>
@@ -9562,7 +9562,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G317" t="n">
-        <v>0.983044981956482</v>
+        <v>0.983045041561127</v>
       </c>
       <c r="H317" t="n">
         <v>3000</v>
@@ -9823,7 +9823,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G326" t="n">
-        <v>1.06311213970184</v>
+        <v>1.06311202049255</v>
       </c>
       <c r="H326" t="n">
         <v>1500</v>
@@ -9852,7 +9852,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G327" t="n">
-        <v>1.05866396427155</v>
+        <v>1.05866384506226</v>
       </c>
       <c r="H327" t="n">
         <v>4500</v>
@@ -9881,7 +9881,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>1.05866396427155</v>
+        <v>1.05866384506226</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G333" t="n">
-        <v>1.08535289764404</v>
+        <v>1.08535277843475</v>
       </c>
       <c r="H333" t="n">
         <v>6000</v>
@@ -10055,7 +10055,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G334" t="n">
-        <v>1.12093830108643</v>
+        <v>1.12093818187714</v>
       </c>
       <c r="H334" t="n">
         <v>63000</v>
@@ -10142,7 +10142,7 @@
         <v>1.25</v>
       </c>
       <c r="G337" t="n">
-        <v>1.11204183101654</v>
+        <v>1.11204195022583</v>
       </c>
       <c r="H337" t="n">
         <v>22500</v>
@@ -10171,7 +10171,7 @@
         <v>1.25</v>
       </c>
       <c r="G338" t="n">
-        <v>1.11204183101654</v>
+        <v>1.11204195022583</v>
       </c>
       <c r="H338" t="n">
         <v>4500</v>
@@ -10200,7 +10200,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G339" t="n">
-        <v>1.08535289764404</v>
+        <v>1.08535277843475</v>
       </c>
       <c r="H339" t="n">
         <v>4500</v>
@@ -10403,7 +10403,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G346" t="n">
-        <v>1.03197491168976</v>
+        <v>1.03197479248047</v>
       </c>
       <c r="H346" t="n">
         <v>34500</v>
@@ -10432,7 +10432,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G347" t="n">
-        <v>1.02307856082916</v>
+        <v>1.02307844161987</v>
       </c>
       <c r="H347" t="n">
         <v>19500</v>
@@ -10461,7 +10461,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G348" t="n">
-        <v>1.03197491168976</v>
+        <v>1.03197479248047</v>
       </c>
       <c r="H348" t="n">
         <v>1500</v>
@@ -10490,7 +10490,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G349" t="n">
-        <v>0.996389627456665</v>
+        <v>0.996389508247375</v>
       </c>
       <c r="H349" t="n">
         <v>24000</v>
@@ -10519,7 +10519,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G350" t="n">
-        <v>0.996389627456665</v>
+        <v>0.996389508247375</v>
       </c>
       <c r="H350" t="n">
         <v>3000</v>
@@ -10548,7 +10548,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G351" t="n">
-        <v>0.996389627456665</v>
+        <v>0.996389508247375</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -10577,7 +10577,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G352" t="n">
-        <v>0.996389627456665</v>
+        <v>0.996389508247375</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10606,7 +10606,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G353" t="n">
-        <v>1.02307856082916</v>
+        <v>1.02307844161987</v>
       </c>
       <c r="H353" t="n">
         <v>4500</v>
@@ -10635,7 +10635,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G354" t="n">
-        <v>1.02307856082916</v>
+        <v>1.02307844161987</v>
       </c>
       <c r="H354" t="n">
         <v>1500</v>
@@ -10664,7 +10664,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>1.05866396427155</v>
+        <v>1.05866384506226</v>
       </c>
       <c r="H355" t="n">
         <v>7500</v>
@@ -10693,7 +10693,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G356" t="n">
-        <v>1.05866396427155</v>
+        <v>1.05866384506226</v>
       </c>
       <c r="H356" t="n">
         <v>9000</v>
@@ -10896,7 +10896,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G363" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H363" t="n">
         <v>22500</v>
@@ -12317,7 +12317,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G412" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H412" t="n">
         <v>1500</v>
@@ -12491,7 +12491,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G418" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H418" t="n">
         <v>3000</v>
@@ -12520,7 +12520,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G419" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G420" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G421" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H421" t="n">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G422" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H422" t="n">
         <v>3000</v>
@@ -12636,7 +12636,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G423" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H423" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G424" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H424" t="n">
         <v>0</v>
@@ -12694,7 +12694,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G425" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G442" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H442" t="n">
         <v>3000</v>
@@ -13216,7 +13216,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G443" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G448" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H448" t="n">
         <v>1500</v>
@@ -13390,7 +13390,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G449" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H449" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G463" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H463" t="n">
         <v>6000</v>
@@ -13825,7 +13825,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G464" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H464" t="n">
         <v>1500</v>
@@ -13854,7 +13854,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G465" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H465" t="n">
         <v>6000</v>
@@ -13883,7 +13883,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G466" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H466" t="n">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G467" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H467" t="n">
         <v>1500</v>
@@ -13941,7 +13941,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G468" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H468" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G496" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H496" t="n">
         <v>6000</v>
@@ -14782,7 +14782,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G497" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H497" t="n">
         <v>0</v>
@@ -14811,7 +14811,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G498" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H498" t="n">
         <v>6000</v>
@@ -14840,7 +14840,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G499" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H499" t="n">
         <v>1500</v>
@@ -14869,7 +14869,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G500" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G518" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H518" t="n">
         <v>3000</v>
@@ -15420,7 +15420,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G519" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H519" t="n">
         <v>0</v>
@@ -15623,7 +15623,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G526" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H526" t="n">
         <v>24000</v>
@@ -15652,7 +15652,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G527" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H527" t="n">
         <v>18000</v>
@@ -16696,7 +16696,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G563" t="n">
-        <v>0.977511882781982</v>
+        <v>0.977511942386627</v>
       </c>
       <c r="H563" t="n">
         <v>10500</v>
@@ -16725,7 +16725,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G564" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H564" t="n">
         <v>9000</v>
@@ -16754,7 +16754,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G565" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H565" t="n">
         <v>0</v>
@@ -16783,7 +16783,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G566" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -16812,7 +16812,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G567" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G568" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H568" t="n">
         <v>4500</v>
@@ -16870,7 +16870,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G569" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H569" t="n">
         <v>0</v>
@@ -16899,7 +16899,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G570" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H570" t="n">
         <v>1500</v>
@@ -16928,7 +16928,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G571" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G572" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H572" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G573" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H573" t="n">
         <v>0</v>
@@ -17015,7 +17015,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G574" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H574" t="n">
         <v>0</v>
@@ -17392,7 +17392,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G587" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H587" t="n">
         <v>1500</v>
@@ -17421,7 +17421,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G588" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H588" t="n">
         <v>0</v>
@@ -17450,7 +17450,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G589" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -17479,7 +17479,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G590" t="n">
-        <v>0.977511882781982</v>
+        <v>0.977511942386627</v>
       </c>
       <c r="H590" t="n">
         <v>12000</v>
@@ -17508,7 +17508,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G591" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H591" t="n">
         <v>1500</v>
@@ -17537,7 +17537,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G592" t="n">
-        <v>0.977511882781982</v>
+        <v>0.977511942386627</v>
       </c>
       <c r="H592" t="n">
         <v>1500</v>
@@ -17566,7 +17566,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G593" t="n">
-        <v>0.977511882781982</v>
+        <v>0.977511942386627</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G594" t="n">
-        <v>0.977511882781982</v>
+        <v>0.977511942386627</v>
       </c>
       <c r="H594" t="n">
         <v>3000</v>
@@ -17624,7 +17624,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>0.977511882781982</v>
+        <v>0.977511942386627</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -17740,7 +17740,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G599" t="n">
-        <v>0.977511882781982</v>
+        <v>0.977511942386627</v>
       </c>
       <c r="H599" t="n">
         <v>9000</v>
@@ -17769,7 +17769,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G600" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H600" t="n">
         <v>1500</v>
@@ -28679,6 +28679,64 @@
         <v>3000</v>
       </c>
       <c r="I976" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="s">
+        <v>9</v>
+      </c>
+      <c r="B977" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C977" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="D977" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="E977" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="F977" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="G977" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="H977" t="n">
+        <v>0</v>
+      </c>
+      <c r="I977" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="s">
+        <v>9</v>
+      </c>
+      <c r="B978" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C978" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="D978" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="E978" t="n">
+        <v>1.11000001430511</v>
+      </c>
+      <c r="F978" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="G978" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="H978" t="n">
+        <v>21000</v>
+      </c>
+      <c r="I978" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SAC.MI.xlsx
+++ b/data/SAC.MI.xlsx
@@ -485,7 +485,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G4" t="n">
-        <v>1.52479517459869</v>
+        <v>1.52479529380798</v>
       </c>
       <c r="H4" t="n">
         <v>36000</v>
@@ -572,7 +572,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G7" t="n">
-        <v>1.81802523136139</v>
+        <v>1.8180251121521</v>
       </c>
       <c r="H7" t="n">
         <v>87000</v>
@@ -688,7 +688,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7091109752655</v>
+        <v>1.70911085605621</v>
       </c>
       <c r="H11" t="n">
         <v>18000</v>
@@ -717,7 +717,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7091109752655</v>
+        <v>1.70911085605621</v>
       </c>
       <c r="H12" t="n">
         <v>3000</v>
@@ -775,7 +775,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G14" t="n">
-        <v>1.73424506187439</v>
+        <v>1.7342449426651</v>
       </c>
       <c r="H14" t="n">
         <v>1500</v>
@@ -833,7 +833,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G16" t="n">
-        <v>1.73424506187439</v>
+        <v>1.7342449426651</v>
       </c>
       <c r="H16" t="n">
         <v>7500</v>
@@ -891,7 +891,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G18" t="n">
-        <v>1.61192631721497</v>
+        <v>1.61192643642426</v>
       </c>
       <c r="H18" t="n">
         <v>28500</v>
@@ -949,7 +949,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G20" t="n">
-        <v>1.59852170944214</v>
+        <v>1.59852159023285</v>
       </c>
       <c r="H20" t="n">
         <v>16500</v>
@@ -1007,7 +1007,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G22" t="n">
-        <v>1.60522389411926</v>
+        <v>1.60522401332855</v>
       </c>
       <c r="H22" t="n">
         <v>6000</v>
@@ -1181,7 +1181,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G28" t="n">
-        <v>1.59852170944214</v>
+        <v>1.59852159023285</v>
       </c>
       <c r="H28" t="n">
         <v>7500</v>
@@ -1210,7 +1210,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G29" t="n">
-        <v>1.54992914199829</v>
+        <v>1.54992926120758</v>
       </c>
       <c r="H29" t="n">
         <v>25500</v>
@@ -1268,7 +1268,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G31" t="n">
-        <v>1.51474165916443</v>
+        <v>1.51474153995514</v>
       </c>
       <c r="H31" t="n">
         <v>10500</v>
@@ -1413,7 +1413,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G36" t="n">
-        <v>1.38655817508698</v>
+        <v>1.38655805587769</v>
       </c>
       <c r="H36" t="n">
         <v>3000</v>
@@ -1471,7 +1471,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G38" t="n">
-        <v>1.315345287323</v>
+        <v>1.31534540653229</v>
       </c>
       <c r="H38" t="n">
         <v>12000</v>
@@ -1616,7 +1616,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G43" t="n">
-        <v>1.19805335998535</v>
+        <v>1.19805312156677</v>
       </c>
       <c r="H43" t="n">
         <v>10500</v>
@@ -1674,7 +1674,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G45" t="n">
-        <v>1.21062040328979</v>
+        <v>1.21062028408051</v>
       </c>
       <c r="H45" t="n">
         <v>100500</v>
@@ -1703,7 +1703,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G46" t="n">
-        <v>1.22737634181976</v>
+        <v>1.22737646102905</v>
       </c>
       <c r="H46" t="n">
         <v>30000</v>
@@ -1761,7 +1761,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G48" t="n">
-        <v>1.26926636695862</v>
+        <v>1.26926624774933</v>
       </c>
       <c r="H48" t="n">
         <v>27000</v>
@@ -1790,7 +1790,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G49" t="n">
-        <v>1.30277812480927</v>
+        <v>1.30277824401855</v>
       </c>
       <c r="H49" t="n">
         <v>48000</v>
@@ -1819,7 +1819,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G50" t="n">
-        <v>1.30277812480927</v>
+        <v>1.30277824401855</v>
       </c>
       <c r="H50" t="n">
         <v>54000</v>
@@ -1877,7 +1877,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G52" t="n">
-        <v>1.28183329105377</v>
+        <v>1.28183341026306</v>
       </c>
       <c r="H52" t="n">
         <v>28500</v>
@@ -2080,7 +2080,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G59" t="n">
-        <v>1.2860221862793</v>
+        <v>1.28602230548859</v>
       </c>
       <c r="H59" t="n">
         <v>4500</v>
@@ -2109,7 +2109,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G60" t="n">
-        <v>1.24832129478455</v>
+        <v>1.24832141399384</v>
       </c>
       <c r="H60" t="n">
         <v>58500</v>
@@ -2138,7 +2138,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G61" t="n">
-        <v>1.24413228034973</v>
+        <v>1.24413239955902</v>
       </c>
       <c r="H61" t="n">
         <v>21000</v>
@@ -2196,7 +2196,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G63" t="n">
-        <v>1.2650773525238</v>
+        <v>1.26507747173309</v>
       </c>
       <c r="H63" t="n">
         <v>15000</v>
@@ -2225,7 +2225,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G64" t="n">
-        <v>1.27764427661896</v>
+        <v>1.27764439582825</v>
       </c>
       <c r="H64" t="n">
         <v>4500</v>
@@ -2254,7 +2254,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G65" t="n">
-        <v>1.26926636695862</v>
+        <v>1.26926624774933</v>
       </c>
       <c r="H65" t="n">
         <v>1500</v>
@@ -2283,7 +2283,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G66" t="n">
-        <v>1.26088833808899</v>
+        <v>1.26088845729828</v>
       </c>
       <c r="H66" t="n">
         <v>21000</v>
@@ -2341,7 +2341,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G68" t="n">
-        <v>1.24832129478455</v>
+        <v>1.24832141399384</v>
       </c>
       <c r="H68" t="n">
         <v>1500</v>
@@ -2428,7 +2428,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G71" t="n">
-        <v>1.28183329105377</v>
+        <v>1.28183341026306</v>
       </c>
       <c r="H71" t="n">
         <v>46500</v>
@@ -2486,7 +2486,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G73" t="n">
-        <v>1.30277812480927</v>
+        <v>1.30277824401855</v>
       </c>
       <c r="H73" t="n">
         <v>1500</v>
@@ -2660,7 +2660,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G79" t="n">
-        <v>1.27764427661896</v>
+        <v>1.27764439582825</v>
       </c>
       <c r="H79" t="n">
         <v>12000</v>
@@ -2689,7 +2689,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G80" t="n">
-        <v>1.27764427661896</v>
+        <v>1.27764439582825</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G83" t="n">
-        <v>1.34047937393188</v>
+        <v>1.3404792547226</v>
       </c>
       <c r="H83" t="n">
         <v>19500</v>
@@ -2805,7 +2805,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G84" t="n">
-        <v>1.35723543167114</v>
+        <v>1.35723519325256</v>
       </c>
       <c r="H84" t="n">
         <v>39000</v>
@@ -2834,7 +2834,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G85" t="n">
-        <v>1.32791233062744</v>
+        <v>1.32791221141815</v>
       </c>
       <c r="H85" t="n">
         <v>19500</v>
@@ -2863,7 +2863,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G86" t="n">
-        <v>1.31953430175781</v>
+        <v>1.3195344209671</v>
       </c>
       <c r="H86" t="n">
         <v>9000</v>
@@ -2921,7 +2921,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G88" t="n">
-        <v>1.2860221862793</v>
+        <v>1.28602230548859</v>
       </c>
       <c r="H88" t="n">
         <v>3000</v>
@@ -2950,7 +2950,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G89" t="n">
-        <v>1.26088833808899</v>
+        <v>1.26088845729828</v>
       </c>
       <c r="H89" t="n">
         <v>6000</v>
@@ -2979,7 +2979,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G90" t="n">
-        <v>1.26088833808899</v>
+        <v>1.26088845729828</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G91" t="n">
-        <v>1.26088833808899</v>
+        <v>1.26088845729828</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G92" t="n">
-        <v>1.26088833808899</v>
+        <v>1.26088845729828</v>
       </c>
       <c r="H92" t="n">
         <v>1500</v>
@@ -3066,7 +3066,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G93" t="n">
-        <v>1.26088833808899</v>
+        <v>1.26088845729828</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G94" t="n">
-        <v>1.24832129478455</v>
+        <v>1.24832141399384</v>
       </c>
       <c r="H94" t="n">
         <v>10500</v>
@@ -3153,7 +3153,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G96" t="n">
-        <v>1.26926636695862</v>
+        <v>1.26926624774933</v>
       </c>
       <c r="H96" t="n">
         <v>1500</v>
@@ -3182,7 +3182,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G97" t="n">
-        <v>1.26926636695862</v>
+        <v>1.26926624774933</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G98" t="n">
-        <v>1.24832129478455</v>
+        <v>1.24832141399384</v>
       </c>
       <c r="H98" t="n">
         <v>4500</v>
@@ -3269,7 +3269,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G100" t="n">
-        <v>1.2276451587677</v>
+        <v>1.22764503955841</v>
       </c>
       <c r="H100" t="n">
         <v>30000</v>
@@ -3298,7 +3298,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G101" t="n">
-        <v>1.21903014183044</v>
+        <v>1.21903002262115</v>
       </c>
       <c r="H101" t="n">
         <v>22500</v>
@@ -3385,7 +3385,7 @@
         <v>1.375</v>
       </c>
       <c r="G104" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H104" t="n">
         <v>9000</v>
@@ -3501,7 +3501,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G108" t="n">
-        <v>1.12857210636139</v>
+        <v>1.1285719871521</v>
       </c>
       <c r="H108" t="n">
         <v>1500</v>
@@ -3530,7 +3530,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G109" t="n">
-        <v>1.12857210636139</v>
+        <v>1.1285719871521</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G110" t="n">
-        <v>1.12857210636139</v>
+        <v>1.1285719871521</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G111" t="n">
-        <v>1.12857210636139</v>
+        <v>1.1285719871521</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G112" t="n">
-        <v>1.12857210636139</v>
+        <v>1.1285719871521</v>
       </c>
       <c r="H112" t="n">
         <v>3000</v>
@@ -3646,7 +3646,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G113" t="n">
-        <v>1.21041512489319</v>
+        <v>1.2104150056839</v>
       </c>
       <c r="H113" t="n">
         <v>9000</v>
@@ -3675,7 +3675,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G114" t="n">
-        <v>1.21903014183044</v>
+        <v>1.21903002262115</v>
       </c>
       <c r="H114" t="n">
         <v>13500</v>
@@ -3791,7 +3791,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G118" t="n">
-        <v>1.17164742946625</v>
+        <v>1.17164731025696</v>
       </c>
       <c r="H118" t="n">
         <v>10500</v>
@@ -3820,7 +3820,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G119" t="n">
-        <v>1.18887746334076</v>
+        <v>1.18887734413147</v>
       </c>
       <c r="H119" t="n">
         <v>1500</v>
@@ -3849,7 +3849,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G120" t="n">
-        <v>1.18887746334076</v>
+        <v>1.18887734413147</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G121" t="n">
-        <v>1.18887746334076</v>
+        <v>1.18887734413147</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G122" t="n">
-        <v>1.21041512489319</v>
+        <v>1.2104150056839</v>
       </c>
       <c r="H122" t="n">
         <v>1500</v>
@@ -3936,7 +3936,7 @@
         <v>1.375</v>
       </c>
       <c r="G123" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H123" t="n">
         <v>3000</v>
@@ -3965,7 +3965,7 @@
         <v>1.375</v>
       </c>
       <c r="G124" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G126" t="n">
-        <v>1.18887746334076</v>
+        <v>1.18887734413147</v>
       </c>
       <c r="H126" t="n">
         <v>3000</v>
@@ -4052,7 +4052,7 @@
         <v>1.375</v>
       </c>
       <c r="G127" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H127" t="n">
         <v>1500</v>
@@ -4081,7 +4081,7 @@
         <v>1.375</v>
       </c>
       <c r="G128" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>1.375</v>
       </c>
       <c r="G129" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H129" t="n">
         <v>3000</v>
@@ -4139,7 +4139,7 @@
         <v>1.375</v>
       </c>
       <c r="G130" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>1.375</v>
       </c>
       <c r="G131" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -4197,7 +4197,7 @@
         <v>1.375</v>
       </c>
       <c r="G132" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H132" t="n">
         <v>1500</v>
@@ -4226,7 +4226,7 @@
         <v>1.375</v>
       </c>
       <c r="G133" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>1.375</v>
       </c>
       <c r="G134" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>1.375</v>
       </c>
       <c r="G135" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>1.375</v>
       </c>
       <c r="G136" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>1.375</v>
       </c>
       <c r="G137" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H137" t="n">
         <v>1500</v>
@@ -4371,7 +4371,7 @@
         <v>1.375</v>
       </c>
       <c r="G138" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G139" t="n">
-        <v>1.20610761642456</v>
+        <v>1.20610749721527</v>
       </c>
       <c r="H139" t="n">
         <v>9000</v>
@@ -4429,7 +4429,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G140" t="n">
-        <v>1.20610761642456</v>
+        <v>1.20610749721527</v>
       </c>
       <c r="H140" t="n">
         <v>1500</v>
@@ -4458,7 +4458,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G141" t="n">
-        <v>1.20610761642456</v>
+        <v>1.20610749721527</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G142" t="n">
-        <v>1.20610761642456</v>
+        <v>1.20610749721527</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G143" t="n">
-        <v>1.20610761642456</v>
+        <v>1.20610749721527</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G144" t="n">
-        <v>1.20610761642456</v>
+        <v>1.20610749721527</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G145" t="n">
-        <v>1.20610761642456</v>
+        <v>1.20610749721527</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G146" t="n">
-        <v>1.13287973403931</v>
+        <v>1.13287961483002</v>
       </c>
       <c r="H146" t="n">
         <v>6000</v>
@@ -4661,7 +4661,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G148" t="n">
-        <v>1.23195266723633</v>
+        <v>1.23195254802704</v>
       </c>
       <c r="H148" t="n">
         <v>3000</v>
@@ -4690,7 +4690,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G149" t="n">
-        <v>1.23195266723633</v>
+        <v>1.23195254802704</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G150" t="n">
-        <v>1.23195266723633</v>
+        <v>1.23195254802704</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G151" t="n">
-        <v>1.16733992099762</v>
+        <v>1.16733980178833</v>
       </c>
       <c r="H151" t="n">
         <v>28500</v>
@@ -4777,7 +4777,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G152" t="n">
-        <v>1.17595493793488</v>
+        <v>1.17595481872559</v>
       </c>
       <c r="H152" t="n">
         <v>18000</v>
@@ -4806,7 +4806,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G153" t="n">
-        <v>1.17164742946625</v>
+        <v>1.17164731025696</v>
       </c>
       <c r="H153" t="n">
         <v>7500</v>
@@ -4835,7 +4835,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G154" t="n">
-        <v>1.16733992099762</v>
+        <v>1.16733980178833</v>
       </c>
       <c r="H154" t="n">
         <v>1500</v>
@@ -4864,7 +4864,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G155" t="n">
-        <v>1.16733992099762</v>
+        <v>1.16733980178833</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G156" t="n">
-        <v>1.16733992099762</v>
+        <v>1.16733980178833</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G157" t="n">
-        <v>1.16733992099762</v>
+        <v>1.16733980178833</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G158" t="n">
-        <v>1.16733992099762</v>
+        <v>1.16733980178833</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>1.16733992099762</v>
+        <v>1.16733980178833</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G160" t="n">
-        <v>1.16733992099762</v>
+        <v>1.16733980178833</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G163" t="n">
-        <v>1.12426435947418</v>
+        <v>1.12426447868347</v>
       </c>
       <c r="H163" t="n">
         <v>4500</v>
@@ -5125,7 +5125,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G164" t="n">
-        <v>1.1458021402359</v>
+        <v>1.14580225944519</v>
       </c>
       <c r="H164" t="n">
         <v>3000</v>
@@ -5154,7 +5154,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G165" t="n">
-        <v>1.1458021402359</v>
+        <v>1.14580225944519</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G166" t="n">
-        <v>1.1458021402359</v>
+        <v>1.14580225944519</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G167" t="n">
-        <v>1.1458021402359</v>
+        <v>1.14580225944519</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -5241,7 +5241,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G168" t="n">
-        <v>1.12426435947418</v>
+        <v>1.12426447868347</v>
       </c>
       <c r="H168" t="n">
         <v>1500</v>
@@ -5270,7 +5270,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G169" t="n">
-        <v>1.12426435947418</v>
+        <v>1.12426447868347</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G171" t="n">
-        <v>1.09411191940308</v>
+        <v>1.09411180019379</v>
       </c>
       <c r="H171" t="n">
         <v>19500</v>
@@ -5531,7 +5531,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G178" t="n">
-        <v>1.0984194278717</v>
+        <v>1.09841930866241</v>
       </c>
       <c r="H178" t="n">
         <v>16500</v>
@@ -5560,7 +5560,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G179" t="n">
-        <v>1.08549678325653</v>
+        <v>1.08549690246582</v>
       </c>
       <c r="H179" t="n">
         <v>7500</v>
@@ -5821,7 +5821,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G188" t="n">
-        <v>0.999346256256104</v>
+        <v>0.999346315860748</v>
       </c>
       <c r="H188" t="n">
         <v>4500</v>
@@ -5879,7 +5879,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G190" t="n">
-        <v>0.926118314266205</v>
+        <v>0.92611837387085</v>
       </c>
       <c r="H190" t="n">
         <v>63000</v>
@@ -5908,7 +5908,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G191" t="n">
-        <v>0.926118314266205</v>
+        <v>0.92611837387085</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G192" t="n">
-        <v>0.926118314266205</v>
+        <v>0.92611837387085</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G193" t="n">
-        <v>0.926118314266205</v>
+        <v>0.92611837387085</v>
       </c>
       <c r="H193" t="n">
         <v>1500</v>
@@ -5995,7 +5995,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G194" t="n">
-        <v>0.900273084640503</v>
+        <v>0.900273144245148</v>
       </c>
       <c r="H194" t="n">
         <v>9000</v>
@@ -6024,7 +6024,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G195" t="n">
-        <v>0.900273084640503</v>
+        <v>0.900273144245148</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G196" t="n">
-        <v>0.900273084640503</v>
+        <v>0.900273144245148</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>0.878735482692719</v>
+        <v>0.878735423088074</v>
       </c>
       <c r="H199" t="n">
         <v>3000</v>
@@ -6169,7 +6169,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>0.89596563577652</v>
+        <v>0.89596551656723</v>
       </c>
       <c r="H200" t="n">
         <v>6000</v>
@@ -6198,7 +6198,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G201" t="n">
-        <v>0.878735482692719</v>
+        <v>0.878735423088074</v>
       </c>
       <c r="H201" t="n">
         <v>3000</v>
@@ -6372,7 +6372,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G207" t="n">
-        <v>0.870120465755463</v>
+        <v>0.870120406150818</v>
       </c>
       <c r="H207" t="n">
         <v>6000</v>
@@ -6401,7 +6401,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G208" t="n">
-        <v>0.870120465755463</v>
+        <v>0.870120406150818</v>
       </c>
       <c r="H208" t="n">
         <v>4500</v>
@@ -6430,7 +6430,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G209" t="n">
-        <v>0.891658067703247</v>
+        <v>0.891658008098602</v>
       </c>
       <c r="H209" t="n">
         <v>3000</v>
@@ -6459,7 +6459,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G210" t="n">
-        <v>0.908888101577759</v>
+        <v>0.908888161182404</v>
       </c>
       <c r="H210" t="n">
         <v>1500</v>
@@ -6488,7 +6488,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G211" t="n">
-        <v>0.908888101577759</v>
+        <v>0.908888161182404</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G212" t="n">
-        <v>0.908888101577759</v>
+        <v>0.908888161182404</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G213" t="n">
-        <v>0.908888101577759</v>
+        <v>0.908888161182404</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>0.878735482692719</v>
+        <v>0.878735423088074</v>
       </c>
       <c r="H227" t="n">
         <v>9000</v>
@@ -6981,7 +6981,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G228" t="n">
-        <v>0.878735482692719</v>
+        <v>0.878735423088074</v>
       </c>
       <c r="H228" t="n">
         <v>15000</v>
@@ -7126,7 +7126,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G233" t="n">
-        <v>0.747786641120911</v>
+        <v>0.747786700725555</v>
       </c>
       <c r="H233" t="n">
         <v>31500</v>
@@ -7155,7 +7155,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G234" t="n">
-        <v>0.680589377880096</v>
+        <v>0.680589318275452</v>
       </c>
       <c r="H234" t="n">
         <v>120000</v>
@@ -7300,7 +7300,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G239" t="n">
-        <v>0.69954240322113</v>
+        <v>0.699542343616486</v>
       </c>
       <c r="H239" t="n">
         <v>16500</v>
@@ -7329,7 +7329,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G240" t="n">
-        <v>0.732279539108276</v>
+        <v>0.732279598712921</v>
       </c>
       <c r="H240" t="n">
         <v>25500</v>
@@ -7358,7 +7358,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G241" t="n">
-        <v>0.739171624183655</v>
+        <v>0.7391716837883</v>
       </c>
       <c r="H241" t="n">
         <v>12000</v>
@@ -7387,7 +7387,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G242" t="n">
-        <v>0.792584896087646</v>
+        <v>0.792584955692291</v>
       </c>
       <c r="H242" t="n">
         <v>75000</v>
@@ -7503,7 +7503,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G246" t="n">
-        <v>0.844275295734406</v>
+        <v>0.84427535533905</v>
       </c>
       <c r="H246" t="n">
         <v>45000</v>
@@ -7532,7 +7532,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G247" t="n">
-        <v>0.851167261600494</v>
+        <v>0.851167321205139</v>
       </c>
       <c r="H247" t="n">
         <v>4500</v>
@@ -7561,7 +7561,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G248" t="n">
-        <v>0.89596563577652</v>
+        <v>0.89596551656723</v>
       </c>
       <c r="H248" t="n">
         <v>25500</v>
@@ -7619,7 +7619,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G250" t="n">
-        <v>1.10703432559967</v>
+        <v>1.10703444480896</v>
       </c>
       <c r="H250" t="n">
         <v>192000</v>
@@ -7677,7 +7677,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G252" t="n">
-        <v>1.07257413864136</v>
+        <v>1.07257425785065</v>
       </c>
       <c r="H252" t="n">
         <v>73500</v>
@@ -7822,7 +7822,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G257" t="n">
-        <v>1.07257413864136</v>
+        <v>1.07257425785065</v>
       </c>
       <c r="H257" t="n">
         <v>45000</v>
@@ -7909,7 +7909,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G260" t="n">
-        <v>1.0984194278717</v>
+        <v>1.09841930866241</v>
       </c>
       <c r="H260" t="n">
         <v>52500</v>
@@ -7938,7 +7938,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G261" t="n">
-        <v>1.10703432559967</v>
+        <v>1.10703444480896</v>
       </c>
       <c r="H261" t="n">
         <v>48000</v>
@@ -7967,7 +7967,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G262" t="n">
-        <v>1.0984194278717</v>
+        <v>1.09841930866241</v>
       </c>
       <c r="H262" t="n">
         <v>36000</v>
@@ -8199,7 +8199,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G270" t="n">
-        <v>1.11995697021484</v>
+        <v>1.11995708942413</v>
       </c>
       <c r="H270" t="n">
         <v>7500</v>
@@ -8286,7 +8286,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G273" t="n">
-        <v>1.13718724250793</v>
+        <v>1.13718712329865</v>
       </c>
       <c r="H273" t="n">
         <v>69000</v>
@@ -8315,7 +8315,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G274" t="n">
-        <v>1.17164742946625</v>
+        <v>1.17164731025696</v>
       </c>
       <c r="H274" t="n">
         <v>54000</v>
@@ -8344,7 +8344,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>1.14762711524963</v>
+        <v>1.14762723445892</v>
       </c>
       <c r="H275" t="n">
         <v>22500</v>
@@ -8605,7 +8605,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G284" t="n">
-        <v>1.08535277843475</v>
+        <v>1.08535289764404</v>
       </c>
       <c r="H284" t="n">
         <v>18000</v>
@@ -8634,7 +8634,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G285" t="n">
-        <v>1.05421555042267</v>
+        <v>1.05421566963196</v>
       </c>
       <c r="H285" t="n">
         <v>16500</v>
@@ -8692,7 +8692,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G287" t="n">
-        <v>1.01863026618958</v>
+        <v>1.01863038539886</v>
       </c>
       <c r="H287" t="n">
         <v>19500</v>
@@ -8721,7 +8721,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G288" t="n">
-        <v>1.01863026618958</v>
+        <v>1.01863038539886</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G290" t="n">
-        <v>1.02307844161987</v>
+        <v>1.02307856082916</v>
       </c>
       <c r="H290" t="n">
         <v>3000</v>
@@ -8808,7 +8808,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G291" t="n">
-        <v>1.02307844161987</v>
+        <v>1.02307856082916</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G294" t="n">
-        <v>0.987493216991425</v>
+        <v>0.98749315738678</v>
       </c>
       <c r="H294" t="n">
         <v>4500</v>
@@ -9069,7 +9069,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G300" t="n">
-        <v>1.02307844161987</v>
+        <v>1.02307856082916</v>
       </c>
       <c r="H300" t="n">
         <v>10500</v>
@@ -9185,7 +9185,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G304" t="n">
-        <v>1.02752661705017</v>
+        <v>1.02752673625946</v>
       </c>
       <c r="H304" t="n">
         <v>25500</v>
@@ -9301,7 +9301,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G308" t="n">
-        <v>0.983045041561127</v>
+        <v>0.983044981956482</v>
       </c>
       <c r="H308" t="n">
         <v>12000</v>
@@ -9533,7 +9533,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G316" t="n">
-        <v>0.987493216991425</v>
+        <v>0.98749315738678</v>
       </c>
       <c r="H316" t="n">
         <v>1500</v>
@@ -9562,7 +9562,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G317" t="n">
-        <v>0.983045041561127</v>
+        <v>0.983044981956482</v>
       </c>
       <c r="H317" t="n">
         <v>3000</v>
@@ -9591,7 +9591,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G318" t="n">
-        <v>0.920770645141602</v>
+        <v>0.920770585536957</v>
       </c>
       <c r="H318" t="n">
         <v>12000</v>
@@ -9823,7 +9823,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G326" t="n">
-        <v>1.06311202049255</v>
+        <v>1.06311213970184</v>
       </c>
       <c r="H326" t="n">
         <v>1500</v>
@@ -9852,7 +9852,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G327" t="n">
-        <v>1.05866384506226</v>
+        <v>1.05866396427155</v>
       </c>
       <c r="H327" t="n">
         <v>4500</v>
@@ -9881,7 +9881,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>1.05866384506226</v>
+        <v>1.05866396427155</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G333" t="n">
-        <v>1.08535277843475</v>
+        <v>1.08535289764404</v>
       </c>
       <c r="H333" t="n">
         <v>6000</v>
@@ -10055,7 +10055,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G334" t="n">
-        <v>1.12093818187714</v>
+        <v>1.12093830108643</v>
       </c>
       <c r="H334" t="n">
         <v>63000</v>
@@ -10113,7 +10113,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>1.09424924850464</v>
+        <v>1.09424936771393</v>
       </c>
       <c r="H336" t="n">
         <v>36000</v>
@@ -10200,7 +10200,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G339" t="n">
-        <v>1.08535277843475</v>
+        <v>1.08535289764404</v>
       </c>
       <c r="H339" t="n">
         <v>4500</v>
@@ -10229,7 +10229,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G340" t="n">
-        <v>1.09424924850464</v>
+        <v>1.09424936771393</v>
       </c>
       <c r="H340" t="n">
         <v>13500</v>
@@ -10258,7 +10258,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G341" t="n">
-        <v>1.09424924850464</v>
+        <v>1.09424936771393</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G346" t="n">
-        <v>1.03197479248047</v>
+        <v>1.03197491168976</v>
       </c>
       <c r="H346" t="n">
         <v>34500</v>
@@ -10432,7 +10432,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G347" t="n">
-        <v>1.02307844161987</v>
+        <v>1.02307856082916</v>
       </c>
       <c r="H347" t="n">
         <v>19500</v>
@@ -10461,7 +10461,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G348" t="n">
-        <v>1.03197479248047</v>
+        <v>1.03197491168976</v>
       </c>
       <c r="H348" t="n">
         <v>1500</v>
@@ -10606,7 +10606,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G353" t="n">
-        <v>1.02307844161987</v>
+        <v>1.02307856082916</v>
       </c>
       <c r="H353" t="n">
         <v>4500</v>
@@ -10635,7 +10635,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G354" t="n">
-        <v>1.02307844161987</v>
+        <v>1.02307856082916</v>
       </c>
       <c r="H354" t="n">
         <v>1500</v>
@@ -10664,7 +10664,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>1.05866384506226</v>
+        <v>1.05866396427155</v>
       </c>
       <c r="H355" t="n">
         <v>7500</v>
@@ -10693,7 +10693,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G356" t="n">
-        <v>1.05866384506226</v>
+        <v>1.05866396427155</v>
       </c>
       <c r="H356" t="n">
         <v>9000</v>
@@ -28737,6 +28737,35 @@
         <v>21000</v>
       </c>
       <c r="I978" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="s">
+        <v>9</v>
+      </c>
+      <c r="B979" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C979" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="D979" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="E979" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="F979" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="G979" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="H979" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I979" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SAC.MI.xlsx
+++ b/data/SAC.MI.xlsx
@@ -543,7 +543,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G6" t="n">
-        <v>1.75100100040436</v>
+        <v>1.75100111961365</v>
       </c>
       <c r="H6" t="n">
         <v>144000</v>
@@ -630,7 +630,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G9" t="n">
-        <v>1.75519013404846</v>
+        <v>1.75519025325775</v>
       </c>
       <c r="H9" t="n">
         <v>57000</v>
@@ -688,7 +688,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>1.70911085605621</v>
+        <v>1.7091109752655</v>
       </c>
       <c r="H11" t="n">
         <v>18000</v>
@@ -717,7 +717,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>1.70911085605621</v>
+        <v>1.7091109752655</v>
       </c>
       <c r="H12" t="n">
         <v>3000</v>
@@ -775,7 +775,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7342449426651</v>
+        <v>1.73424506187439</v>
       </c>
       <c r="H14" t="n">
         <v>1500</v>
@@ -804,7 +804,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G15" t="n">
-        <v>1.69235503673553</v>
+        <v>1.69235515594482</v>
       </c>
       <c r="H15" t="n">
         <v>15000</v>
@@ -833,7 +833,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7342449426651</v>
+        <v>1.73424506187439</v>
       </c>
       <c r="H16" t="n">
         <v>7500</v>
@@ -862,7 +862,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G17" t="n">
-        <v>1.69235503673553</v>
+        <v>1.69235515594482</v>
       </c>
       <c r="H17" t="n">
         <v>12000</v>
@@ -891,7 +891,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G18" t="n">
-        <v>1.61192643642426</v>
+        <v>1.61192631721497</v>
       </c>
       <c r="H18" t="n">
         <v>28500</v>
@@ -920,7 +920,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G19" t="n">
-        <v>1.59181916713715</v>
+        <v>1.59181904792786</v>
       </c>
       <c r="H19" t="n">
         <v>16500</v>
@@ -978,7 +978,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G21" t="n">
-        <v>1.57841432094574</v>
+        <v>1.57841408252716</v>
       </c>
       <c r="H21" t="n">
         <v>6000</v>
@@ -1007,7 +1007,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G22" t="n">
-        <v>1.60522401332855</v>
+        <v>1.60522389411926</v>
       </c>
       <c r="H22" t="n">
         <v>6000</v>
@@ -1094,7 +1094,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G25" t="n">
-        <v>1.6270067691803</v>
+        <v>1.62700688838959</v>
       </c>
       <c r="H25" t="n">
         <v>12000</v>
@@ -1239,7 +1239,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G30" t="n">
-        <v>1.57841432094574</v>
+        <v>1.57841408252716</v>
       </c>
       <c r="H30" t="n">
         <v>24000</v>
@@ -1413,7 +1413,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G36" t="n">
-        <v>1.38655805587769</v>
+        <v>1.38655829429626</v>
       </c>
       <c r="H36" t="n">
         <v>3000</v>
@@ -1442,7 +1442,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G37" t="n">
-        <v>1.34885728359222</v>
+        <v>1.34885740280151</v>
       </c>
       <c r="H37" t="n">
         <v>7500</v>
@@ -1471,7 +1471,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G38" t="n">
-        <v>1.31534540653229</v>
+        <v>1.315345287323</v>
       </c>
       <c r="H38" t="n">
         <v>12000</v>
@@ -1587,7 +1587,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G42" t="n">
-        <v>1.21480929851532</v>
+        <v>1.21480941772461</v>
       </c>
       <c r="H42" t="n">
         <v>13500</v>
@@ -1616,7 +1616,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G43" t="n">
-        <v>1.19805312156677</v>
+        <v>1.19805324077606</v>
       </c>
       <c r="H43" t="n">
         <v>10500</v>
@@ -1645,7 +1645,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G44" t="n">
-        <v>1.20643138885498</v>
+        <v>1.20643150806427</v>
       </c>
       <c r="H44" t="n">
         <v>7500</v>
@@ -1674,7 +1674,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G45" t="n">
-        <v>1.21062028408051</v>
+        <v>1.21062052249908</v>
       </c>
       <c r="H45" t="n">
         <v>100500</v>
@@ -1703,7 +1703,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G46" t="n">
-        <v>1.22737646102905</v>
+        <v>1.22737634181976</v>
       </c>
       <c r="H46" t="n">
         <v>30000</v>
@@ -1761,7 +1761,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G48" t="n">
-        <v>1.26926624774933</v>
+        <v>1.26926636695862</v>
       </c>
       <c r="H48" t="n">
         <v>27000</v>
@@ -1790,7 +1790,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G49" t="n">
-        <v>1.30277824401855</v>
+        <v>1.30277812480927</v>
       </c>
       <c r="H49" t="n">
         <v>48000</v>
@@ -1819,7 +1819,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G50" t="n">
-        <v>1.30277824401855</v>
+        <v>1.30277812480927</v>
       </c>
       <c r="H50" t="n">
         <v>54000</v>
@@ -1877,7 +1877,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G52" t="n">
-        <v>1.28183341026306</v>
+        <v>1.28183317184448</v>
       </c>
       <c r="H52" t="n">
         <v>28500</v>
@@ -2138,7 +2138,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G61" t="n">
-        <v>1.24413239955902</v>
+        <v>1.24413228034973</v>
       </c>
       <c r="H61" t="n">
         <v>21000</v>
@@ -2196,7 +2196,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G63" t="n">
-        <v>1.26507747173309</v>
+        <v>1.2650773525238</v>
       </c>
       <c r="H63" t="n">
         <v>15000</v>
@@ -2225,7 +2225,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G64" t="n">
-        <v>1.27764439582825</v>
+        <v>1.27764427661896</v>
       </c>
       <c r="H64" t="n">
         <v>4500</v>
@@ -2254,7 +2254,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G65" t="n">
-        <v>1.26926624774933</v>
+        <v>1.26926636695862</v>
       </c>
       <c r="H65" t="n">
         <v>1500</v>
@@ -2283,7 +2283,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G66" t="n">
-        <v>1.26088845729828</v>
+        <v>1.26088833808899</v>
       </c>
       <c r="H66" t="n">
         <v>21000</v>
@@ -2428,7 +2428,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G71" t="n">
-        <v>1.28183341026306</v>
+        <v>1.28183317184448</v>
       </c>
       <c r="H71" t="n">
         <v>46500</v>
@@ -2486,7 +2486,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G73" t="n">
-        <v>1.30277824401855</v>
+        <v>1.30277812480927</v>
       </c>
       <c r="H73" t="n">
         <v>1500</v>
@@ -2660,7 +2660,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G79" t="n">
-        <v>1.27764439582825</v>
+        <v>1.27764427661896</v>
       </c>
       <c r="H79" t="n">
         <v>12000</v>
@@ -2689,7 +2689,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G80" t="n">
-        <v>1.27764439582825</v>
+        <v>1.27764427661896</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G81" t="n">
-        <v>1.29858922958374</v>
+        <v>1.29858934879303</v>
       </c>
       <c r="H81" t="n">
         <v>33000</v>
@@ -2747,7 +2747,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G82" t="n">
-        <v>1.34885728359222</v>
+        <v>1.34885740280151</v>
       </c>
       <c r="H82" t="n">
         <v>78000</v>
@@ -2805,7 +2805,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G84" t="n">
-        <v>1.35723519325256</v>
+        <v>1.35723531246185</v>
       </c>
       <c r="H84" t="n">
         <v>39000</v>
@@ -2834,7 +2834,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G85" t="n">
-        <v>1.32791221141815</v>
+        <v>1.32791244983673</v>
       </c>
       <c r="H85" t="n">
         <v>19500</v>
@@ -2892,7 +2892,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G87" t="n">
-        <v>1.30696725845337</v>
+        <v>1.30696713924408</v>
       </c>
       <c r="H87" t="n">
         <v>13500</v>
@@ -2950,7 +2950,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G89" t="n">
-        <v>1.26088845729828</v>
+        <v>1.26088833808899</v>
       </c>
       <c r="H89" t="n">
         <v>6000</v>
@@ -2979,7 +2979,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G90" t="n">
-        <v>1.26088845729828</v>
+        <v>1.26088833808899</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G91" t="n">
-        <v>1.26088845729828</v>
+        <v>1.26088833808899</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G92" t="n">
-        <v>1.26088845729828</v>
+        <v>1.26088833808899</v>
       </c>
       <c r="H92" t="n">
         <v>1500</v>
@@ -3066,7 +3066,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G93" t="n">
-        <v>1.26088845729828</v>
+        <v>1.26088833808899</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G96" t="n">
-        <v>1.26926624774933</v>
+        <v>1.26926636695862</v>
       </c>
       <c r="H96" t="n">
         <v>1500</v>
@@ -3182,7 +3182,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G97" t="n">
-        <v>1.26926624774933</v>
+        <v>1.26926636695862</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>1.5</v>
       </c>
       <c r="G99" t="n">
-        <v>1.29225814342499</v>
+        <v>1.2922580242157</v>
       </c>
       <c r="H99" t="n">
         <v>4500</v>
@@ -3298,7 +3298,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G101" t="n">
-        <v>1.21903002262115</v>
+        <v>1.21903014183044</v>
       </c>
       <c r="H101" t="n">
         <v>22500</v>
@@ -3385,7 +3385,7 @@
         <v>1.375</v>
       </c>
       <c r="G104" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H104" t="n">
         <v>9000</v>
@@ -3414,7 +3414,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G105" t="n">
-        <v>1.15441715717316</v>
+        <v>1.15441727638245</v>
       </c>
       <c r="H105" t="n">
         <v>3000</v>
@@ -3443,7 +3443,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G106" t="n">
-        <v>1.14149475097656</v>
+        <v>1.14149463176727</v>
       </c>
       <c r="H106" t="n">
         <v>4500</v>
@@ -3472,7 +3472,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G107" t="n">
-        <v>1.14149475097656</v>
+        <v>1.14149463176727</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G108" t="n">
-        <v>1.1285719871521</v>
+        <v>1.12857210636139</v>
       </c>
       <c r="H108" t="n">
         <v>1500</v>
@@ -3530,7 +3530,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G109" t="n">
-        <v>1.1285719871521</v>
+        <v>1.12857210636139</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G110" t="n">
-        <v>1.1285719871521</v>
+        <v>1.12857210636139</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G111" t="n">
-        <v>1.1285719871521</v>
+        <v>1.12857210636139</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G112" t="n">
-        <v>1.1285719871521</v>
+        <v>1.12857210636139</v>
       </c>
       <c r="H112" t="n">
         <v>3000</v>
@@ -3646,7 +3646,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G113" t="n">
-        <v>1.2104150056839</v>
+        <v>1.21041512489319</v>
       </c>
       <c r="H113" t="n">
         <v>9000</v>
@@ -3675,7 +3675,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G114" t="n">
-        <v>1.21903002262115</v>
+        <v>1.21903014183044</v>
       </c>
       <c r="H114" t="n">
         <v>13500</v>
@@ -3704,7 +3704,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G115" t="n">
-        <v>1.1931848526001</v>
+        <v>1.19318497180939</v>
       </c>
       <c r="H115" t="n">
         <v>4500</v>
@@ -3733,7 +3733,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G116" t="n">
-        <v>1.1931848526001</v>
+        <v>1.19318497180939</v>
       </c>
       <c r="H116" t="n">
         <v>1500</v>
@@ -3762,7 +3762,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G117" t="n">
-        <v>1.1931848526001</v>
+        <v>1.19318497180939</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G122" t="n">
-        <v>1.2104150056839</v>
+        <v>1.21041512489319</v>
       </c>
       <c r="H122" t="n">
         <v>1500</v>
@@ -3936,7 +3936,7 @@
         <v>1.375</v>
       </c>
       <c r="G123" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H123" t="n">
         <v>3000</v>
@@ -3965,7 +3965,7 @@
         <v>1.375</v>
       </c>
       <c r="G124" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G125" t="n">
-        <v>1.1802624464035</v>
+        <v>1.18026256561279</v>
       </c>
       <c r="H125" t="n">
         <v>3000</v>
@@ -4052,7 +4052,7 @@
         <v>1.375</v>
       </c>
       <c r="G127" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H127" t="n">
         <v>1500</v>
@@ -4081,7 +4081,7 @@
         <v>1.375</v>
       </c>
       <c r="G128" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>1.375</v>
       </c>
       <c r="G129" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H129" t="n">
         <v>3000</v>
@@ -4139,7 +4139,7 @@
         <v>1.375</v>
       </c>
       <c r="G130" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>1.375</v>
       </c>
       <c r="G131" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -4197,7 +4197,7 @@
         <v>1.375</v>
       </c>
       <c r="G132" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H132" t="n">
         <v>1500</v>
@@ -4226,7 +4226,7 @@
         <v>1.375</v>
       </c>
       <c r="G133" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>1.375</v>
       </c>
       <c r="G134" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>1.375</v>
       </c>
       <c r="G135" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>1.375</v>
       </c>
       <c r="G136" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>1.375</v>
       </c>
       <c r="G137" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H137" t="n">
         <v>1500</v>
@@ -4371,7 +4371,7 @@
         <v>1.375</v>
       </c>
       <c r="G138" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G139" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H139" t="n">
         <v>9000</v>
@@ -4429,7 +4429,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G140" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H140" t="n">
         <v>1500</v>
@@ -4458,7 +4458,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G141" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G142" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G143" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G144" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G145" t="n">
-        <v>1.20610749721527</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G147" t="n">
-        <v>1.24056780338287</v>
+        <v>1.24056792259216</v>
       </c>
       <c r="H147" t="n">
         <v>18000</v>
@@ -4661,7 +4661,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G148" t="n">
-        <v>1.23195254802704</v>
+        <v>1.23195266723633</v>
       </c>
       <c r="H148" t="n">
         <v>3000</v>
@@ -4690,7 +4690,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G149" t="n">
-        <v>1.23195254802704</v>
+        <v>1.23195266723633</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G150" t="n">
-        <v>1.23195254802704</v>
+        <v>1.23195266723633</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G152" t="n">
-        <v>1.17595481872559</v>
+        <v>1.17595493793488</v>
       </c>
       <c r="H152" t="n">
         <v>18000</v>
@@ -5038,7 +5038,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G161" t="n">
-        <v>1.1802624464035</v>
+        <v>1.18026256561279</v>
       </c>
       <c r="H161" t="n">
         <v>4500</v>
@@ -5067,7 +5067,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G162" t="n">
-        <v>1.15441715717316</v>
+        <v>1.15441727638245</v>
       </c>
       <c r="H162" t="n">
         <v>3000</v>
@@ -5560,7 +5560,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G179" t="n">
-        <v>1.08549690246582</v>
+        <v>1.08549678325653</v>
       </c>
       <c r="H179" t="n">
         <v>7500</v>
@@ -5792,7 +5792,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G187" t="n">
-        <v>1.02519154548645</v>
+        <v>1.02519142627716</v>
       </c>
       <c r="H187" t="n">
         <v>3000</v>
@@ -5821,7 +5821,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G188" t="n">
-        <v>0.999346315860748</v>
+        <v>0.999346256256104</v>
       </c>
       <c r="H188" t="n">
         <v>4500</v>
@@ -5995,7 +5995,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G194" t="n">
-        <v>0.900273144245148</v>
+        <v>0.900273203849792</v>
       </c>
       <c r="H194" t="n">
         <v>9000</v>
@@ -6024,7 +6024,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G195" t="n">
-        <v>0.900273144245148</v>
+        <v>0.900273203849792</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G196" t="n">
-        <v>0.900273144245148</v>
+        <v>0.900273203849792</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G197" t="n">
-        <v>0.887350499629974</v>
+        <v>0.887350559234619</v>
       </c>
       <c r="H197" t="n">
         <v>3000</v>
@@ -6111,7 +6111,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G198" t="n">
-        <v>0.887350499629974</v>
+        <v>0.887350559234619</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>0.878735423088074</v>
+        <v>0.878735482692719</v>
       </c>
       <c r="H199" t="n">
         <v>3000</v>
@@ -6169,7 +6169,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>0.89596551656723</v>
+        <v>0.895965576171875</v>
       </c>
       <c r="H200" t="n">
         <v>6000</v>
@@ -6198,7 +6198,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G201" t="n">
-        <v>0.878735423088074</v>
+        <v>0.878735482692719</v>
       </c>
       <c r="H201" t="n">
         <v>3000</v>
@@ -6227,7 +6227,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G202" t="n">
-        <v>0.887350499629974</v>
+        <v>0.887350559234619</v>
       </c>
       <c r="H202" t="n">
         <v>7500</v>
@@ -6256,7 +6256,7 @@
         <v>1</v>
       </c>
       <c r="G203" t="n">
-        <v>0.861505389213562</v>
+        <v>0.861505448818207</v>
       </c>
       <c r="H203" t="n">
         <v>1500</v>
@@ -6285,7 +6285,7 @@
         <v>1</v>
       </c>
       <c r="G204" t="n">
-        <v>0.861505389213562</v>
+        <v>0.861505448818207</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6372,7 +6372,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G207" t="n">
-        <v>0.870120406150818</v>
+        <v>0.870120465755463</v>
       </c>
       <c r="H207" t="n">
         <v>6000</v>
@@ -6401,7 +6401,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G208" t="n">
-        <v>0.870120406150818</v>
+        <v>0.870120465755463</v>
       </c>
       <c r="H208" t="n">
         <v>4500</v>
@@ -6430,7 +6430,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G209" t="n">
-        <v>0.891658008098602</v>
+        <v>0.891658067703247</v>
       </c>
       <c r="H209" t="n">
         <v>3000</v>
@@ -6459,7 +6459,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G210" t="n">
-        <v>0.908888161182404</v>
+        <v>0.908888101577759</v>
       </c>
       <c r="H210" t="n">
         <v>1500</v>
@@ -6488,7 +6488,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G211" t="n">
-        <v>0.908888161182404</v>
+        <v>0.908888101577759</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G212" t="n">
-        <v>0.908888161182404</v>
+        <v>0.908888101577759</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G213" t="n">
-        <v>0.908888161182404</v>
+        <v>0.908888101577759</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>0.878735423088074</v>
+        <v>0.878735482692719</v>
       </c>
       <c r="H227" t="n">
         <v>9000</v>
@@ -6981,7 +6981,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G228" t="n">
-        <v>0.878735423088074</v>
+        <v>0.878735482692719</v>
       </c>
       <c r="H228" t="n">
         <v>15000</v>
@@ -7068,7 +7068,7 @@
         <v>1</v>
       </c>
       <c r="G231" t="n">
-        <v>0.861505389213562</v>
+        <v>0.861505448818207</v>
       </c>
       <c r="H231" t="n">
         <v>6000</v>
@@ -7126,7 +7126,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G233" t="n">
-        <v>0.747786700725555</v>
+        <v>0.747786581516266</v>
       </c>
       <c r="H233" t="n">
         <v>31500</v>
@@ -7242,7 +7242,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G237" t="n">
-        <v>0.671974182128906</v>
+        <v>0.671974122524261</v>
       </c>
       <c r="H237" t="n">
         <v>51000</v>
@@ -7300,7 +7300,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G239" t="n">
-        <v>0.699542343616486</v>
+        <v>0.69954240322113</v>
       </c>
       <c r="H239" t="n">
         <v>16500</v>
@@ -7358,7 +7358,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G241" t="n">
-        <v>0.7391716837883</v>
+        <v>0.739171624183655</v>
       </c>
       <c r="H241" t="n">
         <v>12000</v>
@@ -7416,7 +7416,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G243" t="n">
-        <v>0.847721338272095</v>
+        <v>0.84772139787674</v>
       </c>
       <c r="H243" t="n">
         <v>48000</v>
@@ -7445,7 +7445,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G244" t="n">
-        <v>0.797753989696503</v>
+        <v>0.797754049301147</v>
       </c>
       <c r="H244" t="n">
         <v>63000</v>
@@ -7503,7 +7503,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G246" t="n">
-        <v>0.84427535533905</v>
+        <v>0.844275295734406</v>
       </c>
       <c r="H246" t="n">
         <v>45000</v>
@@ -7532,7 +7532,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G247" t="n">
-        <v>0.851167321205139</v>
+        <v>0.851167261600494</v>
       </c>
       <c r="H247" t="n">
         <v>4500</v>
@@ -7561,7 +7561,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G248" t="n">
-        <v>0.89596551656723</v>
+        <v>0.895965576171875</v>
       </c>
       <c r="H248" t="n">
         <v>25500</v>
@@ -7590,7 +7590,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G249" t="n">
-        <v>0.990731239318848</v>
+        <v>0.990731179714203</v>
       </c>
       <c r="H249" t="n">
         <v>90000</v>
@@ -7648,7 +7648,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G251" t="n">
-        <v>1.14149475097656</v>
+        <v>1.14149463176727</v>
       </c>
       <c r="H251" t="n">
         <v>184500</v>
@@ -7677,7 +7677,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G252" t="n">
-        <v>1.07257425785065</v>
+        <v>1.07257413864136</v>
       </c>
       <c r="H252" t="n">
         <v>73500</v>
@@ -7706,7 +7706,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G253" t="n">
-        <v>1.01226878166199</v>
+        <v>1.01226890087128</v>
       </c>
       <c r="H253" t="n">
         <v>136500</v>
@@ -7822,7 +7822,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G257" t="n">
-        <v>1.07257425785065</v>
+        <v>1.07257413864136</v>
       </c>
       <c r="H257" t="n">
         <v>45000</v>
@@ -7996,7 +7996,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G263" t="n">
-        <v>1.11134195327759</v>
+        <v>1.1113418340683</v>
       </c>
       <c r="H263" t="n">
         <v>24000</v>
@@ -8112,7 +8112,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G267" t="n">
-        <v>1.11134195327759</v>
+        <v>1.1113418340683</v>
       </c>
       <c r="H267" t="n">
         <v>69000</v>
@@ -8141,7 +8141,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G268" t="n">
-        <v>1.11134195327759</v>
+        <v>1.1113418340683</v>
       </c>
       <c r="H268" t="n">
         <v>7500</v>
@@ -8170,7 +8170,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G269" t="n">
-        <v>1.11134195327759</v>
+        <v>1.1113418340683</v>
       </c>
       <c r="H269" t="n">
         <v>4500</v>
@@ -8228,7 +8228,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G271" t="n">
-        <v>1.11134195327759</v>
+        <v>1.1113418340683</v>
       </c>
       <c r="H271" t="n">
         <v>63000</v>
@@ -8402,7 +8402,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G277" t="n">
-        <v>1.12983453273773</v>
+        <v>1.12983465194702</v>
       </c>
       <c r="H277" t="n">
         <v>16500</v>
@@ -8431,7 +8431,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>1.12983453273773</v>
+        <v>1.12983465194702</v>
       </c>
       <c r="H278" t="n">
         <v>6000</v>
@@ -8460,7 +8460,7 @@
         <v>1.25</v>
       </c>
       <c r="G279" t="n">
-        <v>1.11204195022583</v>
+        <v>1.11204183101654</v>
       </c>
       <c r="H279" t="n">
         <v>12000</v>
@@ -8518,7 +8518,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G281" t="n">
-        <v>1.12983453273773</v>
+        <v>1.12983465194702</v>
       </c>
       <c r="H281" t="n">
         <v>6000</v>
@@ -8692,7 +8692,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G287" t="n">
-        <v>1.01863038539886</v>
+        <v>1.01863026618958</v>
       </c>
       <c r="H287" t="n">
         <v>19500</v>
@@ -8721,7 +8721,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G288" t="n">
-        <v>1.01863038539886</v>
+        <v>1.01863026618958</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G289" t="n">
-        <v>0.996389508247375</v>
+        <v>0.99638956785202</v>
       </c>
       <c r="H289" t="n">
         <v>12000</v>
@@ -8779,7 +8779,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G290" t="n">
-        <v>1.02307856082916</v>
+        <v>1.02307868003845</v>
       </c>
       <c r="H290" t="n">
         <v>3000</v>
@@ -8808,7 +8808,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G291" t="n">
-        <v>1.02307856082916</v>
+        <v>1.02307868003845</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G292" t="n">
-        <v>1.00528585910797</v>
+        <v>1.00528597831726</v>
       </c>
       <c r="H292" t="n">
         <v>10500</v>
@@ -8924,7 +8924,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G295" t="n">
-        <v>1.00528585910797</v>
+        <v>1.00528597831726</v>
       </c>
       <c r="H295" t="n">
         <v>27000</v>
@@ -9069,7 +9069,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G300" t="n">
-        <v>1.02307856082916</v>
+        <v>1.02307868003845</v>
       </c>
       <c r="H300" t="n">
         <v>10500</v>
@@ -9214,7 +9214,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G305" t="n">
-        <v>1.00528585910797</v>
+        <v>1.00528597831726</v>
       </c>
       <c r="H305" t="n">
         <v>15000</v>
@@ -9243,7 +9243,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G306" t="n">
-        <v>1.00528585910797</v>
+        <v>1.00528597831726</v>
       </c>
       <c r="H306" t="n">
         <v>3000</v>
@@ -9272,7 +9272,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G307" t="n">
-        <v>1.00528585910797</v>
+        <v>1.00528597831726</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G309" t="n">
-        <v>0.991941332817078</v>
+        <v>0.991941392421722</v>
       </c>
       <c r="H309" t="n">
         <v>1500</v>
@@ -9417,7 +9417,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G312" t="n">
-        <v>0.996389508247375</v>
+        <v>0.99638956785202</v>
       </c>
       <c r="H312" t="n">
         <v>1500</v>
@@ -9446,7 +9446,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G313" t="n">
-        <v>0.991941332817078</v>
+        <v>0.991941392421722</v>
       </c>
       <c r="H313" t="n">
         <v>3000</v>
@@ -9475,7 +9475,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G314" t="n">
-        <v>0.991941332817078</v>
+        <v>0.991941392421722</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G318" t="n">
-        <v>0.920770585536957</v>
+        <v>0.920770645141602</v>
       </c>
       <c r="H318" t="n">
         <v>12000</v>
@@ -9678,7 +9678,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G321" t="n">
-        <v>1.12983453273773</v>
+        <v>1.12983465194702</v>
       </c>
       <c r="H321" t="n">
         <v>24000</v>
@@ -9852,7 +9852,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G327" t="n">
-        <v>1.05866396427155</v>
+        <v>1.05866384506226</v>
       </c>
       <c r="H327" t="n">
         <v>4500</v>
@@ -9881,7 +9881,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>1.05866396427155</v>
+        <v>1.05866384506226</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G334" t="n">
-        <v>1.12093830108643</v>
+        <v>1.12093818187714</v>
       </c>
       <c r="H334" t="n">
         <v>63000</v>
@@ -10084,7 +10084,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G335" t="n">
-        <v>1.12983453273773</v>
+        <v>1.12983465194702</v>
       </c>
       <c r="H335" t="n">
         <v>57000</v>
@@ -10113,7 +10113,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>1.09424936771393</v>
+        <v>1.09424912929535</v>
       </c>
       <c r="H336" t="n">
         <v>36000</v>
@@ -10142,7 +10142,7 @@
         <v>1.25</v>
       </c>
       <c r="G337" t="n">
-        <v>1.11204195022583</v>
+        <v>1.11204183101654</v>
       </c>
       <c r="H337" t="n">
         <v>22500</v>
@@ -10171,7 +10171,7 @@
         <v>1.25</v>
       </c>
       <c r="G338" t="n">
-        <v>1.11204195022583</v>
+        <v>1.11204183101654</v>
       </c>
       <c r="H338" t="n">
         <v>4500</v>
@@ -10229,7 +10229,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G340" t="n">
-        <v>1.09424936771393</v>
+        <v>1.09424912929535</v>
       </c>
       <c r="H340" t="n">
         <v>13500</v>
@@ -10258,7 +10258,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G341" t="n">
-        <v>1.09424936771393</v>
+        <v>1.09424912929535</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -10432,7 +10432,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G347" t="n">
-        <v>1.02307856082916</v>
+        <v>1.02307868003845</v>
       </c>
       <c r="H347" t="n">
         <v>19500</v>
@@ -10490,7 +10490,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G349" t="n">
-        <v>0.996389508247375</v>
+        <v>0.99638956785202</v>
       </c>
       <c r="H349" t="n">
         <v>24000</v>
@@ -10519,7 +10519,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G350" t="n">
-        <v>0.996389508247375</v>
+        <v>0.99638956785202</v>
       </c>
       <c r="H350" t="n">
         <v>3000</v>
@@ -10548,7 +10548,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G351" t="n">
-        <v>0.996389508247375</v>
+        <v>0.99638956785202</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -10577,7 +10577,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G352" t="n">
-        <v>0.996389508247375</v>
+        <v>0.99638956785202</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10606,7 +10606,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G353" t="n">
-        <v>1.02307856082916</v>
+        <v>1.02307868003845</v>
       </c>
       <c r="H353" t="n">
         <v>4500</v>
@@ -10635,7 +10635,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G354" t="n">
-        <v>1.02307856082916</v>
+        <v>1.02307868003845</v>
       </c>
       <c r="H354" t="n">
         <v>1500</v>
@@ -10664,7 +10664,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>1.05866396427155</v>
+        <v>1.05866384506226</v>
       </c>
       <c r="H355" t="n">
         <v>7500</v>
@@ -10693,7 +10693,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G356" t="n">
-        <v>1.05866396427155</v>
+        <v>1.05866384506226</v>
       </c>
       <c r="H356" t="n">
         <v>9000</v>
@@ -10896,7 +10896,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G363" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H363" t="n">
         <v>22500</v>
@@ -12317,7 +12317,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G412" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H412" t="n">
         <v>1500</v>
@@ -12491,7 +12491,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G418" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H418" t="n">
         <v>3000</v>
@@ -12520,7 +12520,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G419" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G420" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G421" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H421" t="n">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G422" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H422" t="n">
         <v>3000</v>
@@ -12636,7 +12636,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G423" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H423" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G424" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H424" t="n">
         <v>0</v>
@@ -12694,7 +12694,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G425" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G442" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H442" t="n">
         <v>3000</v>
@@ -13216,7 +13216,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G443" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G448" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H448" t="n">
         <v>1500</v>
@@ -13390,7 +13390,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G449" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H449" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G463" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H463" t="n">
         <v>6000</v>
@@ -13825,7 +13825,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G464" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H464" t="n">
         <v>1500</v>
@@ -13854,7 +13854,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G465" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H465" t="n">
         <v>6000</v>
@@ -13883,7 +13883,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G466" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H466" t="n">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G467" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H467" t="n">
         <v>1500</v>
@@ -13941,7 +13941,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G468" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H468" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G496" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H496" t="n">
         <v>6000</v>
@@ -14782,7 +14782,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G497" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H497" t="n">
         <v>0</v>
@@ -14811,7 +14811,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G498" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H498" t="n">
         <v>6000</v>
@@ -14840,7 +14840,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G499" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H499" t="n">
         <v>1500</v>
@@ -14869,7 +14869,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G500" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G518" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H518" t="n">
         <v>3000</v>
@@ -15420,7 +15420,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G519" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H519" t="n">
         <v>0</v>
@@ -15623,7 +15623,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G526" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H526" t="n">
         <v>24000</v>
@@ -15652,7 +15652,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G527" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H527" t="n">
         <v>18000</v>
@@ -16696,7 +16696,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G563" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H563" t="n">
         <v>10500</v>
@@ -16725,7 +16725,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G564" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H564" t="n">
         <v>9000</v>
@@ -16754,7 +16754,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G565" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H565" t="n">
         <v>0</v>
@@ -16783,7 +16783,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G566" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -16812,7 +16812,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G567" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G568" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H568" t="n">
         <v>4500</v>
@@ -16870,7 +16870,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G569" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H569" t="n">
         <v>0</v>
@@ -16899,7 +16899,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G570" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H570" t="n">
         <v>1500</v>
@@ -16928,7 +16928,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G571" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G572" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H572" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G573" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H573" t="n">
         <v>0</v>
@@ -17015,7 +17015,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G574" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H574" t="n">
         <v>0</v>
@@ -17392,7 +17392,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G587" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H587" t="n">
         <v>1500</v>
@@ -17421,7 +17421,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G588" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H588" t="n">
         <v>0</v>
@@ -17450,7 +17450,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G589" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -17479,7 +17479,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G590" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H590" t="n">
         <v>12000</v>
@@ -17508,7 +17508,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G591" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H591" t="n">
         <v>1500</v>
@@ -17537,7 +17537,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G592" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H592" t="n">
         <v>1500</v>
@@ -17566,7 +17566,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G593" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G594" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H594" t="n">
         <v>3000</v>
@@ -17624,7 +17624,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -17740,7 +17740,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G599" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H599" t="n">
         <v>9000</v>
@@ -17769,7 +17769,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G600" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H600" t="n">
         <v>1500</v>
@@ -28766,6 +28766,35 @@
         <v>3000</v>
       </c>
       <c r="I979" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="s">
+        <v>9</v>
+      </c>
+      <c r="B980" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C980" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="D980" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="E980" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="F980" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="G980" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="H980" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I980" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SAC.MI.xlsx
+++ b/data/SAC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.02749991416931</v>
       </c>
       <c r="G2" t="n">
-        <v>1.69863855838776</v>
+        <v>1.69863843917847</v>
       </c>
       <c r="H2" t="n">
         <v>193500</v>
@@ -485,7 +485,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G4" t="n">
-        <v>1.52479529380798</v>
+        <v>1.52479517459869</v>
       </c>
       <c r="H4" t="n">
         <v>36000</v>
@@ -514,7 +514,7 @@
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>1.67559909820557</v>
+        <v>1.67559897899628</v>
       </c>
       <c r="H5" t="n">
         <v>51000</v>
@@ -543,7 +543,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G6" t="n">
-        <v>1.75100111961365</v>
+        <v>1.75100088119507</v>
       </c>
       <c r="H6" t="n">
         <v>144000</v>
@@ -572,7 +572,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8180251121521</v>
+        <v>1.81802499294281</v>
       </c>
       <c r="H7" t="n">
         <v>87000</v>
@@ -601,7 +601,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G8" t="n">
-        <v>1.82640302181244</v>
+        <v>1.82640314102173</v>
       </c>
       <c r="H8" t="n">
         <v>58500</v>
@@ -630,7 +630,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G9" t="n">
-        <v>1.75519025325775</v>
+        <v>1.75519013404846</v>
       </c>
       <c r="H9" t="n">
         <v>57000</v>
@@ -688,7 +688,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7091109752655</v>
+        <v>1.70911109447479</v>
       </c>
       <c r="H11" t="n">
         <v>18000</v>
@@ -717,7 +717,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7091109752655</v>
+        <v>1.70911109447479</v>
       </c>
       <c r="H12" t="n">
         <v>3000</v>
@@ -804,7 +804,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G15" t="n">
-        <v>1.69235515594482</v>
+        <v>1.69235503673553</v>
       </c>
       <c r="H15" t="n">
         <v>15000</v>
@@ -862,7 +862,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G17" t="n">
-        <v>1.69235515594482</v>
+        <v>1.69235503673553</v>
       </c>
       <c r="H17" t="n">
         <v>12000</v>
@@ -949,7 +949,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G20" t="n">
-        <v>1.59852159023285</v>
+        <v>1.59852147102356</v>
       </c>
       <c r="H20" t="n">
         <v>16500</v>
@@ -978,7 +978,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G21" t="n">
-        <v>1.57841408252716</v>
+        <v>1.57841432094574</v>
       </c>
       <c r="H21" t="n">
         <v>6000</v>
@@ -1036,7 +1036,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G23" t="n">
-        <v>1.60187268257141</v>
+        <v>1.6018728017807</v>
       </c>
       <c r="H23" t="n">
         <v>13500</v>
@@ -1065,7 +1065,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G24" t="n">
-        <v>1.60187268257141</v>
+        <v>1.6018728017807</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G25" t="n">
-        <v>1.62700688838959</v>
+        <v>1.6270067691803</v>
       </c>
       <c r="H25" t="n">
         <v>12000</v>
@@ -1123,7 +1123,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G26" t="n">
-        <v>1.62030434608459</v>
+        <v>1.62030446529388</v>
       </c>
       <c r="H26" t="n">
         <v>9000</v>
@@ -1152,7 +1152,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G27" t="n">
-        <v>1.62030434608459</v>
+        <v>1.62030446529388</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1181,7 +1181,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G28" t="n">
-        <v>1.59852159023285</v>
+        <v>1.59852147102356</v>
       </c>
       <c r="H28" t="n">
         <v>7500</v>
@@ -1210,7 +1210,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G29" t="n">
-        <v>1.54992926120758</v>
+        <v>1.54992914199829</v>
       </c>
       <c r="H29" t="n">
         <v>25500</v>
@@ -1239,7 +1239,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G30" t="n">
-        <v>1.57841408252716</v>
+        <v>1.57841432094574</v>
       </c>
       <c r="H30" t="n">
         <v>24000</v>
@@ -1326,7 +1326,7 @@
         <v>1.75800001621246</v>
       </c>
       <c r="G33" t="n">
-        <v>1.47285163402557</v>
+        <v>1.47285151481628</v>
       </c>
       <c r="H33" t="n">
         <v>1500</v>
@@ -1355,7 +1355,7 @@
         <v>1.75800001621246</v>
       </c>
       <c r="G34" t="n">
-        <v>1.47285163402557</v>
+        <v>1.47285151481628</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G35" t="n">
-        <v>1.41169226169586</v>
+        <v>1.41169214248657</v>
       </c>
       <c r="H35" t="n">
         <v>12000</v>
@@ -1413,7 +1413,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G36" t="n">
-        <v>1.38655829429626</v>
+        <v>1.38655817508698</v>
       </c>
       <c r="H36" t="n">
         <v>3000</v>
@@ -1442,7 +1442,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G37" t="n">
-        <v>1.34885740280151</v>
+        <v>1.34885728359222</v>
       </c>
       <c r="H37" t="n">
         <v>7500</v>
@@ -1471,7 +1471,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G38" t="n">
-        <v>1.315345287323</v>
+        <v>1.31534540653229</v>
       </c>
       <c r="H38" t="n">
         <v>12000</v>
@@ -1645,7 +1645,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G44" t="n">
-        <v>1.20643150806427</v>
+        <v>1.20643138885498</v>
       </c>
       <c r="H44" t="n">
         <v>7500</v>
@@ -1674,7 +1674,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G45" t="n">
-        <v>1.21062052249908</v>
+        <v>1.21062028408051</v>
       </c>
       <c r="H45" t="n">
         <v>100500</v>
@@ -1761,7 +1761,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G48" t="n">
-        <v>1.26926636695862</v>
+        <v>1.26926624774933</v>
       </c>
       <c r="H48" t="n">
         <v>27000</v>
@@ -1790,7 +1790,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G49" t="n">
-        <v>1.30277812480927</v>
+        <v>1.30277824401855</v>
       </c>
       <c r="H49" t="n">
         <v>48000</v>
@@ -1819,7 +1819,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G50" t="n">
-        <v>1.30277812480927</v>
+        <v>1.30277824401855</v>
       </c>
       <c r="H50" t="n">
         <v>54000</v>
@@ -1877,7 +1877,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G52" t="n">
-        <v>1.28183317184448</v>
+        <v>1.28183329105377</v>
       </c>
       <c r="H52" t="n">
         <v>28500</v>
@@ -2051,7 +2051,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>1.23994338512421</v>
+        <v>1.23994326591492</v>
       </c>
       <c r="H58" t="n">
         <v>7500</v>
@@ -2167,7 +2167,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G62" t="n">
-        <v>1.23994338512421</v>
+        <v>1.23994326591492</v>
       </c>
       <c r="H62" t="n">
         <v>10500</v>
@@ -2196,7 +2196,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G63" t="n">
-        <v>1.2650773525238</v>
+        <v>1.26507723331451</v>
       </c>
       <c r="H63" t="n">
         <v>15000</v>
@@ -2225,7 +2225,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G64" t="n">
-        <v>1.27764427661896</v>
+        <v>1.27764439582825</v>
       </c>
       <c r="H64" t="n">
         <v>4500</v>
@@ -2254,7 +2254,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G65" t="n">
-        <v>1.26926636695862</v>
+        <v>1.26926624774933</v>
       </c>
       <c r="H65" t="n">
         <v>1500</v>
@@ -2283,7 +2283,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G66" t="n">
-        <v>1.26088833808899</v>
+        <v>1.26088845729828</v>
       </c>
       <c r="H66" t="n">
         <v>21000</v>
@@ -2312,7 +2312,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G67" t="n">
-        <v>1.23994338512421</v>
+        <v>1.23994326591492</v>
       </c>
       <c r="H67" t="n">
         <v>16500</v>
@@ -2428,7 +2428,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G71" t="n">
-        <v>1.28183317184448</v>
+        <v>1.28183329105377</v>
       </c>
       <c r="H71" t="n">
         <v>46500</v>
@@ -2486,7 +2486,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G73" t="n">
-        <v>1.30277812480927</v>
+        <v>1.30277824401855</v>
       </c>
       <c r="H73" t="n">
         <v>1500</v>
@@ -2660,7 +2660,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G79" t="n">
-        <v>1.27764427661896</v>
+        <v>1.27764439582825</v>
       </c>
       <c r="H79" t="n">
         <v>12000</v>
@@ -2689,7 +2689,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G80" t="n">
-        <v>1.27764427661896</v>
+        <v>1.27764439582825</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G81" t="n">
-        <v>1.29858934879303</v>
+        <v>1.29858922958374</v>
       </c>
       <c r="H81" t="n">
         <v>33000</v>
@@ -2747,7 +2747,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G82" t="n">
-        <v>1.34885740280151</v>
+        <v>1.34885728359222</v>
       </c>
       <c r="H82" t="n">
         <v>78000</v>
@@ -2805,7 +2805,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G84" t="n">
-        <v>1.35723531246185</v>
+        <v>1.35723519325256</v>
       </c>
       <c r="H84" t="n">
         <v>39000</v>
@@ -2834,7 +2834,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G85" t="n">
-        <v>1.32791244983673</v>
+        <v>1.32791221141815</v>
       </c>
       <c r="H85" t="n">
         <v>19500</v>
@@ -2892,7 +2892,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G87" t="n">
-        <v>1.30696713924408</v>
+        <v>1.30696725845337</v>
       </c>
       <c r="H87" t="n">
         <v>13500</v>
@@ -2950,7 +2950,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G89" t="n">
-        <v>1.26088833808899</v>
+        <v>1.26088845729828</v>
       </c>
       <c r="H89" t="n">
         <v>6000</v>
@@ -2979,7 +2979,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G90" t="n">
-        <v>1.26088833808899</v>
+        <v>1.26088845729828</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G91" t="n">
-        <v>1.26088833808899</v>
+        <v>1.26088845729828</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G92" t="n">
-        <v>1.26088833808899</v>
+        <v>1.26088845729828</v>
       </c>
       <c r="H92" t="n">
         <v>1500</v>
@@ -3066,7 +3066,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G93" t="n">
-        <v>1.26088833808899</v>
+        <v>1.26088845729828</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G96" t="n">
-        <v>1.26926636695862</v>
+        <v>1.26926624774933</v>
       </c>
       <c r="H96" t="n">
         <v>1500</v>
@@ -3182,7 +3182,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G97" t="n">
-        <v>1.26926636695862</v>
+        <v>1.26926624774933</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>1.5</v>
       </c>
       <c r="G99" t="n">
-        <v>1.2922580242157</v>
+        <v>1.29225826263428</v>
       </c>
       <c r="H99" t="n">
         <v>4500</v>
@@ -3298,7 +3298,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G101" t="n">
-        <v>1.21903014183044</v>
+        <v>1.21903002262115</v>
       </c>
       <c r="H101" t="n">
         <v>22500</v>
@@ -3385,7 +3385,7 @@
         <v>1.375</v>
       </c>
       <c r="G104" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H104" t="n">
         <v>9000</v>
@@ -3443,7 +3443,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G106" t="n">
-        <v>1.14149463176727</v>
+        <v>1.14149475097656</v>
       </c>
       <c r="H106" t="n">
         <v>4500</v>
@@ -3472,7 +3472,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G107" t="n">
-        <v>1.14149463176727</v>
+        <v>1.14149475097656</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G108" t="n">
-        <v>1.12857210636139</v>
+        <v>1.1285719871521</v>
       </c>
       <c r="H108" t="n">
         <v>1500</v>
@@ -3530,7 +3530,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G109" t="n">
-        <v>1.12857210636139</v>
+        <v>1.1285719871521</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G110" t="n">
-        <v>1.12857210636139</v>
+        <v>1.1285719871521</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G111" t="n">
-        <v>1.12857210636139</v>
+        <v>1.1285719871521</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G112" t="n">
-        <v>1.12857210636139</v>
+        <v>1.1285719871521</v>
       </c>
       <c r="H112" t="n">
         <v>3000</v>
@@ -3646,7 +3646,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G113" t="n">
-        <v>1.21041512489319</v>
+        <v>1.2104150056839</v>
       </c>
       <c r="H113" t="n">
         <v>9000</v>
@@ -3675,7 +3675,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G114" t="n">
-        <v>1.21903014183044</v>
+        <v>1.21903002262115</v>
       </c>
       <c r="H114" t="n">
         <v>13500</v>
@@ -3704,7 +3704,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G115" t="n">
-        <v>1.19318497180939</v>
+        <v>1.1931848526001</v>
       </c>
       <c r="H115" t="n">
         <v>4500</v>
@@ -3733,7 +3733,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G116" t="n">
-        <v>1.19318497180939</v>
+        <v>1.1931848526001</v>
       </c>
       <c r="H116" t="n">
         <v>1500</v>
@@ -3762,7 +3762,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G117" t="n">
-        <v>1.19318497180939</v>
+        <v>1.1931848526001</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G122" t="n">
-        <v>1.21041512489319</v>
+        <v>1.2104150056839</v>
       </c>
       <c r="H122" t="n">
         <v>1500</v>
@@ -3936,7 +3936,7 @@
         <v>1.375</v>
       </c>
       <c r="G123" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H123" t="n">
         <v>3000</v>
@@ -3965,7 +3965,7 @@
         <v>1.375</v>
       </c>
       <c r="G124" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G125" t="n">
-        <v>1.18026256561279</v>
+        <v>1.18026232719421</v>
       </c>
       <c r="H125" t="n">
         <v>3000</v>
@@ -4052,7 +4052,7 @@
         <v>1.375</v>
       </c>
       <c r="G127" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H127" t="n">
         <v>1500</v>
@@ -4081,7 +4081,7 @@
         <v>1.375</v>
       </c>
       <c r="G128" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>1.375</v>
       </c>
       <c r="G129" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H129" t="n">
         <v>3000</v>
@@ -4139,7 +4139,7 @@
         <v>1.375</v>
       </c>
       <c r="G130" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>1.375</v>
       </c>
       <c r="G131" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -4197,7 +4197,7 @@
         <v>1.375</v>
       </c>
       <c r="G132" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H132" t="n">
         <v>1500</v>
@@ -4226,7 +4226,7 @@
         <v>1.375</v>
       </c>
       <c r="G133" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>1.375</v>
       </c>
       <c r="G134" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>1.375</v>
       </c>
       <c r="G135" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>1.375</v>
       </c>
       <c r="G136" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>1.375</v>
       </c>
       <c r="G137" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H137" t="n">
         <v>1500</v>
@@ -4371,7 +4371,7 @@
         <v>1.375</v>
       </c>
       <c r="G138" t="n">
-        <v>1.18457007408142</v>
+        <v>1.18456983566284</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G139" t="n">
-        <v>1.20610761642456</v>
+        <v>1.20610737800598</v>
       </c>
       <c r="H139" t="n">
         <v>9000</v>
@@ -4429,7 +4429,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G140" t="n">
-        <v>1.20610761642456</v>
+        <v>1.20610737800598</v>
       </c>
       <c r="H140" t="n">
         <v>1500</v>
@@ -4458,7 +4458,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G141" t="n">
-        <v>1.20610761642456</v>
+        <v>1.20610737800598</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G142" t="n">
-        <v>1.20610761642456</v>
+        <v>1.20610737800598</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G143" t="n">
-        <v>1.20610761642456</v>
+        <v>1.20610737800598</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G144" t="n">
-        <v>1.20610761642456</v>
+        <v>1.20610737800598</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G145" t="n">
-        <v>1.20610761642456</v>
+        <v>1.20610737800598</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G147" t="n">
-        <v>1.24056792259216</v>
+        <v>1.24056768417358</v>
       </c>
       <c r="H147" t="n">
         <v>18000</v>
@@ -4661,7 +4661,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G148" t="n">
-        <v>1.23195266723633</v>
+        <v>1.23195254802704</v>
       </c>
       <c r="H148" t="n">
         <v>3000</v>
@@ -4690,7 +4690,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G149" t="n">
-        <v>1.23195266723633</v>
+        <v>1.23195254802704</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G150" t="n">
-        <v>1.23195266723633</v>
+        <v>1.23195254802704</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G152" t="n">
-        <v>1.17595493793488</v>
+        <v>1.17595481872559</v>
       </c>
       <c r="H152" t="n">
         <v>18000</v>
@@ -5038,7 +5038,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G161" t="n">
-        <v>1.18026256561279</v>
+        <v>1.18026232719421</v>
       </c>
       <c r="H161" t="n">
         <v>4500</v>
@@ -5328,7 +5328,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G171" t="n">
-        <v>1.09411180019379</v>
+        <v>1.09411191940308</v>
       </c>
       <c r="H171" t="n">
         <v>19500</v>
@@ -5357,7 +5357,7 @@
         <v>1.25</v>
       </c>
       <c r="G172" t="n">
-        <v>1.07688176631927</v>
+        <v>1.07688188552856</v>
       </c>
       <c r="H172" t="n">
         <v>4500</v>
@@ -5386,7 +5386,7 @@
         <v>1.25</v>
       </c>
       <c r="G173" t="n">
-        <v>1.07688176631927</v>
+        <v>1.07688188552856</v>
       </c>
       <c r="H173" t="n">
         <v>33000</v>
@@ -5415,7 +5415,7 @@
         <v>1.25</v>
       </c>
       <c r="G174" t="n">
-        <v>1.07688176631927</v>
+        <v>1.07688188552856</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>1.25</v>
       </c>
       <c r="G175" t="n">
-        <v>1.07688176631927</v>
+        <v>1.07688188552856</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>1.25</v>
       </c>
       <c r="G176" t="n">
-        <v>1.07688176631927</v>
+        <v>1.07688188552856</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>1.25</v>
       </c>
       <c r="G177" t="n">
-        <v>1.07688176631927</v>
+        <v>1.07688188552856</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G178" t="n">
-        <v>1.09841930866241</v>
+        <v>1.0984194278717</v>
       </c>
       <c r="H178" t="n">
         <v>16500</v>
@@ -5560,7 +5560,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G179" t="n">
-        <v>1.08549678325653</v>
+        <v>1.08549690246582</v>
       </c>
       <c r="H179" t="n">
         <v>7500</v>
@@ -5589,7 +5589,7 @@
         <v>1.25</v>
       </c>
       <c r="G180" t="n">
-        <v>1.07688176631927</v>
+        <v>1.07688188552856</v>
       </c>
       <c r="H180" t="n">
         <v>10500</v>
@@ -5618,7 +5618,7 @@
         <v>1.25</v>
       </c>
       <c r="G181" t="n">
-        <v>1.07688176631927</v>
+        <v>1.07688188552856</v>
       </c>
       <c r="H181" t="n">
         <v>1500</v>
@@ -5821,7 +5821,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G188" t="n">
-        <v>0.999346256256104</v>
+        <v>0.999346315860748</v>
       </c>
       <c r="H188" t="n">
         <v>4500</v>
@@ -5850,7 +5850,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G189" t="n">
-        <v>0.930425941944122</v>
+        <v>0.930425882339478</v>
       </c>
       <c r="H189" t="n">
         <v>45000</v>
@@ -5995,7 +5995,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G194" t="n">
-        <v>0.900273203849792</v>
+        <v>0.900273144245148</v>
       </c>
       <c r="H194" t="n">
         <v>9000</v>
@@ -6024,7 +6024,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G195" t="n">
-        <v>0.900273203849792</v>
+        <v>0.900273144245148</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G196" t="n">
-        <v>0.900273203849792</v>
+        <v>0.900273144245148</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G197" t="n">
-        <v>0.887350559234619</v>
+        <v>0.887350499629974</v>
       </c>
       <c r="H197" t="n">
         <v>3000</v>
@@ -6111,7 +6111,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G198" t="n">
-        <v>0.887350559234619</v>
+        <v>0.887350499629974</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>0.895965576171875</v>
+        <v>0.89596551656723</v>
       </c>
       <c r="H200" t="n">
         <v>6000</v>
@@ -6227,7 +6227,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G202" t="n">
-        <v>0.887350559234619</v>
+        <v>0.887350499629974</v>
       </c>
       <c r="H202" t="n">
         <v>7500</v>
@@ -6314,7 +6314,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G205" t="n">
-        <v>0.849444329738617</v>
+        <v>0.849444389343262</v>
       </c>
       <c r="H205" t="n">
         <v>9000</v>
@@ -6343,7 +6343,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G206" t="n">
-        <v>0.86581289768219</v>
+        <v>0.865812957286835</v>
       </c>
       <c r="H206" t="n">
         <v>3000</v>
@@ -6430,7 +6430,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G209" t="n">
-        <v>0.891658067703247</v>
+        <v>0.891658008098602</v>
       </c>
       <c r="H209" t="n">
         <v>3000</v>
@@ -6459,7 +6459,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G210" t="n">
-        <v>0.908888101577759</v>
+        <v>0.908888220787048</v>
       </c>
       <c r="H210" t="n">
         <v>1500</v>
@@ -6488,7 +6488,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G211" t="n">
-        <v>0.908888101577759</v>
+        <v>0.908888220787048</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G212" t="n">
-        <v>0.908888101577759</v>
+        <v>0.908888220787048</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G213" t="n">
-        <v>0.908888101577759</v>
+        <v>0.908888220787048</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G229" t="n">
-        <v>0.86581289768219</v>
+        <v>0.865812957286835</v>
       </c>
       <c r="H229" t="n">
         <v>19500</v>
@@ -7039,7 +7039,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G230" t="n">
-        <v>0.86581289768219</v>
+        <v>0.865812957286835</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G233" t="n">
-        <v>0.747786581516266</v>
+        <v>0.747786700725555</v>
       </c>
       <c r="H233" t="n">
         <v>31500</v>
@@ -7242,7 +7242,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G237" t="n">
-        <v>0.671974122524261</v>
+        <v>0.671974182128906</v>
       </c>
       <c r="H237" t="n">
         <v>51000</v>
@@ -7271,7 +7271,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G238" t="n">
-        <v>0.706434428691864</v>
+        <v>0.706434369087219</v>
       </c>
       <c r="H238" t="n">
         <v>63000</v>
@@ -7358,7 +7358,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G241" t="n">
-        <v>0.739171624183655</v>
+        <v>0.7391716837883</v>
       </c>
       <c r="H241" t="n">
         <v>12000</v>
@@ -7387,7 +7387,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G242" t="n">
-        <v>0.792584955692291</v>
+        <v>0.792585015296936</v>
       </c>
       <c r="H242" t="n">
         <v>75000</v>
@@ -7416,7 +7416,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G243" t="n">
-        <v>0.84772139787674</v>
+        <v>0.847721338272095</v>
       </c>
       <c r="H243" t="n">
         <v>48000</v>
@@ -7445,7 +7445,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G244" t="n">
-        <v>0.797754049301147</v>
+        <v>0.797753989696503</v>
       </c>
       <c r="H244" t="n">
         <v>63000</v>
@@ -7532,7 +7532,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G247" t="n">
-        <v>0.851167261600494</v>
+        <v>0.851167321205139</v>
       </c>
       <c r="H247" t="n">
         <v>4500</v>
@@ -7561,7 +7561,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G248" t="n">
-        <v>0.895965576171875</v>
+        <v>0.89596551656723</v>
       </c>
       <c r="H248" t="n">
         <v>25500</v>
@@ -7590,7 +7590,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G249" t="n">
-        <v>0.990731179714203</v>
+        <v>0.990731298923492</v>
       </c>
       <c r="H249" t="n">
         <v>90000</v>
@@ -7648,7 +7648,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G251" t="n">
-        <v>1.14149463176727</v>
+        <v>1.14149475097656</v>
       </c>
       <c r="H251" t="n">
         <v>184500</v>
@@ -7677,7 +7677,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G252" t="n">
-        <v>1.07257413864136</v>
+        <v>1.07257437705994</v>
       </c>
       <c r="H252" t="n">
         <v>73500</v>
@@ -7706,7 +7706,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G253" t="n">
-        <v>1.01226890087128</v>
+        <v>1.01226878166199</v>
       </c>
       <c r="H253" t="n">
         <v>136500</v>
@@ -7735,7 +7735,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G254" t="n">
-        <v>1.03380644321442</v>
+        <v>1.03380656242371</v>
       </c>
       <c r="H254" t="n">
         <v>37500</v>
@@ -7822,7 +7822,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G257" t="n">
-        <v>1.07257413864136</v>
+        <v>1.07257437705994</v>
       </c>
       <c r="H257" t="n">
         <v>45000</v>
@@ -7880,7 +7880,7 @@
         <v>1.25</v>
       </c>
       <c r="G259" t="n">
-        <v>1.07688176631927</v>
+        <v>1.07688188552856</v>
       </c>
       <c r="H259" t="n">
         <v>4500</v>
@@ -7909,7 +7909,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G260" t="n">
-        <v>1.09841930866241</v>
+        <v>1.0984194278717</v>
       </c>
       <c r="H260" t="n">
         <v>52500</v>
@@ -7967,7 +7967,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G262" t="n">
-        <v>1.09841930866241</v>
+        <v>1.0984194278717</v>
       </c>
       <c r="H262" t="n">
         <v>36000</v>
@@ -7996,7 +7996,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G263" t="n">
-        <v>1.1113418340683</v>
+        <v>1.11134195327759</v>
       </c>
       <c r="H263" t="n">
         <v>24000</v>
@@ -8112,7 +8112,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G267" t="n">
-        <v>1.1113418340683</v>
+        <v>1.11134195327759</v>
       </c>
       <c r="H267" t="n">
         <v>69000</v>
@@ -8141,7 +8141,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G268" t="n">
-        <v>1.1113418340683</v>
+        <v>1.11134195327759</v>
       </c>
       <c r="H268" t="n">
         <v>7500</v>
@@ -8170,7 +8170,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G269" t="n">
-        <v>1.1113418340683</v>
+        <v>1.11134195327759</v>
       </c>
       <c r="H269" t="n">
         <v>4500</v>
@@ -8199,7 +8199,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G270" t="n">
-        <v>1.11995708942413</v>
+        <v>1.11995697021484</v>
       </c>
       <c r="H270" t="n">
         <v>7500</v>
@@ -8228,7 +8228,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G271" t="n">
-        <v>1.1113418340683</v>
+        <v>1.11134195327759</v>
       </c>
       <c r="H271" t="n">
         <v>63000</v>
@@ -8286,7 +8286,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G273" t="n">
-        <v>1.13718712329865</v>
+        <v>1.13718724250793</v>
       </c>
       <c r="H273" t="n">
         <v>69000</v>
@@ -8402,7 +8402,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G277" t="n">
-        <v>1.12983465194702</v>
+        <v>1.12983453273773</v>
       </c>
       <c r="H277" t="n">
         <v>16500</v>
@@ -8431,7 +8431,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>1.12983465194702</v>
+        <v>1.12983453273773</v>
       </c>
       <c r="H278" t="n">
         <v>6000</v>
@@ -8460,7 +8460,7 @@
         <v>1.25</v>
       </c>
       <c r="G279" t="n">
-        <v>1.11204183101654</v>
+        <v>1.11204195022583</v>
       </c>
       <c r="H279" t="n">
         <v>12000</v>
@@ -8518,7 +8518,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G281" t="n">
-        <v>1.12983465194702</v>
+        <v>1.12983453273773</v>
       </c>
       <c r="H281" t="n">
         <v>6000</v>
@@ -8692,7 +8692,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G287" t="n">
-        <v>1.01863026618958</v>
+        <v>1.01863038539886</v>
       </c>
       <c r="H287" t="n">
         <v>19500</v>
@@ -8721,7 +8721,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G288" t="n">
-        <v>1.01863026618958</v>
+        <v>1.01863038539886</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G289" t="n">
-        <v>0.99638956785202</v>
+        <v>0.996389508247375</v>
       </c>
       <c r="H289" t="n">
         <v>12000</v>
@@ -8779,7 +8779,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G290" t="n">
-        <v>1.02307868003845</v>
+        <v>1.02307856082916</v>
       </c>
       <c r="H290" t="n">
         <v>3000</v>
@@ -8808,7 +8808,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G291" t="n">
-        <v>1.02307868003845</v>
+        <v>1.02307856082916</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G292" t="n">
-        <v>1.00528597831726</v>
+        <v>1.00528585910797</v>
       </c>
       <c r="H292" t="n">
         <v>10500</v>
@@ -8924,7 +8924,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G295" t="n">
-        <v>1.00528597831726</v>
+        <v>1.00528585910797</v>
       </c>
       <c r="H295" t="n">
         <v>27000</v>
@@ -9069,7 +9069,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G300" t="n">
-        <v>1.02307868003845</v>
+        <v>1.02307856082916</v>
       </c>
       <c r="H300" t="n">
         <v>10500</v>
@@ -9214,7 +9214,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G305" t="n">
-        <v>1.00528597831726</v>
+        <v>1.00528585910797</v>
       </c>
       <c r="H305" t="n">
         <v>15000</v>
@@ -9243,7 +9243,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G306" t="n">
-        <v>1.00528597831726</v>
+        <v>1.00528585910797</v>
       </c>
       <c r="H306" t="n">
         <v>3000</v>
@@ -9272,7 +9272,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G307" t="n">
-        <v>1.00528597831726</v>
+        <v>1.00528585910797</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G309" t="n">
-        <v>0.991941392421722</v>
+        <v>0.991941332817078</v>
       </c>
       <c r="H309" t="n">
         <v>1500</v>
@@ -9417,7 +9417,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G312" t="n">
-        <v>0.99638956785202</v>
+        <v>0.996389508247375</v>
       </c>
       <c r="H312" t="n">
         <v>1500</v>
@@ -9446,7 +9446,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G313" t="n">
-        <v>0.991941392421722</v>
+        <v>0.991941332817078</v>
       </c>
       <c r="H313" t="n">
         <v>3000</v>
@@ -9475,7 +9475,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G314" t="n">
-        <v>0.991941392421722</v>
+        <v>0.991941332817078</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G318" t="n">
-        <v>0.920770645141602</v>
+        <v>0.920770585536957</v>
       </c>
       <c r="H318" t="n">
         <v>12000</v>
@@ -9678,7 +9678,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G321" t="n">
-        <v>1.12983465194702</v>
+        <v>1.12983453273773</v>
       </c>
       <c r="H321" t="n">
         <v>24000</v>
@@ -9852,7 +9852,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G327" t="n">
-        <v>1.05866384506226</v>
+        <v>1.05866396427155</v>
       </c>
       <c r="H327" t="n">
         <v>4500</v>
@@ -9881,7 +9881,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>1.05866384506226</v>
+        <v>1.05866396427155</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G334" t="n">
-        <v>1.12093818187714</v>
+        <v>1.12093830108643</v>
       </c>
       <c r="H334" t="n">
         <v>63000</v>
@@ -10084,7 +10084,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G335" t="n">
-        <v>1.12983465194702</v>
+        <v>1.12983453273773</v>
       </c>
       <c r="H335" t="n">
         <v>57000</v>
@@ -10113,7 +10113,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>1.09424912929535</v>
+        <v>1.09424936771393</v>
       </c>
       <c r="H336" t="n">
         <v>36000</v>
@@ -10142,7 +10142,7 @@
         <v>1.25</v>
       </c>
       <c r="G337" t="n">
-        <v>1.11204183101654</v>
+        <v>1.11204195022583</v>
       </c>
       <c r="H337" t="n">
         <v>22500</v>
@@ -10171,7 +10171,7 @@
         <v>1.25</v>
       </c>
       <c r="G338" t="n">
-        <v>1.11204183101654</v>
+        <v>1.11204195022583</v>
       </c>
       <c r="H338" t="n">
         <v>4500</v>
@@ -10229,7 +10229,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G340" t="n">
-        <v>1.09424912929535</v>
+        <v>1.09424936771393</v>
       </c>
       <c r="H340" t="n">
         <v>13500</v>
@@ -10258,7 +10258,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G341" t="n">
-        <v>1.09424912929535</v>
+        <v>1.09424936771393</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -10432,7 +10432,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G347" t="n">
-        <v>1.02307868003845</v>
+        <v>1.02307856082916</v>
       </c>
       <c r="H347" t="n">
         <v>19500</v>
@@ -10490,7 +10490,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G349" t="n">
-        <v>0.99638956785202</v>
+        <v>0.996389508247375</v>
       </c>
       <c r="H349" t="n">
         <v>24000</v>
@@ -10519,7 +10519,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G350" t="n">
-        <v>0.99638956785202</v>
+        <v>0.996389508247375</v>
       </c>
       <c r="H350" t="n">
         <v>3000</v>
@@ -10548,7 +10548,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G351" t="n">
-        <v>0.99638956785202</v>
+        <v>0.996389508247375</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -10577,7 +10577,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G352" t="n">
-        <v>0.99638956785202</v>
+        <v>0.996389508247375</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10606,7 +10606,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G353" t="n">
-        <v>1.02307868003845</v>
+        <v>1.02307856082916</v>
       </c>
       <c r="H353" t="n">
         <v>4500</v>
@@ -10635,7 +10635,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G354" t="n">
-        <v>1.02307868003845</v>
+        <v>1.02307856082916</v>
       </c>
       <c r="H354" t="n">
         <v>1500</v>
@@ -10664,7 +10664,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>1.05866384506226</v>
+        <v>1.05866396427155</v>
       </c>
       <c r="H355" t="n">
         <v>7500</v>
@@ -10693,7 +10693,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G356" t="n">
-        <v>1.05866384506226</v>
+        <v>1.05866396427155</v>
       </c>
       <c r="H356" t="n">
         <v>9000</v>
@@ -10896,7 +10896,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G363" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H363" t="n">
         <v>22500</v>
@@ -12317,7 +12317,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G412" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H412" t="n">
         <v>1500</v>
@@ -12491,7 +12491,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G418" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H418" t="n">
         <v>3000</v>
@@ -12520,7 +12520,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G419" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G420" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G421" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H421" t="n">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G422" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H422" t="n">
         <v>3000</v>
@@ -12636,7 +12636,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G423" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H423" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G424" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H424" t="n">
         <v>0</v>
@@ -12694,7 +12694,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G425" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G442" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H442" t="n">
         <v>3000</v>
@@ -13216,7 +13216,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G443" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G448" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H448" t="n">
         <v>1500</v>
@@ -13390,7 +13390,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G449" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H449" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G463" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H463" t="n">
         <v>6000</v>
@@ -13825,7 +13825,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G464" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H464" t="n">
         <v>1500</v>
@@ -13854,7 +13854,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G465" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H465" t="n">
         <v>6000</v>
@@ -13883,7 +13883,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G466" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H466" t="n">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G467" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H467" t="n">
         <v>1500</v>
@@ -13941,7 +13941,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G468" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H468" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G496" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H496" t="n">
         <v>6000</v>
@@ -14782,7 +14782,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G497" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H497" t="n">
         <v>0</v>
@@ -14811,7 +14811,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G498" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H498" t="n">
         <v>6000</v>
@@ -14840,7 +14840,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G499" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H499" t="n">
         <v>1500</v>
@@ -14869,7 +14869,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G500" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G518" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H518" t="n">
         <v>3000</v>
@@ -15420,7 +15420,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G519" t="n">
-        <v>1.03284287452698</v>
+        <v>1.03284275531769</v>
       </c>
       <c r="H519" t="n">
         <v>0</v>
@@ -15623,7 +15623,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G526" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H526" t="n">
         <v>24000</v>
@@ -15652,7 +15652,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G527" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H527" t="n">
         <v>18000</v>
@@ -16696,7 +16696,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G563" t="n">
-        <v>0.977511882781982</v>
+        <v>0.977511942386627</v>
       </c>
       <c r="H563" t="n">
         <v>10500</v>
@@ -16725,7 +16725,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G564" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H564" t="n">
         <v>9000</v>
@@ -16754,7 +16754,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G565" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H565" t="n">
         <v>0</v>
@@ -16783,7 +16783,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G566" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -16812,7 +16812,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G567" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G568" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H568" t="n">
         <v>4500</v>
@@ -16870,7 +16870,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G569" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H569" t="n">
         <v>0</v>
@@ -16899,7 +16899,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G570" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H570" t="n">
         <v>1500</v>
@@ -16928,7 +16928,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G571" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G572" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H572" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G573" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H573" t="n">
         <v>0</v>
@@ -17015,7 +17015,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G574" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H574" t="n">
         <v>0</v>
@@ -17392,7 +17392,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G587" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H587" t="n">
         <v>1500</v>
@@ -17421,7 +17421,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G588" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H588" t="n">
         <v>0</v>
@@ -17450,7 +17450,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G589" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -17479,7 +17479,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G590" t="n">
-        <v>0.977511882781982</v>
+        <v>0.977511942386627</v>
       </c>
       <c r="H590" t="n">
         <v>12000</v>
@@ -17508,7 +17508,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G591" t="n">
-        <v>0.986733734607697</v>
+        <v>0.986733853816986</v>
       </c>
       <c r="H591" t="n">
         <v>1500</v>
@@ -17537,7 +17537,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G592" t="n">
-        <v>0.977511882781982</v>
+        <v>0.977511942386627</v>
       </c>
       <c r="H592" t="n">
         <v>1500</v>
@@ -17566,7 +17566,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G593" t="n">
-        <v>0.977511882781982</v>
+        <v>0.977511942386627</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G594" t="n">
-        <v>0.977511882781982</v>
+        <v>0.977511942386627</v>
       </c>
       <c r="H594" t="n">
         <v>3000</v>
@@ -17624,7 +17624,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>0.977511882781982</v>
+        <v>0.977511942386627</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -17740,7 +17740,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G599" t="n">
-        <v>0.977511882781982</v>
+        <v>0.977511942386627</v>
       </c>
       <c r="H599" t="n">
         <v>9000</v>
@@ -17769,7 +17769,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G600" t="n">
-        <v>0.995955586433411</v>
+        <v>0.995955646038055</v>
       </c>
       <c r="H600" t="n">
         <v>1500</v>
@@ -28795,6 +28795,35 @@
         <v>3000</v>
       </c>
       <c r="I980" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="s">
+        <v>9</v>
+      </c>
+      <c r="B981" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C981" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="D981" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="E981" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="F981" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="G981" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="H981" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I981" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SAC.MI.xlsx
+++ b/data/SAC.MI.xlsx
@@ -514,7 +514,7 @@
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>1.67559897899628</v>
+        <v>1.67559909820557</v>
       </c>
       <c r="H5" t="n">
         <v>51000</v>
@@ -601,7 +601,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G8" t="n">
-        <v>1.82640314102173</v>
+        <v>1.82640302181244</v>
       </c>
       <c r="H8" t="n">
         <v>58500</v>
@@ -630,7 +630,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G9" t="n">
-        <v>1.75519013404846</v>
+        <v>1.75519001483917</v>
       </c>
       <c r="H9" t="n">
         <v>57000</v>
@@ -891,7 +891,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G18" t="n">
-        <v>1.61192631721497</v>
+        <v>1.61192643642426</v>
       </c>
       <c r="H18" t="n">
         <v>28500</v>
@@ -920,7 +920,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G19" t="n">
-        <v>1.59181904792786</v>
+        <v>1.59181916713715</v>
       </c>
       <c r="H19" t="n">
         <v>16500</v>
@@ -949,7 +949,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G20" t="n">
-        <v>1.59852147102356</v>
+        <v>1.59852159023285</v>
       </c>
       <c r="H20" t="n">
         <v>16500</v>
@@ -1007,7 +1007,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G22" t="n">
-        <v>1.60522389411926</v>
+        <v>1.60522401332855</v>
       </c>
       <c r="H22" t="n">
         <v>6000</v>
@@ -1181,7 +1181,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G28" t="n">
-        <v>1.59852147102356</v>
+        <v>1.59852159023285</v>
       </c>
       <c r="H28" t="n">
         <v>7500</v>
@@ -1210,7 +1210,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G29" t="n">
-        <v>1.54992914199829</v>
+        <v>1.54992926120758</v>
       </c>
       <c r="H29" t="n">
         <v>25500</v>
@@ -1326,7 +1326,7 @@
         <v>1.75800001621246</v>
       </c>
       <c r="G33" t="n">
-        <v>1.47285151481628</v>
+        <v>1.47285163402557</v>
       </c>
       <c r="H33" t="n">
         <v>1500</v>
@@ -1355,7 +1355,7 @@
         <v>1.75800001621246</v>
       </c>
       <c r="G34" t="n">
-        <v>1.47285151481628</v>
+        <v>1.47285163402557</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G35" t="n">
-        <v>1.41169214248657</v>
+        <v>1.41169226169586</v>
       </c>
       <c r="H35" t="n">
         <v>12000</v>
@@ -1413,7 +1413,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G36" t="n">
-        <v>1.38655817508698</v>
+        <v>1.38655805587769</v>
       </c>
       <c r="H36" t="n">
         <v>3000</v>
@@ -1616,7 +1616,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G43" t="n">
-        <v>1.19805324077606</v>
+        <v>1.19805335998535</v>
       </c>
       <c r="H43" t="n">
         <v>10500</v>
@@ -1761,7 +1761,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G48" t="n">
-        <v>1.26926624774933</v>
+        <v>1.26926636695862</v>
       </c>
       <c r="H48" t="n">
         <v>27000</v>
@@ -1790,7 +1790,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G49" t="n">
-        <v>1.30277824401855</v>
+        <v>1.30277812480927</v>
       </c>
       <c r="H49" t="n">
         <v>48000</v>
@@ -1819,7 +1819,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G50" t="n">
-        <v>1.30277824401855</v>
+        <v>1.30277812480927</v>
       </c>
       <c r="H50" t="n">
         <v>54000</v>
@@ -2051,7 +2051,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>1.23994326591492</v>
+        <v>1.23994338512421</v>
       </c>
       <c r="H58" t="n">
         <v>7500</v>
@@ -2167,7 +2167,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G62" t="n">
-        <v>1.23994326591492</v>
+        <v>1.23994338512421</v>
       </c>
       <c r="H62" t="n">
         <v>10500</v>
@@ -2225,7 +2225,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G64" t="n">
-        <v>1.27764439582825</v>
+        <v>1.27764427661896</v>
       </c>
       <c r="H64" t="n">
         <v>4500</v>
@@ -2254,7 +2254,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G65" t="n">
-        <v>1.26926624774933</v>
+        <v>1.26926636695862</v>
       </c>
       <c r="H65" t="n">
         <v>1500</v>
@@ -2283,7 +2283,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G66" t="n">
-        <v>1.26088845729828</v>
+        <v>1.26088833808899</v>
       </c>
       <c r="H66" t="n">
         <v>21000</v>
@@ -2312,7 +2312,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G67" t="n">
-        <v>1.23994326591492</v>
+        <v>1.23994338512421</v>
       </c>
       <c r="H67" t="n">
         <v>16500</v>
@@ -2486,7 +2486,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G73" t="n">
-        <v>1.30277824401855</v>
+        <v>1.30277812480927</v>
       </c>
       <c r="H73" t="n">
         <v>1500</v>
@@ -2660,7 +2660,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G79" t="n">
-        <v>1.27764439582825</v>
+        <v>1.27764427661896</v>
       </c>
       <c r="H79" t="n">
         <v>12000</v>
@@ -2689,7 +2689,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G80" t="n">
-        <v>1.27764439582825</v>
+        <v>1.27764427661896</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G83" t="n">
-        <v>1.3404792547226</v>
+        <v>1.34047937393188</v>
       </c>
       <c r="H83" t="n">
         <v>19500</v>
@@ -2805,7 +2805,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G84" t="n">
-        <v>1.35723519325256</v>
+        <v>1.35723531246185</v>
       </c>
       <c r="H84" t="n">
         <v>39000</v>
@@ -2863,7 +2863,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G86" t="n">
-        <v>1.3195344209671</v>
+        <v>1.31953430175781</v>
       </c>
       <c r="H86" t="n">
         <v>9000</v>
@@ -2892,7 +2892,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G87" t="n">
-        <v>1.30696725845337</v>
+        <v>1.30696737766266</v>
       </c>
       <c r="H87" t="n">
         <v>13500</v>
@@ -2950,7 +2950,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G89" t="n">
-        <v>1.26088845729828</v>
+        <v>1.26088833808899</v>
       </c>
       <c r="H89" t="n">
         <v>6000</v>
@@ -2979,7 +2979,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G90" t="n">
-        <v>1.26088845729828</v>
+        <v>1.26088833808899</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G91" t="n">
-        <v>1.26088845729828</v>
+        <v>1.26088833808899</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G92" t="n">
-        <v>1.26088845729828</v>
+        <v>1.26088833808899</v>
       </c>
       <c r="H92" t="n">
         <v>1500</v>
@@ -3066,7 +3066,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G93" t="n">
-        <v>1.26088845729828</v>
+        <v>1.26088833808899</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G96" t="n">
-        <v>1.26926624774933</v>
+        <v>1.26926636695862</v>
       </c>
       <c r="H96" t="n">
         <v>1500</v>
@@ -3182,7 +3182,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G97" t="n">
-        <v>1.26926624774933</v>
+        <v>1.26926636695862</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>1.5</v>
       </c>
       <c r="G99" t="n">
-        <v>1.29225826263428</v>
+        <v>1.29225814342499</v>
       </c>
       <c r="H99" t="n">
         <v>4500</v>
@@ -3269,7 +3269,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G100" t="n">
-        <v>1.22764503955841</v>
+        <v>1.2276451587677</v>
       </c>
       <c r="H100" t="n">
         <v>30000</v>
@@ -3298,7 +3298,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G101" t="n">
-        <v>1.21903002262115</v>
+        <v>1.21903014183044</v>
       </c>
       <c r="H101" t="n">
         <v>22500</v>
@@ -3327,7 +3327,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G102" t="n">
-        <v>1.27502810955048</v>
+        <v>1.27502799034119</v>
       </c>
       <c r="H102" t="n">
         <v>9000</v>
@@ -3356,7 +3356,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G103" t="n">
-        <v>1.27502810955048</v>
+        <v>1.27502799034119</v>
       </c>
       <c r="H103" t="n">
         <v>9000</v>
@@ -3385,7 +3385,7 @@
         <v>1.375</v>
       </c>
       <c r="G104" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H104" t="n">
         <v>9000</v>
@@ -3501,7 +3501,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G108" t="n">
-        <v>1.1285719871521</v>
+        <v>1.12857210636139</v>
       </c>
       <c r="H108" t="n">
         <v>1500</v>
@@ -3530,7 +3530,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G109" t="n">
-        <v>1.1285719871521</v>
+        <v>1.12857210636139</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G110" t="n">
-        <v>1.1285719871521</v>
+        <v>1.12857210636139</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G111" t="n">
-        <v>1.1285719871521</v>
+        <v>1.12857210636139</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G112" t="n">
-        <v>1.1285719871521</v>
+        <v>1.12857210636139</v>
       </c>
       <c r="H112" t="n">
         <v>3000</v>
@@ -3646,7 +3646,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G113" t="n">
-        <v>1.2104150056839</v>
+        <v>1.21041512489319</v>
       </c>
       <c r="H113" t="n">
         <v>9000</v>
@@ -3675,7 +3675,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G114" t="n">
-        <v>1.21903002262115</v>
+        <v>1.21903014183044</v>
       </c>
       <c r="H114" t="n">
         <v>13500</v>
@@ -3704,7 +3704,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G115" t="n">
-        <v>1.1931848526001</v>
+        <v>1.19318497180939</v>
       </c>
       <c r="H115" t="n">
         <v>4500</v>
@@ -3733,7 +3733,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G116" t="n">
-        <v>1.1931848526001</v>
+        <v>1.19318497180939</v>
       </c>
       <c r="H116" t="n">
         <v>1500</v>
@@ -3762,7 +3762,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G117" t="n">
-        <v>1.1931848526001</v>
+        <v>1.19318497180939</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G118" t="n">
-        <v>1.17164731025696</v>
+        <v>1.17164742946625</v>
       </c>
       <c r="H118" t="n">
         <v>10500</v>
@@ -3820,7 +3820,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G119" t="n">
-        <v>1.18887734413147</v>
+        <v>1.18887746334076</v>
       </c>
       <c r="H119" t="n">
         <v>1500</v>
@@ -3849,7 +3849,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G120" t="n">
-        <v>1.18887734413147</v>
+        <v>1.18887746334076</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G121" t="n">
-        <v>1.18887734413147</v>
+        <v>1.18887746334076</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G122" t="n">
-        <v>1.2104150056839</v>
+        <v>1.21041512489319</v>
       </c>
       <c r="H122" t="n">
         <v>1500</v>
@@ -3936,7 +3936,7 @@
         <v>1.375</v>
       </c>
       <c r="G123" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H123" t="n">
         <v>3000</v>
@@ -3965,7 +3965,7 @@
         <v>1.375</v>
       </c>
       <c r="G124" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G125" t="n">
-        <v>1.18026232719421</v>
+        <v>1.1802624464035</v>
       </c>
       <c r="H125" t="n">
         <v>3000</v>
@@ -4023,7 +4023,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G126" t="n">
-        <v>1.18887734413147</v>
+        <v>1.18887746334076</v>
       </c>
       <c r="H126" t="n">
         <v>3000</v>
@@ -4052,7 +4052,7 @@
         <v>1.375</v>
       </c>
       <c r="G127" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H127" t="n">
         <v>1500</v>
@@ -4081,7 +4081,7 @@
         <v>1.375</v>
       </c>
       <c r="G128" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>1.375</v>
       </c>
       <c r="G129" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H129" t="n">
         <v>3000</v>
@@ -4139,7 +4139,7 @@
         <v>1.375</v>
       </c>
       <c r="G130" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>1.375</v>
       </c>
       <c r="G131" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -4197,7 +4197,7 @@
         <v>1.375</v>
       </c>
       <c r="G132" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H132" t="n">
         <v>1500</v>
@@ -4226,7 +4226,7 @@
         <v>1.375</v>
       </c>
       <c r="G133" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>1.375</v>
       </c>
       <c r="G134" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>1.375</v>
       </c>
       <c r="G135" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>1.375</v>
       </c>
       <c r="G136" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>1.375</v>
       </c>
       <c r="G137" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H137" t="n">
         <v>1500</v>
@@ -4371,7 +4371,7 @@
         <v>1.375</v>
       </c>
       <c r="G138" t="n">
-        <v>1.18456983566284</v>
+        <v>1.18456995487213</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G139" t="n">
-        <v>1.20610737800598</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H139" t="n">
         <v>9000</v>
@@ -4429,7 +4429,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G140" t="n">
-        <v>1.20610737800598</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H140" t="n">
         <v>1500</v>
@@ -4458,7 +4458,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G141" t="n">
-        <v>1.20610737800598</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G142" t="n">
-        <v>1.20610737800598</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G143" t="n">
-        <v>1.20610737800598</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G144" t="n">
-        <v>1.20610737800598</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G145" t="n">
-        <v>1.20610737800598</v>
+        <v>1.20610761642456</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G146" t="n">
-        <v>1.13287961483002</v>
+        <v>1.13287973403931</v>
       </c>
       <c r="H146" t="n">
         <v>6000</v>
@@ -4632,7 +4632,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G147" t="n">
-        <v>1.24056768417358</v>
+        <v>1.24056780338287</v>
       </c>
       <c r="H147" t="n">
         <v>18000</v>
@@ -4661,7 +4661,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G148" t="n">
-        <v>1.23195254802704</v>
+        <v>1.23195266723633</v>
       </c>
       <c r="H148" t="n">
         <v>3000</v>
@@ -4690,7 +4690,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G149" t="n">
-        <v>1.23195254802704</v>
+        <v>1.23195266723633</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G150" t="n">
-        <v>1.23195254802704</v>
+        <v>1.23195266723633</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G151" t="n">
-        <v>1.16733980178833</v>
+        <v>1.16733992099762</v>
       </c>
       <c r="H151" t="n">
         <v>28500</v>
@@ -4777,7 +4777,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G152" t="n">
-        <v>1.17595481872559</v>
+        <v>1.17595493793488</v>
       </c>
       <c r="H152" t="n">
         <v>18000</v>
@@ -4806,7 +4806,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G153" t="n">
-        <v>1.17164731025696</v>
+        <v>1.17164742946625</v>
       </c>
       <c r="H153" t="n">
         <v>7500</v>
@@ -4835,7 +4835,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G154" t="n">
-        <v>1.16733980178833</v>
+        <v>1.16733992099762</v>
       </c>
       <c r="H154" t="n">
         <v>1500</v>
@@ -4864,7 +4864,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G155" t="n">
-        <v>1.16733980178833</v>
+        <v>1.16733992099762</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G156" t="n">
-        <v>1.16733980178833</v>
+        <v>1.16733992099762</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G157" t="n">
-        <v>1.16733980178833</v>
+        <v>1.16733992099762</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G158" t="n">
-        <v>1.16733980178833</v>
+        <v>1.16733992099762</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>1.16733980178833</v>
+        <v>1.16733992099762</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G160" t="n">
-        <v>1.16733980178833</v>
+        <v>1.16733992099762</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G161" t="n">
-        <v>1.18026232719421</v>
+        <v>1.1802624464035</v>
       </c>
       <c r="H161" t="n">
         <v>4500</v>
@@ -5357,7 +5357,7 @@
         <v>1.25</v>
       </c>
       <c r="G172" t="n">
-        <v>1.07688188552856</v>
+        <v>1.07688176631927</v>
       </c>
       <c r="H172" t="n">
         <v>4500</v>
@@ -5386,7 +5386,7 @@
         <v>1.25</v>
       </c>
       <c r="G173" t="n">
-        <v>1.07688188552856</v>
+        <v>1.07688176631927</v>
       </c>
       <c r="H173" t="n">
         <v>33000</v>
@@ -5415,7 +5415,7 @@
         <v>1.25</v>
       </c>
       <c r="G174" t="n">
-        <v>1.07688188552856</v>
+        <v>1.07688176631927</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>1.25</v>
       </c>
       <c r="G175" t="n">
-        <v>1.07688188552856</v>
+        <v>1.07688176631927</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>1.25</v>
       </c>
       <c r="G176" t="n">
-        <v>1.07688188552856</v>
+        <v>1.07688176631927</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>1.25</v>
       </c>
       <c r="G177" t="n">
-        <v>1.07688188552856</v>
+        <v>1.07688176631927</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G179" t="n">
-        <v>1.08549690246582</v>
+        <v>1.08549678325653</v>
       </c>
       <c r="H179" t="n">
         <v>7500</v>
@@ -5589,7 +5589,7 @@
         <v>1.25</v>
       </c>
       <c r="G180" t="n">
-        <v>1.07688188552856</v>
+        <v>1.07688176631927</v>
       </c>
       <c r="H180" t="n">
         <v>10500</v>
@@ -5618,7 +5618,7 @@
         <v>1.25</v>
       </c>
       <c r="G181" t="n">
-        <v>1.07688188552856</v>
+        <v>1.07688176631927</v>
       </c>
       <c r="H181" t="n">
         <v>1500</v>
@@ -5821,7 +5821,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G188" t="n">
-        <v>0.999346315860748</v>
+        <v>0.999346137046814</v>
       </c>
       <c r="H188" t="n">
         <v>4500</v>
@@ -5879,7 +5879,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G190" t="n">
-        <v>0.92611837387085</v>
+        <v>0.926118314266205</v>
       </c>
       <c r="H190" t="n">
         <v>63000</v>
@@ -5908,7 +5908,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G191" t="n">
-        <v>0.92611837387085</v>
+        <v>0.926118314266205</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G192" t="n">
-        <v>0.92611837387085</v>
+        <v>0.926118314266205</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G193" t="n">
-        <v>0.92611837387085</v>
+        <v>0.926118314266205</v>
       </c>
       <c r="H193" t="n">
         <v>1500</v>
@@ -5995,7 +5995,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G194" t="n">
-        <v>0.900273144245148</v>
+        <v>0.900273084640503</v>
       </c>
       <c r="H194" t="n">
         <v>9000</v>
@@ -6024,7 +6024,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G195" t="n">
-        <v>0.900273144245148</v>
+        <v>0.900273084640503</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G196" t="n">
-        <v>0.900273144245148</v>
+        <v>0.900273084640503</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>0.89596551656723</v>
+        <v>0.895965576171875</v>
       </c>
       <c r="H200" t="n">
         <v>6000</v>
@@ -6256,7 +6256,7 @@
         <v>1</v>
       </c>
       <c r="G203" t="n">
-        <v>0.861505448818207</v>
+        <v>0.861505389213562</v>
       </c>
       <c r="H203" t="n">
         <v>1500</v>
@@ -6285,7 +6285,7 @@
         <v>1</v>
       </c>
       <c r="G204" t="n">
-        <v>0.861505448818207</v>
+        <v>0.861505389213562</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G205" t="n">
-        <v>0.849444389343262</v>
+        <v>0.849444329738617</v>
       </c>
       <c r="H205" t="n">
         <v>9000</v>
@@ -6343,7 +6343,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G206" t="n">
-        <v>0.865812957286835</v>
+        <v>0.86581289768219</v>
       </c>
       <c r="H206" t="n">
         <v>3000</v>
@@ -6430,7 +6430,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G209" t="n">
-        <v>0.891658008098602</v>
+        <v>0.891658067703247</v>
       </c>
       <c r="H209" t="n">
         <v>3000</v>
@@ -7010,7 +7010,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G229" t="n">
-        <v>0.865812957286835</v>
+        <v>0.86581289768219</v>
       </c>
       <c r="H229" t="n">
         <v>19500</v>
@@ -7039,7 +7039,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G230" t="n">
-        <v>0.865812957286835</v>
+        <v>0.86581289768219</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>1</v>
       </c>
       <c r="G231" t="n">
-        <v>0.861505448818207</v>
+        <v>0.861505389213562</v>
       </c>
       <c r="H231" t="n">
         <v>6000</v>
@@ -7300,7 +7300,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G239" t="n">
-        <v>0.69954240322113</v>
+        <v>0.699542343616486</v>
       </c>
       <c r="H239" t="n">
         <v>16500</v>
@@ -7358,7 +7358,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G241" t="n">
-        <v>0.7391716837883</v>
+        <v>0.739171624183655</v>
       </c>
       <c r="H241" t="n">
         <v>12000</v>
@@ -7387,7 +7387,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G242" t="n">
-        <v>0.792585015296936</v>
+        <v>0.792584955692291</v>
       </c>
       <c r="H242" t="n">
         <v>75000</v>
@@ -7474,7 +7474,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G245" t="n">
-        <v>0.83566027879715</v>
+        <v>0.835660338401794</v>
       </c>
       <c r="H245" t="n">
         <v>43500</v>
@@ -7503,7 +7503,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G246" t="n">
-        <v>0.844275295734406</v>
+        <v>0.84427535533905</v>
       </c>
       <c r="H246" t="n">
         <v>45000</v>
@@ -7561,7 +7561,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G248" t="n">
-        <v>0.89596551656723</v>
+        <v>0.895965576171875</v>
       </c>
       <c r="H248" t="n">
         <v>25500</v>
@@ -7590,7 +7590,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G249" t="n">
-        <v>0.990731298923492</v>
+        <v>0.990731120109558</v>
       </c>
       <c r="H249" t="n">
         <v>90000</v>
@@ -7619,7 +7619,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G250" t="n">
-        <v>1.10703444480896</v>
+        <v>1.10703432559967</v>
       </c>
       <c r="H250" t="n">
         <v>192000</v>
@@ -7677,7 +7677,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G252" t="n">
-        <v>1.07257437705994</v>
+        <v>1.07257425785065</v>
       </c>
       <c r="H252" t="n">
         <v>73500</v>
@@ -7735,7 +7735,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G254" t="n">
-        <v>1.03380656242371</v>
+        <v>1.03380644321442</v>
       </c>
       <c r="H254" t="n">
         <v>37500</v>
@@ -7764,7 +7764,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G255" t="n">
-        <v>1.04242157936096</v>
+        <v>1.04242146015167</v>
       </c>
       <c r="H255" t="n">
         <v>22500</v>
@@ -7822,7 +7822,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G257" t="n">
-        <v>1.07257437705994</v>
+        <v>1.07257425785065</v>
       </c>
       <c r="H257" t="n">
         <v>45000</v>
@@ -7880,7 +7880,7 @@
         <v>1.25</v>
       </c>
       <c r="G259" t="n">
-        <v>1.07688188552856</v>
+        <v>1.07688176631927</v>
       </c>
       <c r="H259" t="n">
         <v>4500</v>
@@ -7938,7 +7938,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G261" t="n">
-        <v>1.10703444480896</v>
+        <v>1.10703432559967</v>
       </c>
       <c r="H261" t="n">
         <v>48000</v>
@@ -7996,7 +7996,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G263" t="n">
-        <v>1.11134195327759</v>
+        <v>1.1113418340683</v>
       </c>
       <c r="H263" t="n">
         <v>24000</v>
@@ -8112,7 +8112,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G267" t="n">
-        <v>1.11134195327759</v>
+        <v>1.1113418340683</v>
       </c>
       <c r="H267" t="n">
         <v>69000</v>
@@ -8141,7 +8141,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G268" t="n">
-        <v>1.11134195327759</v>
+        <v>1.1113418340683</v>
       </c>
       <c r="H268" t="n">
         <v>7500</v>
@@ -8170,7 +8170,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G269" t="n">
-        <v>1.11134195327759</v>
+        <v>1.1113418340683</v>
       </c>
       <c r="H269" t="n">
         <v>4500</v>
@@ -8228,7 +8228,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G271" t="n">
-        <v>1.11134195327759</v>
+        <v>1.1113418340683</v>
       </c>
       <c r="H271" t="n">
         <v>63000</v>
@@ -8315,7 +8315,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G274" t="n">
-        <v>1.17164731025696</v>
+        <v>1.17164742946625</v>
       </c>
       <c r="H274" t="n">
         <v>54000</v>
@@ -8344,7 +8344,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>1.14762723445892</v>
+        <v>1.14762711524963</v>
       </c>
       <c r="H275" t="n">
         <v>22500</v>
@@ -8605,7 +8605,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G284" t="n">
-        <v>1.08535289764404</v>
+        <v>1.08535277843475</v>
       </c>
       <c r="H284" t="n">
         <v>18000</v>
@@ -8634,7 +8634,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G285" t="n">
-        <v>1.05421566963196</v>
+        <v>1.05421555042267</v>
       </c>
       <c r="H285" t="n">
         <v>16500</v>
@@ -8692,7 +8692,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G287" t="n">
-        <v>1.01863038539886</v>
+        <v>1.01863026618958</v>
       </c>
       <c r="H287" t="n">
         <v>19500</v>
@@ -8721,7 +8721,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G288" t="n">
-        <v>1.01863038539886</v>
+        <v>1.01863026618958</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G290" t="n">
-        <v>1.02307856082916</v>
+        <v>1.02307844161987</v>
       </c>
       <c r="H290" t="n">
         <v>3000</v>
@@ -8808,7 +8808,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G291" t="n">
-        <v>1.02307856082916</v>
+        <v>1.02307844161987</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G294" t="n">
-        <v>0.98749315738678</v>
+        <v>0.987493216991425</v>
       </c>
       <c r="H294" t="n">
         <v>4500</v>
@@ -9069,7 +9069,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G300" t="n">
-        <v>1.02307856082916</v>
+        <v>1.02307844161987</v>
       </c>
       <c r="H300" t="n">
         <v>10500</v>
@@ -9185,7 +9185,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G304" t="n">
-        <v>1.02752673625946</v>
+        <v>1.02752661705017</v>
       </c>
       <c r="H304" t="n">
         <v>25500</v>
@@ -9301,7 +9301,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G308" t="n">
-        <v>0.983044981956482</v>
+        <v>0.983045041561127</v>
       </c>
       <c r="H308" t="n">
         <v>12000</v>
@@ -9533,7 +9533,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G316" t="n">
-        <v>0.98749315738678</v>
+        <v>0.987493216991425</v>
       </c>
       <c r="H316" t="n">
         <v>1500</v>
@@ -9562,7 +9562,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G317" t="n">
-        <v>0.983044981956482</v>
+        <v>0.983045041561127</v>
       </c>
       <c r="H317" t="n">
         <v>3000</v>
@@ -9591,7 +9591,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G318" t="n">
-        <v>0.920770585536957</v>
+        <v>0.920770645141602</v>
       </c>
       <c r="H318" t="n">
         <v>12000</v>
@@ -9823,7 +9823,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G326" t="n">
-        <v>1.06311213970184</v>
+        <v>1.06311202049255</v>
       </c>
       <c r="H326" t="n">
         <v>1500</v>
@@ -9852,7 +9852,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G327" t="n">
-        <v>1.05866396427155</v>
+        <v>1.05866384506226</v>
       </c>
       <c r="H327" t="n">
         <v>4500</v>
@@ -9881,7 +9881,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G328" t="n">
-        <v>1.05866396427155</v>
+        <v>1.05866384506226</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G333" t="n">
-        <v>1.08535289764404</v>
+        <v>1.08535277843475</v>
       </c>
       <c r="H333" t="n">
         <v>6000</v>
@@ -10055,7 +10055,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G334" t="n">
-        <v>1.12093830108643</v>
+        <v>1.12093818187714</v>
       </c>
       <c r="H334" t="n">
         <v>63000</v>
@@ -10113,7 +10113,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>1.09424936771393</v>
+        <v>1.09424924850464</v>
       </c>
       <c r="H336" t="n">
         <v>36000</v>
@@ -10200,7 +10200,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G339" t="n">
-        <v>1.08535289764404</v>
+        <v>1.08535277843475</v>
       </c>
       <c r="H339" t="n">
         <v>4500</v>
@@ -10229,7 +10229,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G340" t="n">
-        <v>1.09424936771393</v>
+        <v>1.09424924850464</v>
       </c>
       <c r="H340" t="n">
         <v>13500</v>
@@ -10258,7 +10258,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G341" t="n">
-        <v>1.09424936771393</v>
+        <v>1.09424924850464</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G346" t="n">
-        <v>1.03197491168976</v>
+        <v>1.03197479248047</v>
       </c>
       <c r="H346" t="n">
         <v>34500</v>
@@ -10432,7 +10432,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G347" t="n">
-        <v>1.02307856082916</v>
+        <v>1.02307844161987</v>
       </c>
       <c r="H347" t="n">
         <v>19500</v>
@@ -10461,7 +10461,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G348" t="n">
-        <v>1.03197491168976</v>
+        <v>1.03197479248047</v>
       </c>
       <c r="H348" t="n">
         <v>1500</v>
@@ -10606,7 +10606,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G353" t="n">
-        <v>1.02307856082916</v>
+        <v>1.02307844161987</v>
       </c>
       <c r="H353" t="n">
         <v>4500</v>
@@ -10635,7 +10635,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G354" t="n">
-        <v>1.02307856082916</v>
+        <v>1.02307844161987</v>
       </c>
       <c r="H354" t="n">
         <v>1500</v>
@@ -10664,7 +10664,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>1.05866396427155</v>
+        <v>1.05866384506226</v>
       </c>
       <c r="H355" t="n">
         <v>7500</v>
@@ -10693,7 +10693,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G356" t="n">
-        <v>1.05866396427155</v>
+        <v>1.05866384506226</v>
       </c>
       <c r="H356" t="n">
         <v>9000</v>

--- a/data/SAC.MI.xlsx
+++ b/data/SAC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.02749991416931</v>
       </c>
       <c r="G2" t="n">
-        <v>1.69863843917847</v>
+        <v>1.69863855838776</v>
       </c>
       <c r="H2" t="n">
         <v>193500</v>
@@ -456,7 +456,7 @@
         <v>1.96200001239777</v>
       </c>
       <c r="G3" t="n">
-        <v>1.64376270771027</v>
+        <v>1.64376258850098</v>
       </c>
       <c r="H3" t="n">
         <v>132000</v>
@@ -485,7 +485,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G4" t="n">
-        <v>1.52479517459869</v>
+        <v>1.52479529380798</v>
       </c>
       <c r="H4" t="n">
         <v>36000</v>
@@ -601,7 +601,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G8" t="n">
-        <v>1.82640302181244</v>
+        <v>1.82640290260315</v>
       </c>
       <c r="H8" t="n">
         <v>58500</v>
@@ -630,7 +630,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G9" t="n">
-        <v>1.75519001483917</v>
+        <v>1.75519013404846</v>
       </c>
       <c r="H9" t="n">
         <v>57000</v>
@@ -659,7 +659,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G10" t="n">
-        <v>1.70492208003998</v>
+        <v>1.70492219924927</v>
       </c>
       <c r="H10" t="n">
         <v>13500</v>
@@ -688,7 +688,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>1.70911109447479</v>
+        <v>1.7091109752655</v>
       </c>
       <c r="H11" t="n">
         <v>18000</v>
@@ -717,7 +717,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>1.70911109447479</v>
+        <v>1.7091109752655</v>
       </c>
       <c r="H12" t="n">
         <v>3000</v>
@@ -746,7 +746,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G13" t="n">
-        <v>1.70492208003998</v>
+        <v>1.70492219924927</v>
       </c>
       <c r="H13" t="n">
         <v>18000</v>
@@ -775,7 +775,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G14" t="n">
-        <v>1.73424506187439</v>
+        <v>1.73424518108368</v>
       </c>
       <c r="H14" t="n">
         <v>1500</v>
@@ -833,7 +833,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G16" t="n">
-        <v>1.73424506187439</v>
+        <v>1.73424518108368</v>
       </c>
       <c r="H16" t="n">
         <v>7500</v>
@@ -891,7 +891,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G18" t="n">
-        <v>1.61192643642426</v>
+        <v>1.61192631721497</v>
       </c>
       <c r="H18" t="n">
         <v>28500</v>
@@ -920,7 +920,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G19" t="n">
-        <v>1.59181916713715</v>
+        <v>1.59181904792786</v>
       </c>
       <c r="H19" t="n">
         <v>16500</v>
@@ -949,7 +949,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G20" t="n">
-        <v>1.59852159023285</v>
+        <v>1.59852135181427</v>
       </c>
       <c r="H20" t="n">
         <v>16500</v>
@@ -978,7 +978,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G21" t="n">
-        <v>1.57841432094574</v>
+        <v>1.57841420173645</v>
       </c>
       <c r="H21" t="n">
         <v>6000</v>
@@ -1007,7 +1007,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G22" t="n">
-        <v>1.60522401332855</v>
+        <v>1.60522389411926</v>
       </c>
       <c r="H22" t="n">
         <v>6000</v>
@@ -1036,7 +1036,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G23" t="n">
-        <v>1.6018728017807</v>
+        <v>1.60187268257141</v>
       </c>
       <c r="H23" t="n">
         <v>13500</v>
@@ -1065,7 +1065,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G24" t="n">
-        <v>1.6018728017807</v>
+        <v>1.60187268257141</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G26" t="n">
-        <v>1.62030446529388</v>
+        <v>1.62030434608459</v>
       </c>
       <c r="H26" t="n">
         <v>9000</v>
@@ -1152,7 +1152,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G27" t="n">
-        <v>1.62030446529388</v>
+        <v>1.62030434608459</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1181,7 +1181,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G28" t="n">
-        <v>1.59852159023285</v>
+        <v>1.59852135181427</v>
       </c>
       <c r="H28" t="n">
         <v>7500</v>
@@ -1210,7 +1210,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G29" t="n">
-        <v>1.54992926120758</v>
+        <v>1.54992914199829</v>
       </c>
       <c r="H29" t="n">
         <v>25500</v>
@@ -1239,7 +1239,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G30" t="n">
-        <v>1.57841432094574</v>
+        <v>1.57841420173645</v>
       </c>
       <c r="H30" t="n">
         <v>24000</v>
@@ -1297,7 +1297,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G32" t="n">
-        <v>1.44604194164276</v>
+        <v>1.44604206085205</v>
       </c>
       <c r="H32" t="n">
         <v>18000</v>
@@ -1413,7 +1413,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G36" t="n">
-        <v>1.38655805587769</v>
+        <v>1.38655829429626</v>
       </c>
       <c r="H36" t="n">
         <v>3000</v>
@@ -1471,7 +1471,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G38" t="n">
-        <v>1.31534540653229</v>
+        <v>1.315345287323</v>
       </c>
       <c r="H38" t="n">
         <v>12000</v>
@@ -1529,7 +1529,7 @@
         <v>1.5</v>
       </c>
       <c r="G40" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H40" t="n">
         <v>15000</v>
@@ -1558,7 +1558,7 @@
         <v>1.5</v>
       </c>
       <c r="G41" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G45" t="n">
-        <v>1.21062028408051</v>
+        <v>1.21062040328979</v>
       </c>
       <c r="H45" t="n">
         <v>100500</v>
@@ -1703,7 +1703,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G46" t="n">
-        <v>1.22737634181976</v>
+        <v>1.22737646102905</v>
       </c>
       <c r="H46" t="n">
         <v>30000</v>
@@ -1732,7 +1732,7 @@
         <v>1.5</v>
       </c>
       <c r="G47" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H47" t="n">
         <v>28500</v>
@@ -1790,7 +1790,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G49" t="n">
-        <v>1.30277812480927</v>
+        <v>1.30277824401855</v>
       </c>
       <c r="H49" t="n">
         <v>48000</v>
@@ -1819,7 +1819,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G50" t="n">
-        <v>1.30277812480927</v>
+        <v>1.30277824401855</v>
       </c>
       <c r="H50" t="n">
         <v>54000</v>
@@ -1848,7 +1848,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G51" t="n">
-        <v>1.27345526218414</v>
+        <v>1.27345538139343</v>
       </c>
       <c r="H51" t="n">
         <v>7500</v>
@@ -1906,7 +1906,7 @@
         <v>1.5</v>
       </c>
       <c r="G53" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H53" t="n">
         <v>13500</v>
@@ -1935,7 +1935,7 @@
         <v>1.5</v>
       </c>
       <c r="G54" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>1.5</v>
       </c>
       <c r="G55" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>1.5</v>
       </c>
       <c r="G57" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H57" t="n">
         <v>9000</v>
@@ -2051,7 +2051,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>1.23994338512421</v>
+        <v>1.23994326591492</v>
       </c>
       <c r="H58" t="n">
         <v>7500</v>
@@ -2167,7 +2167,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G62" t="n">
-        <v>1.23994338512421</v>
+        <v>1.23994326591492</v>
       </c>
       <c r="H62" t="n">
         <v>10500</v>
@@ -2196,7 +2196,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G63" t="n">
-        <v>1.26507723331451</v>
+        <v>1.2650773525238</v>
       </c>
       <c r="H63" t="n">
         <v>15000</v>
@@ -2225,7 +2225,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G64" t="n">
-        <v>1.27764427661896</v>
+        <v>1.27764415740967</v>
       </c>
       <c r="H64" t="n">
         <v>4500</v>
@@ -2283,7 +2283,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G66" t="n">
-        <v>1.26088833808899</v>
+        <v>1.2608882188797</v>
       </c>
       <c r="H66" t="n">
         <v>21000</v>
@@ -2312,7 +2312,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G67" t="n">
-        <v>1.23994338512421</v>
+        <v>1.23994326591492</v>
       </c>
       <c r="H67" t="n">
         <v>16500</v>
@@ -2370,7 +2370,7 @@
         <v>1.5</v>
       </c>
       <c r="G69" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H69" t="n">
         <v>1500</v>
@@ -2399,7 +2399,7 @@
         <v>1.5</v>
       </c>
       <c r="G70" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G73" t="n">
-        <v>1.30277812480927</v>
+        <v>1.30277824401855</v>
       </c>
       <c r="H73" t="n">
         <v>1500</v>
@@ -2515,7 +2515,7 @@
         <v>1.5</v>
       </c>
       <c r="G74" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H74" t="n">
         <v>31500</v>
@@ -2544,7 +2544,7 @@
         <v>1.5</v>
       </c>
       <c r="G75" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>1.5</v>
       </c>
       <c r="G76" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>1.5</v>
       </c>
       <c r="G77" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H77" t="n">
         <v>3000</v>
@@ -2631,7 +2631,7 @@
         <v>1.5</v>
       </c>
       <c r="G78" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H78" t="n">
         <v>1500</v>
@@ -2660,7 +2660,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G79" t="n">
-        <v>1.27764427661896</v>
+        <v>1.27764415740967</v>
       </c>
       <c r="H79" t="n">
         <v>12000</v>
@@ -2689,7 +2689,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G80" t="n">
-        <v>1.27764427661896</v>
+        <v>1.27764415740967</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G84" t="n">
-        <v>1.35723531246185</v>
+        <v>1.35723519325256</v>
       </c>
       <c r="H84" t="n">
         <v>39000</v>
@@ -2834,7 +2834,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G85" t="n">
-        <v>1.32791221141815</v>
+        <v>1.32791233062744</v>
       </c>
       <c r="H85" t="n">
         <v>19500</v>
@@ -2863,7 +2863,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G86" t="n">
-        <v>1.31953430175781</v>
+        <v>1.3195344209671</v>
       </c>
       <c r="H86" t="n">
         <v>9000</v>
@@ -2892,7 +2892,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G87" t="n">
-        <v>1.30696737766266</v>
+        <v>1.30696725845337</v>
       </c>
       <c r="H87" t="n">
         <v>13500</v>
@@ -2950,7 +2950,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G89" t="n">
-        <v>1.26088833808899</v>
+        <v>1.2608882188797</v>
       </c>
       <c r="H89" t="n">
         <v>6000</v>
@@ -2979,7 +2979,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G90" t="n">
-        <v>1.26088833808899</v>
+        <v>1.2608882188797</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G91" t="n">
-        <v>1.26088833808899</v>
+        <v>1.2608882188797</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G92" t="n">
-        <v>1.26088833808899</v>
+        <v>1.2608882188797</v>
       </c>
       <c r="H92" t="n">
         <v>1500</v>
@@ -3066,7 +3066,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G93" t="n">
-        <v>1.26088833808899</v>
+        <v>1.2608882188797</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>1.5</v>
       </c>
       <c r="G95" t="n">
-        <v>1.25669932365417</v>
+        <v>1.25669944286346</v>
       </c>
       <c r="H95" t="n">
         <v>1500</v>
@@ -3240,7 +3240,7 @@
         <v>1.5</v>
       </c>
       <c r="G99" t="n">
-        <v>1.29225814342499</v>
+        <v>1.2922580242157</v>
       </c>
       <c r="H99" t="n">
         <v>4500</v>
@@ -3269,7 +3269,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G100" t="n">
-        <v>1.2276451587677</v>
+        <v>1.22764503955841</v>
       </c>
       <c r="H100" t="n">
         <v>30000</v>
@@ -3385,7 +3385,7 @@
         <v>1.375</v>
       </c>
       <c r="G104" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H104" t="n">
         <v>9000</v>
@@ -3443,7 +3443,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G106" t="n">
-        <v>1.14149475097656</v>
+        <v>1.14149463176727</v>
       </c>
       <c r="H106" t="n">
         <v>4500</v>
@@ -3472,7 +3472,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G107" t="n">
-        <v>1.14149475097656</v>
+        <v>1.14149463176727</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G113" t="n">
-        <v>1.21041512489319</v>
+        <v>1.2104150056839</v>
       </c>
       <c r="H113" t="n">
         <v>9000</v>
@@ -3704,7 +3704,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G115" t="n">
-        <v>1.19318497180939</v>
+        <v>1.1931848526001</v>
       </c>
       <c r="H115" t="n">
         <v>4500</v>
@@ -3733,7 +3733,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G116" t="n">
-        <v>1.19318497180939</v>
+        <v>1.1931848526001</v>
       </c>
       <c r="H116" t="n">
         <v>1500</v>
@@ -3762,7 +3762,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G117" t="n">
-        <v>1.19318497180939</v>
+        <v>1.1931848526001</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G118" t="n">
-        <v>1.17164742946625</v>
+        <v>1.17164731025696</v>
       </c>
       <c r="H118" t="n">
         <v>10500</v>
@@ -3907,7 +3907,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G122" t="n">
-        <v>1.21041512489319</v>
+        <v>1.2104150056839</v>
       </c>
       <c r="H122" t="n">
         <v>1500</v>
@@ -3936,7 +3936,7 @@
         <v>1.375</v>
       </c>
       <c r="G123" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H123" t="n">
         <v>3000</v>
@@ -3965,7 +3965,7 @@
         <v>1.375</v>
       </c>
       <c r="G124" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -4052,7 +4052,7 @@
         <v>1.375</v>
       </c>
       <c r="G127" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H127" t="n">
         <v>1500</v>
@@ -4081,7 +4081,7 @@
         <v>1.375</v>
       </c>
       <c r="G128" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>1.375</v>
       </c>
       <c r="G129" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H129" t="n">
         <v>3000</v>
@@ -4139,7 +4139,7 @@
         <v>1.375</v>
       </c>
       <c r="G130" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>1.375</v>
       </c>
       <c r="G131" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -4197,7 +4197,7 @@
         <v>1.375</v>
       </c>
       <c r="G132" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H132" t="n">
         <v>1500</v>
@@ -4226,7 +4226,7 @@
         <v>1.375</v>
       </c>
       <c r="G133" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>1.375</v>
       </c>
       <c r="G134" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>1.375</v>
       </c>
       <c r="G135" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>1.375</v>
       </c>
       <c r="G136" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>1.375</v>
       </c>
       <c r="G137" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H137" t="n">
         <v>1500</v>
@@ -4371,7 +4371,7 @@
         <v>1.375</v>
       </c>
       <c r="G138" t="n">
-        <v>1.18456995487213</v>
+        <v>1.18457007408142</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G146" t="n">
-        <v>1.13287973403931</v>
+        <v>1.13287961483002</v>
       </c>
       <c r="H146" t="n">
         <v>6000</v>
@@ -4632,7 +4632,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G147" t="n">
-        <v>1.24056780338287</v>
+        <v>1.24056792259216</v>
       </c>
       <c r="H147" t="n">
         <v>18000</v>
@@ -4748,7 +4748,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G151" t="n">
-        <v>1.16733992099762</v>
+        <v>1.16733980178833</v>
       </c>
       <c r="H151" t="n">
         <v>28500</v>
@@ -4806,7 +4806,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G153" t="n">
-        <v>1.17164742946625</v>
+        <v>1.17164731025696</v>
       </c>
       <c r="H153" t="n">
         <v>7500</v>
@@ -4835,7 +4835,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G154" t="n">
-        <v>1.16733992099762</v>
+        <v>1.16733980178833</v>
       </c>
       <c r="H154" t="n">
         <v>1500</v>
@@ -4864,7 +4864,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G155" t="n">
-        <v>1.16733992099762</v>
+        <v>1.16733980178833</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G156" t="n">
-        <v>1.16733992099762</v>
+        <v>1.16733980178833</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G157" t="n">
-        <v>1.16733992099762</v>
+        <v>1.16733980178833</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G158" t="n">
-        <v>1.16733992099762</v>
+        <v>1.16733980178833</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>1.16733992099762</v>
+        <v>1.16733980178833</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G160" t="n">
-        <v>1.16733992099762</v>
+        <v>1.16733980178833</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>1.25</v>
       </c>
       <c r="G172" t="n">
-        <v>1.07688176631927</v>
+        <v>1.07688164710999</v>
       </c>
       <c r="H172" t="n">
         <v>4500</v>
@@ -5386,7 +5386,7 @@
         <v>1.25</v>
       </c>
       <c r="G173" t="n">
-        <v>1.07688176631927</v>
+        <v>1.07688164710999</v>
       </c>
       <c r="H173" t="n">
         <v>33000</v>
@@ -5415,7 +5415,7 @@
         <v>1.25</v>
       </c>
       <c r="G174" t="n">
-        <v>1.07688176631927</v>
+        <v>1.07688164710999</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>1.25</v>
       </c>
       <c r="G175" t="n">
-        <v>1.07688176631927</v>
+        <v>1.07688164710999</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>1.25</v>
       </c>
       <c r="G176" t="n">
-        <v>1.07688176631927</v>
+        <v>1.07688164710999</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>1.25</v>
       </c>
       <c r="G177" t="n">
-        <v>1.07688176631927</v>
+        <v>1.07688164710999</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
         <v>1.25</v>
       </c>
       <c r="G180" t="n">
-        <v>1.07688176631927</v>
+        <v>1.07688164710999</v>
       </c>
       <c r="H180" t="n">
         <v>10500</v>
@@ -5618,7 +5618,7 @@
         <v>1.25</v>
       </c>
       <c r="G181" t="n">
-        <v>1.07688176631927</v>
+        <v>1.07688164710999</v>
       </c>
       <c r="H181" t="n">
         <v>1500</v>
@@ -5821,7 +5821,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G188" t="n">
-        <v>0.999346137046814</v>
+        <v>0.999346256256104</v>
       </c>
       <c r="H188" t="n">
         <v>4500</v>
@@ -5850,7 +5850,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G189" t="n">
-        <v>0.930425882339478</v>
+        <v>0.930425941944122</v>
       </c>
       <c r="H189" t="n">
         <v>45000</v>
@@ -5879,7 +5879,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G190" t="n">
-        <v>0.926118314266205</v>
+        <v>0.92611837387085</v>
       </c>
       <c r="H190" t="n">
         <v>63000</v>
@@ -5908,7 +5908,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G191" t="n">
-        <v>0.926118314266205</v>
+        <v>0.92611837387085</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G192" t="n">
-        <v>0.926118314266205</v>
+        <v>0.92611837387085</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G193" t="n">
-        <v>0.926118314266205</v>
+        <v>0.92611837387085</v>
       </c>
       <c r="H193" t="n">
         <v>1500</v>
@@ -5995,7 +5995,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G194" t="n">
-        <v>0.900273084640503</v>
+        <v>0.900273144245148</v>
       </c>
       <c r="H194" t="n">
         <v>9000</v>
@@ -6024,7 +6024,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G195" t="n">
-        <v>0.900273084640503</v>
+        <v>0.900273144245148</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G196" t="n">
-        <v>0.900273084640503</v>
+        <v>0.900273144245148</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G197" t="n">
-        <v>0.887350499629974</v>
+        <v>0.887350618839264</v>
       </c>
       <c r="H197" t="n">
         <v>3000</v>
@@ -6111,7 +6111,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G198" t="n">
-        <v>0.887350499629974</v>
+        <v>0.887350618839264</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G202" t="n">
-        <v>0.887350499629974</v>
+        <v>0.887350618839264</v>
       </c>
       <c r="H202" t="n">
         <v>7500</v>
@@ -6256,7 +6256,7 @@
         <v>1</v>
       </c>
       <c r="G203" t="n">
-        <v>0.861505389213562</v>
+        <v>0.861505448818207</v>
       </c>
       <c r="H203" t="n">
         <v>1500</v>
@@ -6285,7 +6285,7 @@
         <v>1</v>
       </c>
       <c r="G204" t="n">
-        <v>0.861505389213562</v>
+        <v>0.861505448818207</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G209" t="n">
-        <v>0.891658067703247</v>
+        <v>0.891658127307892</v>
       </c>
       <c r="H209" t="n">
         <v>3000</v>
@@ -6459,7 +6459,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G210" t="n">
-        <v>0.908888220787048</v>
+        <v>0.908888161182404</v>
       </c>
       <c r="H210" t="n">
         <v>1500</v>
@@ -6488,7 +6488,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G211" t="n">
-        <v>0.908888220787048</v>
+        <v>0.908888161182404</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G212" t="n">
-        <v>0.908888220787048</v>
+        <v>0.908888161182404</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G213" t="n">
-        <v>0.908888220787048</v>
+        <v>0.908888161182404</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>1</v>
       </c>
       <c r="G231" t="n">
-        <v>0.861505389213562</v>
+        <v>0.861505448818207</v>
       </c>
       <c r="H231" t="n">
         <v>6000</v>
@@ -7126,7 +7126,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G233" t="n">
-        <v>0.747786700725555</v>
+        <v>0.747786641120911</v>
       </c>
       <c r="H233" t="n">
         <v>31500</v>
@@ -7155,7 +7155,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G234" t="n">
-        <v>0.680589318275452</v>
+        <v>0.680589258670807</v>
       </c>
       <c r="H234" t="n">
         <v>120000</v>
@@ -7271,7 +7271,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G238" t="n">
-        <v>0.706434369087219</v>
+        <v>0.706434428691864</v>
       </c>
       <c r="H238" t="n">
         <v>63000</v>
@@ -7300,7 +7300,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G239" t="n">
-        <v>0.699542343616486</v>
+        <v>0.69954240322113</v>
       </c>
       <c r="H239" t="n">
         <v>16500</v>
@@ -7416,7 +7416,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G243" t="n">
-        <v>0.847721338272095</v>
+        <v>0.84772139787674</v>
       </c>
       <c r="H243" t="n">
         <v>48000</v>
@@ -7445,7 +7445,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G244" t="n">
-        <v>0.797753989696503</v>
+        <v>0.797754049301147</v>
       </c>
       <c r="H244" t="n">
         <v>63000</v>
@@ -7474,7 +7474,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G245" t="n">
-        <v>0.835660338401794</v>
+        <v>0.835660219192505</v>
       </c>
       <c r="H245" t="n">
         <v>43500</v>
@@ -7503,7 +7503,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G246" t="n">
-        <v>0.84427535533905</v>
+        <v>0.844275295734406</v>
       </c>
       <c r="H246" t="n">
         <v>45000</v>
@@ -7590,7 +7590,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G249" t="n">
-        <v>0.990731120109558</v>
+        <v>0.990731179714203</v>
       </c>
       <c r="H249" t="n">
         <v>90000</v>
@@ -7619,7 +7619,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G250" t="n">
-        <v>1.10703432559967</v>
+        <v>1.10703444480896</v>
       </c>
       <c r="H250" t="n">
         <v>192000</v>
@@ -7648,7 +7648,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G251" t="n">
-        <v>1.14149475097656</v>
+        <v>1.14149463176727</v>
       </c>
       <c r="H251" t="n">
         <v>184500</v>
@@ -7677,7 +7677,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G252" t="n">
-        <v>1.07257425785065</v>
+        <v>1.07257413864136</v>
       </c>
       <c r="H252" t="n">
         <v>73500</v>
@@ -7706,7 +7706,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G253" t="n">
-        <v>1.01226878166199</v>
+        <v>1.01226890087128</v>
       </c>
       <c r="H253" t="n">
         <v>136500</v>
@@ -7735,7 +7735,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G254" t="n">
-        <v>1.03380644321442</v>
+        <v>1.03380656242371</v>
       </c>
       <c r="H254" t="n">
         <v>37500</v>
@@ -7822,7 +7822,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G257" t="n">
-        <v>1.07257425785065</v>
+        <v>1.07257413864136</v>
       </c>
       <c r="H257" t="n">
         <v>45000</v>
@@ -7851,7 +7851,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>1.05965173244476</v>
+        <v>1.05965161323547</v>
       </c>
       <c r="H258" t="n">
         <v>18000</v>
@@ -7880,7 +7880,7 @@
         <v>1.25</v>
       </c>
       <c r="G259" t="n">
-        <v>1.07688176631927</v>
+        <v>1.07688164710999</v>
       </c>
       <c r="H259" t="n">
         <v>4500</v>
@@ -7938,7 +7938,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G261" t="n">
-        <v>1.10703432559967</v>
+        <v>1.10703444480896</v>
       </c>
       <c r="H261" t="n">
         <v>48000</v>
@@ -7996,7 +7996,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G263" t="n">
-        <v>1.1113418340683</v>
+        <v>1.11134195327759</v>
       </c>
       <c r="H263" t="n">
         <v>24000</v>
@@ -8112,7 +8112,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G267" t="n">
-        <v>1.1113418340683</v>
+        <v>1.11134195327759</v>
       </c>
       <c r="H267" t="n">
         <v>69000</v>
@@ -8141,7 +8141,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G268" t="n">
-        <v>1.1113418340683</v>
+        <v>1.11134195327759</v>
       </c>
       <c r="H268" t="n">
         <v>7500</v>
@@ -8170,7 +8170,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G269" t="n">
-        <v>1.1113418340683</v>
+        <v>1.11134195327759</v>
       </c>
       <c r="H269" t="n">
         <v>4500</v>
@@ -8228,7 +8228,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G271" t="n">
-        <v>1.1113418340683</v>
+        <v>1.11134195327759</v>
       </c>
       <c r="H271" t="n">
         <v>63000</v>
@@ -8286,7 +8286,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G273" t="n">
-        <v>1.13718724250793</v>
+        <v>1.13718712329865</v>
       </c>
       <c r="H273" t="n">
         <v>69000</v>
@@ -8315,7 +8315,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G274" t="n">
-        <v>1.17164742946625</v>
+        <v>1.17164731025696</v>
       </c>
       <c r="H274" t="n">
         <v>54000</v>
@@ -8344,7 +8344,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>1.14762711524963</v>
+        <v>1.14762723445892</v>
       </c>
       <c r="H275" t="n">
         <v>22500</v>
@@ -8402,7 +8402,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G277" t="n">
-        <v>1.12983453273773</v>
+        <v>1.12983465194702</v>
       </c>
       <c r="H277" t="n">
         <v>16500</v>
@@ -8431,7 +8431,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>1.12983453273773</v>
+        <v>1.12983465194702</v>
       </c>
       <c r="H278" t="n">
         <v>6000</v>
@@ -8460,7 +8460,7 @@
         <v>1.25</v>
       </c>
       <c r="G279" t="n">
-        <v>1.11204195022583</v>
+        <v>1.11204183101654</v>
       </c>
       <c r="H279" t="n">
         <v>12000</v>
@@ -8518,7 +8518,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G281" t="n">
-        <v>1.12983453273773</v>
+        <v>1.12983465194702</v>
       </c>
       <c r="H281" t="n">
         <v>6000</v>
@@ -8605,7 +8605,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G284" t="n">
-        <v>1.08535277843475</v>
+        <v>1.08535289764404</v>
       </c>
       <c r="H284" t="n">
         <v>18000</v>
@@ -8634,7 +8634,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G285" t="n">
-        <v>1.05421555042267</v>
+        <v>1.05421566963196</v>
       </c>
       <c r="H285" t="n">
         <v>16500</v>
@@ -8750,7 +8750,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G289" t="n">
-        <v>0.996389508247375</v>
+        <v>0.99638956785202</v>
       </c>
       <c r="H289" t="n">
         <v>12000</v>
@@ -8779,7 +8779,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G290" t="n">
-        <v>1.02307844161987</v>
+        <v>1.02307868003845</v>
       </c>
       <c r="H290" t="n">
         <v>3000</v>
@@ -8808,7 +8808,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G291" t="n">
-        <v>1.02307844161987</v>
+        <v>1.02307868003845</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G292" t="n">
-        <v>1.00528585910797</v>
+        <v>1.00528597831726</v>
       </c>
       <c r="H292" t="n">
         <v>10500</v>
@@ -8895,7 +8895,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G294" t="n">
-        <v>0.987493216991425</v>
+        <v>0.98749315738678</v>
       </c>
       <c r="H294" t="n">
         <v>4500</v>
@@ -8924,7 +8924,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G295" t="n">
-        <v>1.00528585910797</v>
+        <v>1.00528597831726</v>
       </c>
       <c r="H295" t="n">
         <v>27000</v>
@@ -9069,7 +9069,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G300" t="n">
-        <v>1.02307844161987</v>
+        <v>1.02307868003845</v>
       </c>
       <c r="H300" t="n">
         <v>10500</v>
@@ -9185,7 +9185,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G304" t="n">
-        <v>1.02752661705017</v>
+        <v>1.02752673625946</v>
       </c>
       <c r="H304" t="n">
         <v>25500</v>
@@ -9214,7 +9214,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G305" t="n">
-        <v>1.00528585910797</v>
+        <v>1.00528597831726</v>
       </c>
       <c r="H305" t="n">
         <v>15000</v>
@@ -9243,7 +9243,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G306" t="n">
-        <v>1.00528585910797</v>
+        <v>1.00528597831726</v>
       </c>
       <c r="H306" t="n">
         <v>3000</v>
@@ -9272,7 +9272,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G307" t="n">
-        <v>1.00528585910797</v>
+        <v>1.00528597831726</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G308" t="n">
-        <v>0.983045041561127</v>
+        <v>0.983044981956482</v>
       </c>
       <c r="H308" t="n">
         <v>12000</v>
@@ -9330,7 +9330,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G309" t="n">
-        <v>0.991941332817078</v>
+        <v>0.991941392421722</v>
       </c>
       <c r="H309" t="n">
         <v>1500</v>
@@ -9417,7 +9417,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G312" t="n">
-        <v>0.996389508247375</v>
+        <v>0.99638956785202</v>
       </c>
       <c r="H312" t="n">
         <v>1500</v>
@@ -9446,7 +9446,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G313" t="n">
-        <v>0.991941332817078</v>
+        <v>0.991941392421722</v>
       </c>
       <c r="H313" t="n">
         <v>3000</v>
@@ -9475,7 +9475,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G314" t="n">
-        <v>0.991941332817078</v>
+        <v>0.991941392421722</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G316" t="n">
-        <v>0.987493216991425</v>
+        <v>0.98749315738678</v>
       </c>
       <c r="H316" t="n">
         <v>1500</v>
@@ -9562,7 +9562,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G317" t="n">
-        <v>0.983045041561127</v>
+        <v>0.983044981956482</v>
       </c>
       <c r="H317" t="n">
         <v>3000</v>
@@ -9678,7 +9678,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G321" t="n">
-        <v>1.12983453273773</v>
+        <v>1.12983465194702</v>
       </c>
       <c r="H321" t="n">
         <v>24000</v>
@@ -9823,7 +9823,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G326" t="n">
-        <v>1.06311202049255</v>
+        <v>1.06311213970184</v>
       </c>
       <c r="H326" t="n">
         <v>1500</v>
@@ -10026,7 +10026,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G333" t="n">
-        <v>1.08535277843475</v>
+        <v>1.08535289764404</v>
       </c>
       <c r="H333" t="n">
         <v>6000</v>
@@ -10084,7 +10084,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G335" t="n">
-        <v>1.12983453273773</v>
+        <v>1.12983465194702</v>
       </c>
       <c r="H335" t="n">
         <v>57000</v>
@@ -10113,7 +10113,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G336" t="n">
-        <v>1.09424924850464</v>
+        <v>1.09424912929535</v>
       </c>
       <c r="H336" t="n">
         <v>36000</v>
@@ -10142,7 +10142,7 @@
         <v>1.25</v>
       </c>
       <c r="G337" t="n">
-        <v>1.11204195022583</v>
+        <v>1.11204183101654</v>
       </c>
       <c r="H337" t="n">
         <v>22500</v>
@@ -10171,7 +10171,7 @@
         <v>1.25</v>
       </c>
       <c r="G338" t="n">
-        <v>1.11204195022583</v>
+        <v>1.11204183101654</v>
       </c>
       <c r="H338" t="n">
         <v>4500</v>
@@ -10200,7 +10200,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G339" t="n">
-        <v>1.08535277843475</v>
+        <v>1.08535289764404</v>
       </c>
       <c r="H339" t="n">
         <v>4500</v>
@@ -10229,7 +10229,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G340" t="n">
-        <v>1.09424924850464</v>
+        <v>1.09424912929535</v>
       </c>
       <c r="H340" t="n">
         <v>13500</v>
@@ -10258,7 +10258,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G341" t="n">
-        <v>1.09424924850464</v>
+        <v>1.09424912929535</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G346" t="n">
-        <v>1.03197479248047</v>
+        <v>1.03197491168976</v>
       </c>
       <c r="H346" t="n">
         <v>34500</v>
@@ -10432,7 +10432,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G347" t="n">
-        <v>1.02307844161987</v>
+        <v>1.02307868003845</v>
       </c>
       <c r="H347" t="n">
         <v>19500</v>
@@ -10461,7 +10461,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G348" t="n">
-        <v>1.03197479248047</v>
+        <v>1.03197491168976</v>
       </c>
       <c r="H348" t="n">
         <v>1500</v>
@@ -10490,7 +10490,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G349" t="n">
-        <v>0.996389508247375</v>
+        <v>0.99638956785202</v>
       </c>
       <c r="H349" t="n">
         <v>24000</v>
@@ -10519,7 +10519,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G350" t="n">
-        <v>0.996389508247375</v>
+        <v>0.99638956785202</v>
       </c>
       <c r="H350" t="n">
         <v>3000</v>
@@ -10548,7 +10548,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G351" t="n">
-        <v>0.996389508247375</v>
+        <v>0.99638956785202</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -10577,7 +10577,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G352" t="n">
-        <v>0.996389508247375</v>
+        <v>0.99638956785202</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10606,7 +10606,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G353" t="n">
-        <v>1.02307844161987</v>
+        <v>1.02307868003845</v>
       </c>
       <c r="H353" t="n">
         <v>4500</v>
@@ -10635,7 +10635,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G354" t="n">
-        <v>1.02307844161987</v>
+        <v>1.02307868003845</v>
       </c>
       <c r="H354" t="n">
         <v>1500</v>
@@ -10896,7 +10896,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G363" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H363" t="n">
         <v>22500</v>
@@ -12317,7 +12317,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G412" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H412" t="n">
         <v>1500</v>
@@ -12491,7 +12491,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G418" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H418" t="n">
         <v>3000</v>
@@ -12520,7 +12520,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G419" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H419" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G420" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G421" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H421" t="n">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G422" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H422" t="n">
         <v>3000</v>
@@ -12636,7 +12636,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G423" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H423" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G424" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H424" t="n">
         <v>0</v>
@@ -12694,7 +12694,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G425" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G442" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H442" t="n">
         <v>3000</v>
@@ -13216,7 +13216,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G443" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G448" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H448" t="n">
         <v>1500</v>
@@ -13390,7 +13390,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G449" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H449" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G463" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H463" t="n">
         <v>6000</v>
@@ -13825,7 +13825,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G464" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H464" t="n">
         <v>1500</v>
@@ -13854,7 +13854,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G465" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H465" t="n">
         <v>6000</v>
@@ -13883,7 +13883,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G466" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H466" t="n">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G467" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H467" t="n">
         <v>1500</v>
@@ -13941,7 +13941,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G468" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H468" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G496" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H496" t="n">
         <v>6000</v>
@@ -14782,7 +14782,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G497" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H497" t="n">
         <v>0</v>
@@ -14811,7 +14811,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G498" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H498" t="n">
         <v>6000</v>
@@ -14840,7 +14840,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G499" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H499" t="n">
         <v>1500</v>
@@ -14869,7 +14869,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G500" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G518" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H518" t="n">
         <v>3000</v>
@@ -15420,7 +15420,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G519" t="n">
-        <v>1.03284275531769</v>
+        <v>1.03284287452698</v>
       </c>
       <c r="H519" t="n">
         <v>0</v>
@@ -15623,7 +15623,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G526" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H526" t="n">
         <v>24000</v>
@@ -15652,7 +15652,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G527" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H527" t="n">
         <v>18000</v>
@@ -16696,7 +16696,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G563" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H563" t="n">
         <v>10500</v>
@@ -16725,7 +16725,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G564" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H564" t="n">
         <v>9000</v>
@@ -16754,7 +16754,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G565" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H565" t="n">
         <v>0</v>
@@ -16783,7 +16783,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G566" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -16812,7 +16812,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G567" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G568" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H568" t="n">
         <v>4500</v>
@@ -16870,7 +16870,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G569" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H569" t="n">
         <v>0</v>
@@ -16899,7 +16899,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G570" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H570" t="n">
         <v>1500</v>
@@ -16928,7 +16928,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G571" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G572" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H572" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G573" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H573" t="n">
         <v>0</v>
@@ -17015,7 +17015,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G574" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H574" t="n">
         <v>0</v>
@@ -17392,7 +17392,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G587" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H587" t="n">
         <v>1500</v>
@@ -17421,7 +17421,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G588" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H588" t="n">
         <v>0</v>
@@ -17450,7 +17450,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G589" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -17479,7 +17479,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G590" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H590" t="n">
         <v>12000</v>
@@ -17508,7 +17508,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G591" t="n">
-        <v>0.986733853816986</v>
+        <v>0.986733734607697</v>
       </c>
       <c r="H591" t="n">
         <v>1500</v>
@@ -17537,7 +17537,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G592" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H592" t="n">
         <v>1500</v>
@@ -17566,7 +17566,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G593" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G594" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H594" t="n">
         <v>3000</v>
@@ -17624,7 +17624,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G595" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -17740,7 +17740,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G599" t="n">
-        <v>0.977511942386627</v>
+        <v>0.977511882781982</v>
       </c>
       <c r="H599" t="n">
         <v>9000</v>
@@ -17769,7 +17769,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G600" t="n">
-        <v>0.995955646038055</v>
+        <v>0.995955586433411</v>
       </c>
       <c r="H600" t="n">
         <v>1500</v>
@@ -28824,6 +28824,64 @@
         <v>9000</v>
       </c>
       <c r="I981" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="s">
+        <v>9</v>
+      </c>
+      <c r="B982" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C982" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="D982" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="E982" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="F982" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="G982" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="H982" t="n">
+        <v>0</v>
+      </c>
+      <c r="I982" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="s">
+        <v>9</v>
+      </c>
+      <c r="B983" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C983" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="D983" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E983" t="n">
+        <v>1.17999994754791</v>
+      </c>
+      <c r="F983" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="G983" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="H983" t="n">
+        <v>13500</v>
+      </c>
+      <c r="I983" t="s">
         <v>9</v>
       </c>
     </row>
